--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>69334</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.451999992132187</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.449000000953674</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.45100000500679</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.451499998569489</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>137085</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.451999992132187</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.444999992847443</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.45100000500679</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.442499995231628</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -62920,7 +62920,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="D2720" t="n">
-        <v>0.444999992847443</v>
+        <v>0.442499995231628</v>
       </c>
       <c r="E2720" t="n">
         <v>0.45100000500679</v>
@@ -62929,6 +62929,29 @@
         <v>0.442499995231628</v>
       </c>
       <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>154269</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.44650000333786</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.443500012159348</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.441000014543533</v>
+      </c>
+      <c r="G2721" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>126926</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.440499991178513</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.444000005722046</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.449499994516373</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>77965</v>
+        <v>90543</v>
       </c>
       <c r="C2715" t="n">
         <v>0.453999996185303</v>
       </c>
       <c r="D2715" t="n">
+        <v>0.449000000953674</v>
+      </c>
+      <c r="E2715" t="n">
         <v>0.450500011444092</v>
       </c>
-      <c r="E2715" t="n">
-        <v>0.453999996185303</v>
-      </c>
       <c r="F2715" t="n">
-        <v>0.452499985694885</v>
+        <v>0.45100000500679</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>241053</v>
+        <v>77965</v>
       </c>
       <c r="C2716" t="n">
-        <v>0.453500002622604</v>
+        <v>0.453999996185303</v>
       </c>
       <c r="D2716" t="n">
-        <v>0.449000000953674</v>
+        <v>0.450500011444092</v>
       </c>
       <c r="E2716" t="n">
-        <v>0.453000009059906</v>
+        <v>0.453999996185303</v>
       </c>
       <c r="F2716" t="n">
-        <v>0.451999992132187</v>
+        <v>0.452499985694885</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>156326</v>
+        <v>241053</v>
       </c>
       <c r="C2717" t="n">
+        <v>0.453500002622604</v>
+      </c>
+      <c r="D2717" t="n">
+        <v>0.449000000953674</v>
+      </c>
+      <c r="E2717" t="n">
         <v>0.453000009059906</v>
       </c>
-      <c r="D2717" t="n">
-        <v>0.449499994516373</v>
-      </c>
-      <c r="E2717" t="n">
-        <v>0.451499998569489</v>
-      </c>
       <c r="F2717" t="n">
-        <v>0.450500011444092</v>
+        <v>0.451999992132187</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>241690</v>
+        <v>156326</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.458999991416931</v>
+        <v>0.453000009059906</v>
       </c>
       <c r="D2718" t="n">
         <v>0.449499994516373</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.458999991416931</v>
+        <v>0.451499998569489</v>
       </c>
       <c r="F2718" t="n">
-        <v>0.449999988079071</v>
+        <v>0.450500011444092</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>69334</v>
+        <v>241690</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.451999992132187</v>
+        <v>0.458999991416931</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.449000000953674</v>
+        <v>0.449499994516373</v>
       </c>
       <c r="E2719" t="n">
-        <v>0.45100000500679</v>
+        <v>0.458999991416931</v>
       </c>
       <c r="F2719" t="n">
-        <v>0.451499998569489</v>
+        <v>0.449999988079071</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>137085</v>
+        <v>69334</v>
       </c>
       <c r="C2720" t="n">
         <v>0.451999992132187</v>
       </c>
       <c r="D2720" t="n">
-        <v>0.442499995231628</v>
+        <v>0.449000000953674</v>
       </c>
       <c r="E2720" t="n">
         <v>0.45100000500679</v>
       </c>
       <c r="F2720" t="n">
-        <v>0.442499995231628</v>
+        <v>0.451499998569489</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>154269</v>
+        <v>137085</v>
       </c>
       <c r="C2721" t="n">
-        <v>0.44650000333786</v>
+        <v>0.451999992132187</v>
       </c>
       <c r="D2721" t="n">
-        <v>0.4375</v>
+        <v>0.442499995231628</v>
       </c>
       <c r="E2721" t="n">
-        <v>0.443500012159348</v>
+        <v>0.45100000500679</v>
       </c>
       <c r="F2721" t="n">
-        <v>0.441000014543533</v>
+        <v>0.442499995231628</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>126926</v>
+        <v>154269</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.449999988079071</v>
+        <v>0.44650000333786</v>
       </c>
       <c r="D2722" t="n">
-        <v>0.440499991178513</v>
+        <v>0.4375</v>
       </c>
       <c r="E2722" t="n">
-        <v>0.444000005722046</v>
+        <v>0.443500012159348</v>
       </c>
       <c r="F2722" t="n">
+        <v>0.441000014543533</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>145601</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>0.45100000500679</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>0.444499999284744</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>0.45100000500679</v>
+      </c>
+      <c r="F2723" t="n">
         <v>0.449499994516373</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>0.456499993801117</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>0.446000009775162</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>102748</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.447499990463257</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.441000014543533</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.447499990463257</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.447499990463257</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.441000014543533</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>155714</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.446000009775162</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.435000002384186</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.443500012159348</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -63311,13 +63311,36 @@
         <v>0.446000009775162</v>
       </c>
       <c r="D2737" t="n">
-        <v>0.435000002384186</v>
+        <v>0.431499987840652</v>
       </c>
       <c r="E2737" t="n">
         <v>0.443500012159348</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.431499987840652</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>257046</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.43299999833107</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.421499997377396</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.43299999833107</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>0.43299999833107</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.421499997377396</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>253893</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>0.448500007390976</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>0.421499997377396</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>0.448500007390976</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>292331</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.435999989509583</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.435999989509583</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FNM.MI.xlsx
+++ b/data/FNM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.463899999856949</v>
       </c>
       <c r="G2" t="n">
-        <v>0.312055021524429</v>
+        <v>0.312055051326752</v>
       </c>
       <c r="H2" t="n">
         <v>113577</v>
@@ -456,7 +456,7 @@
         <v>0.464599996805191</v>
       </c>
       <c r="G3" t="n">
-        <v>0.312525928020477</v>
+        <v>0.312525898218155</v>
       </c>
       <c r="H3" t="n">
         <v>18674</v>
@@ -514,7 +514,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G5" t="n">
-        <v>0.304050177335739</v>
+        <v>0.304050147533417</v>
       </c>
       <c r="H5" t="n">
         <v>399163</v>
@@ -601,7 +601,7 @@
         <v>0.426099985837936</v>
       </c>
       <c r="G8" t="n">
-        <v>0.28662782907486</v>
+        <v>0.286627769470215</v>
       </c>
       <c r="H8" t="n">
         <v>360755</v>
@@ -630,7 +630,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G9" t="n">
-        <v>0.295978039503098</v>
+        <v>0.295978009700775</v>
       </c>
       <c r="H9" t="n">
         <v>173371</v>
@@ -659,7 +659,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G10" t="n">
-        <v>0.289251267910004</v>
+        <v>0.289251297712326</v>
       </c>
       <c r="H10" t="n">
         <v>179882</v>
@@ -688,7 +688,7 @@
         <v>0.408100008964539</v>
       </c>
       <c r="G11" t="n">
-        <v>0.274519622325897</v>
+        <v>0.27451965212822</v>
       </c>
       <c r="H11" t="n">
         <v>329854</v>
@@ -717,7 +717,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G12" t="n">
-        <v>0.262344121932983</v>
+        <v>0.262344151735306</v>
       </c>
       <c r="H12" t="n">
         <v>246084</v>
@@ -775,7 +775,7 @@
         <v>0.377099990844727</v>
       </c>
       <c r="G14" t="n">
-        <v>0.253666549921036</v>
+        <v>0.253666639328003</v>
       </c>
       <c r="H14" t="n">
         <v>171306</v>
@@ -833,7 +833,7 @@
         <v>0.384999990463257</v>
       </c>
       <c r="G16" t="n">
-        <v>0.258980751037598</v>
+        <v>0.25898078083992</v>
       </c>
       <c r="H16" t="n">
         <v>290169</v>
@@ -891,7 +891,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G18" t="n">
-        <v>0.26099881529808</v>
+        <v>0.260998785495758</v>
       </c>
       <c r="H18" t="n">
         <v>236528</v>
@@ -978,7 +978,7 @@
         <v>0.413399994373322</v>
       </c>
       <c r="G21" t="n">
-        <v>0.278084814548492</v>
+        <v>0.27808478474617</v>
       </c>
       <c r="H21" t="n">
         <v>427578</v>
@@ -1007,7 +1007,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G22" t="n">
-        <v>0.275797665119171</v>
+        <v>0.275797724723816</v>
       </c>
       <c r="H22" t="n">
         <v>95651</v>
@@ -1036,7 +1036,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G23" t="n">
-        <v>0.281179130077362</v>
+        <v>0.281179159879684</v>
       </c>
       <c r="H23" t="n">
         <v>354808</v>
@@ -1065,7 +1065,7 @@
         <v>0.392899990081787</v>
       </c>
       <c r="G24" t="n">
-        <v>0.264294922351837</v>
+        <v>0.26429495215416</v>
       </c>
       <c r="H24" t="n">
         <v>147174</v>
@@ -1094,7 +1094,7 @@
         <v>0.388300001621246</v>
       </c>
       <c r="G25" t="n">
-        <v>0.26120063662529</v>
+        <v>0.261200577020645</v>
       </c>
       <c r="H25" t="n">
         <v>88306</v>
@@ -1152,7 +1152,7 @@
         <v>0.370000004768372</v>
       </c>
       <c r="G27" t="n">
-        <v>0.248890608549118</v>
+        <v>0.248890563845634</v>
       </c>
       <c r="H27" t="n">
         <v>364032</v>
@@ -1210,7 +1210,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="G29" t="n">
-        <v>0.235437050461769</v>
+        <v>0.235437095165253</v>
       </c>
       <c r="H29" t="n">
         <v>192364</v>
@@ -1239,7 +1239,7 @@
         <v>0.340799987316132</v>
       </c>
       <c r="G30" t="n">
-        <v>0.22924841940403</v>
+        <v>0.229248404502869</v>
       </c>
       <c r="H30" t="n">
         <v>195790</v>
@@ -1297,7 +1297,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G32" t="n">
-        <v>0.259653449058533</v>
+        <v>0.259653478860855</v>
       </c>
       <c r="H32" t="n">
         <v>278993</v>
@@ -1326,7 +1326,7 @@
         <v>0.392500013113022</v>
       </c>
       <c r="G33" t="n">
-        <v>0.264025896787643</v>
+        <v>0.264025866985321</v>
       </c>
       <c r="H33" t="n">
         <v>383815</v>
@@ -1355,7 +1355,7 @@
         <v>0.390399992465973</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2626131772995</v>
+        <v>0.262613236904144</v>
       </c>
       <c r="H34" t="n">
         <v>83209</v>
@@ -1413,7 +1413,7 @@
         <v>0.385199993848801</v>
       </c>
       <c r="G36" t="n">
-        <v>0.259115308523178</v>
+        <v>0.259115278720856</v>
       </c>
       <c r="H36" t="n">
         <v>284174</v>
@@ -1442,7 +1442,7 @@
         <v>0.400200009346008</v>
       </c>
       <c r="G37" t="n">
-        <v>0.269205510616302</v>
+        <v>0.26920548081398</v>
       </c>
       <c r="H37" t="n">
         <v>39927</v>
@@ -1471,7 +1471,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G38" t="n">
-        <v>0.265034914016724</v>
+        <v>0.265034854412079</v>
       </c>
       <c r="H38" t="n">
         <v>251272</v>
@@ -1529,7 +1529,7 @@
         <v>0.381000012159348</v>
       </c>
       <c r="G40" t="n">
-        <v>0.256290048360825</v>
+        <v>0.256290107965469</v>
       </c>
       <c r="H40" t="n">
         <v>304962</v>
@@ -1558,7 +1558,7 @@
         <v>0.400999993085861</v>
       </c>
       <c r="G41" t="n">
-        <v>0.269743591547012</v>
+        <v>0.269743621349335</v>
       </c>
       <c r="H41" t="n">
         <v>98843</v>
@@ -1616,7 +1616,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G43" t="n">
-        <v>0.280506461858749</v>
+        <v>0.280506491661072</v>
       </c>
       <c r="H43" t="n">
         <v>340265</v>
@@ -1674,7 +1674,7 @@
         <v>0.410299986600876</v>
       </c>
       <c r="G45" t="n">
-        <v>0.275999516248703</v>
+        <v>0.275999486446381</v>
       </c>
       <c r="H45" t="n">
         <v>72859</v>
@@ -1790,7 +1790,7 @@
         <v>0.395700007677078</v>
       </c>
       <c r="G49" t="n">
-        <v>0.26617842912674</v>
+        <v>0.266178399324417</v>
       </c>
       <c r="H49" t="n">
         <v>35990</v>
@@ -1848,7 +1848,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G51" t="n">
-        <v>0.274452328681946</v>
+        <v>0.274452358484268</v>
       </c>
       <c r="H51" t="n">
         <v>183597</v>
@@ -1906,7 +1906,7 @@
         <v>0.420500010251999</v>
       </c>
       <c r="G53" t="n">
-        <v>0.282860845327377</v>
+        <v>0.282860785722733</v>
       </c>
       <c r="H53" t="n">
         <v>95744</v>
@@ -1935,7 +1935,7 @@
         <v>0.436699986457825</v>
       </c>
       <c r="G54" t="n">
-        <v>0.293758153915405</v>
+        <v>0.293758183717728</v>
       </c>
       <c r="H54" t="n">
         <v>251105</v>
@@ -1964,7 +1964,7 @@
         <v>0.434500008821487</v>
       </c>
       <c r="G55" t="n">
-        <v>0.292278319597244</v>
+        <v>0.292278349399567</v>
       </c>
       <c r="H55" t="n">
         <v>561310</v>
@@ -1993,7 +1993,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G56" t="n">
-        <v>0.300014078617096</v>
+        <v>0.300014108419418</v>
       </c>
       <c r="H56" t="n">
         <v>320433</v>
@@ -2022,7 +2022,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G57" t="n">
-        <v>0.306404560804367</v>
+        <v>0.306404501199722</v>
       </c>
       <c r="H57" t="n">
         <v>741251</v>
@@ -2080,7 +2080,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G59" t="n">
-        <v>0.302704721689224</v>
+        <v>0.302704840898514</v>
       </c>
       <c r="H59" t="n">
         <v>93088</v>
@@ -2109,7 +2109,7 @@
         <v>0.43520000576973</v>
       </c>
       <c r="G60" t="n">
-        <v>0.292749166488647</v>
+        <v>0.292749136686325</v>
       </c>
       <c r="H60" t="n">
         <v>141424</v>
@@ -2167,7 +2167,7 @@
         <v>0.442699998617172</v>
       </c>
       <c r="G62" t="n">
-        <v>0.297794282436371</v>
+        <v>0.297794252634048</v>
       </c>
       <c r="H62" t="n">
         <v>100321</v>
@@ -2196,7 +2196,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G63" t="n">
-        <v>0.288578569889069</v>
+        <v>0.288578599691391</v>
       </c>
       <c r="H63" t="n">
         <v>79812</v>
@@ -2225,7 +2225,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G64" t="n">
-        <v>0.289251267910004</v>
+        <v>0.289251297712326</v>
       </c>
       <c r="H64" t="n">
         <v>25300</v>
@@ -2254,7 +2254,7 @@
         <v>0.40939998626709</v>
       </c>
       <c r="G65" t="n">
-        <v>0.275394111871719</v>
+        <v>0.275394052267075</v>
       </c>
       <c r="H65" t="n">
         <v>253125</v>
@@ -2312,7 +2312,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G67" t="n">
-        <v>0.275797665119171</v>
+        <v>0.275797724723816</v>
       </c>
       <c r="H67" t="n">
         <v>118188</v>
@@ -2341,7 +2341,7 @@
         <v>0.398799985647202</v>
       </c>
       <c r="G68" t="n">
-        <v>0.268263727426529</v>
+        <v>0.268263757228851</v>
       </c>
       <c r="H68" t="n">
         <v>90996</v>
@@ -2399,7 +2399,7 @@
         <v>0.414900004863739</v>
       </c>
       <c r="G70" t="n">
-        <v>0.279093831777573</v>
+        <v>0.27909380197525</v>
       </c>
       <c r="H70" t="n">
         <v>361046</v>
@@ -2457,7 +2457,7 @@
         <v>0.428400009870529</v>
       </c>
       <c r="G72" t="n">
-        <v>0.288174986839294</v>
+        <v>0.288174957036972</v>
       </c>
       <c r="H72" t="n">
         <v>164164</v>
@@ -2515,7 +2515,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G74" t="n">
-        <v>0.296650767326355</v>
+        <v>0.296650677919388</v>
       </c>
       <c r="H74" t="n">
         <v>60654</v>
@@ -2602,7 +2602,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G77" t="n">
-        <v>0.302704721689224</v>
+        <v>0.302704840898514</v>
       </c>
       <c r="H77" t="n">
         <v>363678</v>
@@ -2631,7 +2631,7 @@
         <v>0.447100013494492</v>
       </c>
       <c r="G78" t="n">
-        <v>0.30075404047966</v>
+        <v>0.300754100084305</v>
       </c>
       <c r="H78" t="n">
         <v>122237</v>
@@ -2660,7 +2660,7 @@
         <v>0.450100004673004</v>
       </c>
       <c r="G79" t="n">
-        <v>0.302772045135498</v>
+        <v>0.30277207493782</v>
       </c>
       <c r="H79" t="n">
         <v>194381</v>
@@ -2689,7 +2689,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G80" t="n">
-        <v>0.302704721689224</v>
+        <v>0.302704840898514</v>
       </c>
       <c r="H80" t="n">
         <v>7060</v>
@@ -2718,7 +2718,7 @@
         <v>0.453000009059906</v>
       </c>
       <c r="G81" t="n">
-        <v>0.304722845554352</v>
+        <v>0.304722785949707</v>
       </c>
       <c r="H81" t="n">
         <v>60016</v>
@@ -2776,7 +2776,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G83" t="n">
-        <v>0.316158324480057</v>
+        <v>0.316158384084702</v>
       </c>
       <c r="H83" t="n">
         <v>319951</v>
@@ -2950,7 +2950,7 @@
         <v>0.452800005674362</v>
       </c>
       <c r="G89" t="n">
-        <v>0.304588377475739</v>
+        <v>0.304588317871094</v>
       </c>
       <c r="H89" t="n">
         <v>50024</v>
@@ -3037,7 +3037,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G92" t="n">
-        <v>0.304050177335739</v>
+        <v>0.304050147533417</v>
       </c>
       <c r="H92" t="n">
         <v>41043</v>
@@ -3066,7 +3066,7 @@
         <v>0.456299990415573</v>
       </c>
       <c r="G93" t="n">
-        <v>0.306942671537399</v>
+        <v>0.306942641735077</v>
       </c>
       <c r="H93" t="n">
         <v>105211</v>
@@ -3095,7 +3095,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G94" t="n">
-        <v>0.302704721689224</v>
+        <v>0.302704840898514</v>
       </c>
       <c r="H94" t="n">
         <v>19755</v>
@@ -3124,7 +3124,7 @@
         <v>0.461800009012222</v>
       </c>
       <c r="G95" t="n">
-        <v>0.310642391443253</v>
+        <v>0.31064236164093</v>
       </c>
       <c r="H95" t="n">
         <v>29342</v>
@@ -3153,7 +3153,7 @@
         <v>0.460200011730194</v>
       </c>
       <c r="G96" t="n">
-        <v>0.309566140174866</v>
+        <v>0.309566110372543</v>
       </c>
       <c r="H96" t="n">
         <v>114075</v>
@@ -3211,7 +3211,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G98" t="n">
-        <v>0.304050177335739</v>
+        <v>0.304050147533417</v>
       </c>
       <c r="H98" t="n">
         <v>44647</v>
@@ -3240,7 +3240,7 @@
         <v>0.456400007009506</v>
       </c>
       <c r="G99" t="n">
-        <v>0.307009935379028</v>
+        <v>0.307009994983673</v>
       </c>
       <c r="H99" t="n">
         <v>19758</v>
@@ -3269,7 +3269,7 @@
         <v>0.46450001001358</v>
       </c>
       <c r="G100" t="n">
-        <v>0.312458634376526</v>
+        <v>0.312458604574203</v>
       </c>
       <c r="H100" t="n">
         <v>151288</v>
@@ -3298,7 +3298,7 @@
         <v>0.471599996089935</v>
       </c>
       <c r="G101" t="n">
-        <v>0.317234665155411</v>
+        <v>0.317234635353088</v>
       </c>
       <c r="H101" t="n">
         <v>373681</v>
@@ -3327,7 +3327,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>0.329611927270889</v>
+        <v>0.329611897468567</v>
       </c>
       <c r="H102" t="n">
         <v>844265</v>
@@ -3356,7 +3356,7 @@
         <v>0.486200004816055</v>
       </c>
       <c r="G103" t="n">
-        <v>0.327055722475052</v>
+        <v>0.327055692672729</v>
       </c>
       <c r="H103" t="n">
         <v>249061</v>
@@ -3414,7 +3414,7 @@
         <v>0.500500023365021</v>
       </c>
       <c r="G105" t="n">
-        <v>0.336675047874451</v>
+        <v>0.336675018072128</v>
       </c>
       <c r="H105" t="n">
         <v>831496</v>
@@ -3443,7 +3443,7 @@
         <v>0.504499971866608</v>
       </c>
       <c r="G106" t="n">
-        <v>0.339365720748901</v>
+        <v>0.339365661144257</v>
       </c>
       <c r="H106" t="n">
         <v>268568</v>
@@ -3472,7 +3472,7 @@
         <v>0.499900013208389</v>
       </c>
       <c r="G107" t="n">
-        <v>0.336271435022354</v>
+        <v>0.336271405220032</v>
       </c>
       <c r="H107" t="n">
         <v>309535</v>
@@ -3501,7 +3501,7 @@
         <v>0.497999995946884</v>
       </c>
       <c r="G108" t="n">
-        <v>0.334993332624435</v>
+        <v>0.334993302822113</v>
       </c>
       <c r="H108" t="n">
         <v>12135</v>
@@ -3530,7 +3530,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G109" t="n">
-        <v>0.328266590833664</v>
+        <v>0.328266531229019</v>
       </c>
       <c r="H109" t="n">
         <v>68219</v>
@@ -3559,7 +3559,7 @@
         <v>0.487800002098083</v>
       </c>
       <c r="G110" t="n">
-        <v>0.328132003545761</v>
+        <v>0.328132033348083</v>
       </c>
       <c r="H110" t="n">
         <v>50127</v>
@@ -3588,7 +3588,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G111" t="n">
-        <v>0.326248556375504</v>
+        <v>0.326248496770859</v>
       </c>
       <c r="H111" t="n">
         <v>136014</v>
@@ -3646,7 +3646,7 @@
         <v>0.479099988937378</v>
       </c>
       <c r="G113" t="n">
-        <v>0.322279721498489</v>
+        <v>0.322279751300812</v>
       </c>
       <c r="H113" t="n">
         <v>257668</v>
@@ -3675,7 +3675,7 @@
         <v>0.469999998807907</v>
       </c>
       <c r="G114" t="n">
-        <v>0.316158324480057</v>
+        <v>0.316158384084702</v>
       </c>
       <c r="H114" t="n">
         <v>169086</v>
@@ -3791,7 +3791,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>0.295358419418335</v>
+        <v>0.295358449220657</v>
       </c>
       <c r="H118" t="n">
         <v>145190</v>
@@ -3820,7 +3820,7 @@
         <v>0.430200010538101</v>
       </c>
       <c r="G119" t="n">
-        <v>0.298270434141159</v>
+        <v>0.298270463943481</v>
       </c>
       <c r="H119" t="n">
         <v>328370</v>
@@ -3907,7 +3907,7 @@
         <v>0.439399987459183</v>
       </c>
       <c r="G122" t="n">
-        <v>0.30464905500412</v>
+        <v>0.304649084806442</v>
       </c>
       <c r="H122" t="n">
         <v>65991</v>
@@ -3936,7 +3936,7 @@
         <v>0.447100013494492</v>
       </c>
       <c r="G123" t="n">
-        <v>0.309987723827362</v>
+        <v>0.309987753629684</v>
       </c>
       <c r="H123" t="n">
         <v>89125</v>
@@ -3965,7 +3965,7 @@
         <v>0.423700004816055</v>
       </c>
       <c r="G124" t="n">
-        <v>0.293763786554337</v>
+        <v>0.293763816356659</v>
       </c>
       <c r="H124" t="n">
         <v>202954</v>
@@ -3994,7 +3994,7 @@
         <v>0.412499994039536</v>
       </c>
       <c r="G125" t="n">
-        <v>0.285998523235321</v>
+        <v>0.285998493432999</v>
       </c>
       <c r="H125" t="n">
         <v>82663</v>
@@ -4023,7 +4023,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G126" t="n">
-        <v>0.286345154047012</v>
+        <v>0.286345183849335</v>
       </c>
       <c r="H126" t="n">
         <v>82338</v>
@@ -4052,7 +4052,7 @@
         <v>0.431800007820129</v>
       </c>
       <c r="G127" t="n">
-        <v>0.299379795789719</v>
+        <v>0.299379736185074</v>
       </c>
       <c r="H127" t="n">
         <v>67305</v>
@@ -4081,7 +4081,7 @@
         <v>0.442499995231628</v>
       </c>
       <c r="G128" t="n">
-        <v>0.306798368692398</v>
+        <v>0.306798428297043</v>
       </c>
       <c r="H128" t="n">
         <v>79269</v>
@@ -4168,7 +4168,7 @@
         <v>0.439000010490417</v>
       </c>
       <c r="G131" t="n">
-        <v>0.304371744394302</v>
+        <v>0.304371774196625</v>
       </c>
       <c r="H131" t="n">
         <v>46421</v>
@@ -4197,7 +4197,7 @@
         <v>0.426899999380112</v>
       </c>
       <c r="G132" t="n">
-        <v>0.295982480049133</v>
+        <v>0.295982450246811</v>
       </c>
       <c r="H132" t="n">
         <v>70121</v>
@@ -4226,7 +4226,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G133" t="n">
-        <v>0.298131793737411</v>
+        <v>0.298131823539734</v>
       </c>
       <c r="H133" t="n">
         <v>35208</v>
@@ -4255,7 +4255,7 @@
         <v>0.428299993276596</v>
       </c>
       <c r="G134" t="n">
-        <v>0.296953141689301</v>
+        <v>0.296953111886978</v>
       </c>
       <c r="H134" t="n">
         <v>48610</v>
@@ -4313,7 +4313,7 @@
         <v>0.44420000910759</v>
       </c>
       <c r="G136" t="n">
-        <v>0.307977080345154</v>
+        <v>0.307977050542831</v>
       </c>
       <c r="H136" t="n">
         <v>140340</v>
@@ -4342,7 +4342,7 @@
         <v>0.439399987459183</v>
       </c>
       <c r="G137" t="n">
-        <v>0.30464905500412</v>
+        <v>0.304649084806442</v>
       </c>
       <c r="H137" t="n">
         <v>49759</v>
@@ -4400,7 +4400,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G139" t="n">
-        <v>0.305758446455002</v>
+        <v>0.305758416652679</v>
       </c>
       <c r="H139" t="n">
         <v>31830</v>
@@ -4574,7 +4574,7 @@
         <v>0.416200011968613</v>
       </c>
       <c r="G145" t="n">
-        <v>0.288563817739487</v>
+        <v>0.288563877344131</v>
       </c>
       <c r="H145" t="n">
         <v>116786</v>
@@ -4603,7 +4603,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G146" t="n">
-        <v>0.287731826305389</v>
+        <v>0.287731856107712</v>
       </c>
       <c r="H146" t="n">
         <v>65130</v>
@@ -4632,7 +4632,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G147" t="n">
-        <v>0.285651862621307</v>
+        <v>0.285651832818985</v>
       </c>
       <c r="H147" t="n">
         <v>120486</v>
@@ -4661,7 +4661,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G148" t="n">
-        <v>0.285651862621307</v>
+        <v>0.285651832818985</v>
       </c>
       <c r="H148" t="n">
         <v>61174</v>
@@ -4719,7 +4719,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G150" t="n">
-        <v>0.278718590736389</v>
+        <v>0.278718560934067</v>
       </c>
       <c r="H150" t="n">
         <v>160185</v>
@@ -4748,7 +4748,7 @@
         <v>0.405900001525879</v>
       </c>
       <c r="G151" t="n">
-        <v>0.281422555446625</v>
+        <v>0.281422525644302</v>
       </c>
       <c r="H151" t="n">
         <v>41710</v>
@@ -4777,7 +4777,7 @@
         <v>0.419900000095367</v>
       </c>
       <c r="G152" t="n">
-        <v>0.291129171848297</v>
+        <v>0.291129142045975</v>
       </c>
       <c r="H152" t="n">
         <v>46026</v>
@@ -4806,7 +4806,7 @@
         <v>0.415399998426437</v>
       </c>
       <c r="G153" t="n">
-        <v>0.288009166717529</v>
+        <v>0.288009196519852</v>
       </c>
       <c r="H153" t="n">
         <v>25255</v>
@@ -4835,7 +4835,7 @@
         <v>0.417499989271164</v>
       </c>
       <c r="G154" t="n">
-        <v>0.289465099573135</v>
+        <v>0.28946515917778</v>
       </c>
       <c r="H154" t="n">
         <v>40486</v>
@@ -4893,7 +4893,7 @@
         <v>0.414600014686584</v>
       </c>
       <c r="G156" t="n">
-        <v>0.28745448589325</v>
+        <v>0.287454515695572</v>
       </c>
       <c r="H156" t="n">
         <v>16647</v>
@@ -4951,7 +4951,7 @@
         <v>0.413300007581711</v>
       </c>
       <c r="G158" t="n">
-        <v>0.286553174257278</v>
+        <v>0.286553144454956</v>
       </c>
       <c r="H158" t="n">
         <v>31506</v>
@@ -4980,7 +4980,7 @@
         <v>0.416399985551834</v>
       </c>
       <c r="G159" t="n">
-        <v>0.288702487945557</v>
+        <v>0.288702458143234</v>
       </c>
       <c r="H159" t="n">
         <v>32950</v>
@@ -5009,7 +5009,7 @@
         <v>0.41609999537468</v>
       </c>
       <c r="G160" t="n">
-        <v>0.288494557142258</v>
+        <v>0.288494497537613</v>
       </c>
       <c r="H160" t="n">
         <v>56566</v>
@@ -5038,7 +5038,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G161" t="n">
-        <v>0.289118498563766</v>
+        <v>0.289118528366089</v>
       </c>
       <c r="H161" t="n">
         <v>35295</v>
@@ -5067,7 +5067,7 @@
         <v>0.41389998793602</v>
       </c>
       <c r="G162" t="n">
-        <v>0.286969184875488</v>
+        <v>0.286969155073166</v>
       </c>
       <c r="H162" t="n">
         <v>21664</v>
@@ -5096,7 +5096,7 @@
         <v>0.416799992322922</v>
       </c>
       <c r="G163" t="n">
-        <v>0.288979798555374</v>
+        <v>0.288979828357697</v>
       </c>
       <c r="H163" t="n">
         <v>55214</v>
@@ -5125,7 +5125,7 @@
         <v>0.409799993038177</v>
       </c>
       <c r="G164" t="n">
-        <v>0.28412652015686</v>
+        <v>0.284126490354538</v>
       </c>
       <c r="H164" t="n">
         <v>36074</v>
@@ -5154,7 +5154,7 @@
         <v>0.407700002193451</v>
       </c>
       <c r="G165" t="n">
-        <v>0.282670527696609</v>
+        <v>0.282670557498932</v>
       </c>
       <c r="H165" t="n">
         <v>26093</v>
@@ -5212,7 +5212,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G167" t="n">
-        <v>0.284265160560608</v>
+        <v>0.28426519036293</v>
       </c>
       <c r="H167" t="n">
         <v>42008</v>
@@ -5241,7 +5241,7 @@
         <v>0.402300000190735</v>
       </c>
       <c r="G168" t="n">
-        <v>0.278926521539688</v>
+        <v>0.27892655134201</v>
       </c>
       <c r="H168" t="n">
         <v>132579</v>
@@ -5270,7 +5270,7 @@
         <v>0.403200000524521</v>
       </c>
       <c r="G169" t="n">
-        <v>0.279550552368164</v>
+        <v>0.279550522565842</v>
       </c>
       <c r="H169" t="n">
         <v>13600</v>
@@ -5299,7 +5299,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G170" t="n">
-        <v>0.27733188867569</v>
+        <v>0.277331858873367</v>
       </c>
       <c r="H170" t="n">
         <v>31357</v>
@@ -5328,7 +5328,7 @@
         <v>0.396499991416931</v>
       </c>
       <c r="G171" t="n">
-        <v>0.274905234575272</v>
+        <v>0.274905204772949</v>
       </c>
       <c r="H171" t="n">
         <v>52650</v>
@@ -5473,7 +5473,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G176" t="n">
-        <v>0.284265160560608</v>
+        <v>0.28426519036293</v>
       </c>
       <c r="H176" t="n">
         <v>66150</v>
@@ -5502,7 +5502,7 @@
         <v>0.406199991703033</v>
       </c>
       <c r="G177" t="n">
-        <v>0.281630516052246</v>
+        <v>0.281630545854568</v>
       </c>
       <c r="H177" t="n">
         <v>34503</v>
@@ -5531,7 +5531,7 @@
         <v>0.398999989032745</v>
       </c>
       <c r="G178" t="n">
-        <v>0.27663853764534</v>
+        <v>0.276638567447662</v>
       </c>
       <c r="H178" t="n">
         <v>130281</v>
@@ -5560,7 +5560,7 @@
         <v>0.397100001573563</v>
       </c>
       <c r="G179" t="n">
-        <v>0.275321215391159</v>
+        <v>0.275321245193481</v>
       </c>
       <c r="H179" t="n">
         <v>67427</v>
@@ -5589,7 +5589,7 @@
         <v>0.390300005674362</v>
       </c>
       <c r="G180" t="n">
-        <v>0.270606607198715</v>
+        <v>0.270606577396393</v>
       </c>
       <c r="H180" t="n">
         <v>40182</v>
@@ -5734,7 +5734,7 @@
         <v>0.372000008821487</v>
       </c>
       <c r="G185" t="n">
-        <v>0.257918655872345</v>
+        <v>0.257918626070023</v>
       </c>
       <c r="H185" t="n">
         <v>133862</v>
@@ -5763,7 +5763,7 @@
         <v>0.376899987459183</v>
       </c>
       <c r="G186" t="n">
-        <v>0.261316001415253</v>
+        <v>0.26131597161293</v>
       </c>
       <c r="H186" t="n">
         <v>145993</v>
@@ -5792,7 +5792,7 @@
         <v>0.385500013828278</v>
       </c>
       <c r="G187" t="n">
-        <v>0.267278641462326</v>
+        <v>0.267278611660004</v>
       </c>
       <c r="H187" t="n">
         <v>99576</v>
@@ -5850,7 +5850,7 @@
         <v>0.391400009393692</v>
       </c>
       <c r="G189" t="n">
-        <v>0.271369218826294</v>
+        <v>0.271369278430939</v>
       </c>
       <c r="H189" t="n">
         <v>15005</v>
@@ -5879,7 +5879,7 @@
         <v>0.389099985361099</v>
       </c>
       <c r="G190" t="n">
-        <v>0.269774585962296</v>
+        <v>0.269774615764618</v>
       </c>
       <c r="H190" t="n">
         <v>84813</v>
@@ -5908,7 +5908,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G191" t="n">
-        <v>0.274558573961258</v>
+        <v>0.274558544158936</v>
       </c>
       <c r="H191" t="n">
         <v>210447</v>
@@ -5937,7 +5937,7 @@
         <v>0.403899997472763</v>
       </c>
       <c r="G192" t="n">
-        <v>0.280035883188248</v>
+        <v>0.280035853385925</v>
       </c>
       <c r="H192" t="n">
         <v>232233</v>
@@ -5966,7 +5966,7 @@
         <v>0.415699988603592</v>
       </c>
       <c r="G193" t="n">
-        <v>0.288217157125473</v>
+        <v>0.288217127323151</v>
       </c>
       <c r="H193" t="n">
         <v>460681</v>
@@ -5995,7 +5995,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G194" t="n">
-        <v>0.282878518104553</v>
+        <v>0.282878547906876</v>
       </c>
       <c r="H194" t="n">
         <v>44712</v>
@@ -6024,7 +6024,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>0.282878518104553</v>
+        <v>0.282878547906876</v>
       </c>
       <c r="H195" t="n">
         <v>40343</v>
@@ -6053,7 +6053,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>0.282878518104553</v>
+        <v>0.282878547906876</v>
       </c>
       <c r="H196" t="n">
         <v>10030</v>
@@ -6111,7 +6111,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G198" t="n">
-        <v>0.283571839332581</v>
+        <v>0.283571869134903</v>
       </c>
       <c r="H198" t="n">
         <v>91525</v>
@@ -6198,7 +6198,7 @@
         <v>0.409700006246567</v>
       </c>
       <c r="G201" t="n">
-        <v>0.284057170152664</v>
+        <v>0.284057199954987</v>
       </c>
       <c r="H201" t="n">
         <v>29815</v>
@@ -6285,7 +6285,7 @@
         <v>0.408300012350082</v>
       </c>
       <c r="G204" t="n">
-        <v>0.283086538314819</v>
+        <v>0.283086508512497</v>
       </c>
       <c r="H204" t="n">
         <v>42837</v>
@@ -6314,7 +6314,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G205" t="n">
-        <v>0.285651862621307</v>
+        <v>0.285651832818985</v>
       </c>
       <c r="H205" t="n">
         <v>62013</v>
@@ -6343,7 +6343,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G206" t="n">
-        <v>0.284265160560608</v>
+        <v>0.28426519036293</v>
       </c>
       <c r="H206" t="n">
         <v>33348</v>
@@ -6372,7 +6372,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G207" t="n">
-        <v>0.285651862621307</v>
+        <v>0.285651832818985</v>
       </c>
       <c r="H207" t="n">
         <v>100149</v>
@@ -6430,7 +6430,7 @@
         <v>0.422600001096725</v>
       </c>
       <c r="G209" t="n">
-        <v>0.293001145124435</v>
+        <v>0.293001174926758</v>
       </c>
       <c r="H209" t="n">
         <v>331850</v>
@@ -6459,7 +6459,7 @@
         <v>0.417199999094009</v>
       </c>
       <c r="G210" t="n">
-        <v>0.289257168769836</v>
+        <v>0.289257138967514</v>
       </c>
       <c r="H210" t="n">
         <v>162764</v>
@@ -6488,7 +6488,7 @@
         <v>0.422100007534027</v>
       </c>
       <c r="G211" t="n">
-        <v>0.292654484510422</v>
+        <v>0.292654454708099</v>
       </c>
       <c r="H211" t="n">
         <v>158762</v>
@@ -6517,7 +6517,7 @@
         <v>0.423500001430511</v>
       </c>
       <c r="G212" t="n">
-        <v>0.293625175952911</v>
+        <v>0.293625116348267</v>
       </c>
       <c r="H212" t="n">
         <v>85774</v>
@@ -6575,7 +6575,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G214" t="n">
-        <v>0.285651862621307</v>
+        <v>0.285651832818985</v>
       </c>
       <c r="H214" t="n">
         <v>18054</v>
@@ -6604,7 +6604,7 @@
         <v>0.405600011348724</v>
       </c>
       <c r="G215" t="n">
-        <v>0.281214535236359</v>
+        <v>0.281214565038681</v>
       </c>
       <c r="H215" t="n">
         <v>32794</v>
@@ -6633,7 +6633,7 @@
         <v>0.405600011348724</v>
       </c>
       <c r="G216" t="n">
-        <v>0.281214535236359</v>
+        <v>0.281214565038681</v>
       </c>
       <c r="H216" t="n">
         <v>67993</v>
@@ -6662,7 +6662,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G217" t="n">
-        <v>0.283571839332581</v>
+        <v>0.283571869134903</v>
       </c>
       <c r="H217" t="n">
         <v>8110</v>
@@ -6691,7 +6691,7 @@
         <v>0.390399992465973</v>
       </c>
       <c r="G218" t="n">
-        <v>0.270675867795944</v>
+        <v>0.270675927400589</v>
       </c>
       <c r="H218" t="n">
         <v>113438</v>
@@ -6720,7 +6720,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G219" t="n">
-        <v>0.275251895189285</v>
+        <v>0.275251924991608</v>
       </c>
       <c r="H219" t="n">
         <v>156788</v>
@@ -6778,7 +6778,7 @@
         <v>0.393900007009506</v>
       </c>
       <c r="G221" t="n">
-        <v>0.273102581501007</v>
+        <v>0.273102611303329</v>
       </c>
       <c r="H221" t="n">
         <v>90093</v>
@@ -6836,7 +6836,7 @@
         <v>0.398299992084503</v>
       </c>
       <c r="G223" t="n">
-        <v>0.276153236627579</v>
+        <v>0.276153206825256</v>
       </c>
       <c r="H223" t="n">
         <v>172609</v>
@@ -6865,7 +6865,7 @@
         <v>0.405099987983704</v>
       </c>
       <c r="G224" t="n">
-        <v>0.280867874622345</v>
+        <v>0.280867844820023</v>
       </c>
       <c r="H224" t="n">
         <v>62740</v>
@@ -6923,7 +6923,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G226" t="n">
-        <v>0.27733188867569</v>
+        <v>0.277331858873367</v>
       </c>
       <c r="H226" t="n">
         <v>70073</v>
@@ -6981,7 +6981,7 @@
         <v>0.388099998235703</v>
       </c>
       <c r="G228" t="n">
-        <v>0.269081234931946</v>
+        <v>0.269081264734268</v>
       </c>
       <c r="H228" t="n">
         <v>166780</v>
@@ -7010,7 +7010,7 @@
         <v>0.387100011110306</v>
       </c>
       <c r="G229" t="n">
-        <v>0.268387913703918</v>
+        <v>0.268387973308563</v>
       </c>
       <c r="H229" t="n">
         <v>15865</v>
@@ -7039,7 +7039,7 @@
         <v>0.384799987077713</v>
       </c>
       <c r="G230" t="n">
-        <v>0.266793251037598</v>
+        <v>0.26679328083992</v>
       </c>
       <c r="H230" t="n">
         <v>88305</v>
@@ -7068,7 +7068,7 @@
         <v>0.384799987077713</v>
       </c>
       <c r="G231" t="n">
-        <v>0.266793251037598</v>
+        <v>0.26679328083992</v>
       </c>
       <c r="H231" t="n">
         <v>99587</v>
@@ -7213,7 +7213,7 @@
         <v>0.409999996423721</v>
       </c>
       <c r="G236" t="n">
-        <v>0.284265160560608</v>
+        <v>0.28426519036293</v>
       </c>
       <c r="H236" t="n">
         <v>100550</v>
@@ -7271,7 +7271,7 @@
         <v>0.398000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>0.275945216417313</v>
+        <v>0.275945246219635</v>
       </c>
       <c r="H238" t="n">
         <v>90286</v>
@@ -7300,7 +7300,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G239" t="n">
-        <v>0.274558573961258</v>
+        <v>0.274558544158936</v>
       </c>
       <c r="H239" t="n">
         <v>56212</v>
@@ -7329,7 +7329,7 @@
         <v>0.396499991416931</v>
       </c>
       <c r="G240" t="n">
-        <v>0.274905234575272</v>
+        <v>0.274905204772949</v>
       </c>
       <c r="H240" t="n">
         <v>97927</v>
@@ -7387,7 +7387,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G242" t="n">
-        <v>0.27733188867569</v>
+        <v>0.277331858873367</v>
       </c>
       <c r="H242" t="n">
         <v>51710</v>
@@ -7445,7 +7445,7 @@
         <v>0.402900010347366</v>
       </c>
       <c r="G244" t="n">
-        <v>0.279342532157898</v>
+        <v>0.27934256196022</v>
       </c>
       <c r="H244" t="n">
         <v>110396</v>
@@ -7474,7 +7474,7 @@
         <v>0.405900001525879</v>
       </c>
       <c r="G245" t="n">
-        <v>0.281422555446625</v>
+        <v>0.281422525644302</v>
       </c>
       <c r="H245" t="n">
         <v>56657</v>
@@ -7503,7 +7503,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G246" t="n">
-        <v>0.281491845846176</v>
+        <v>0.281491905450821</v>
       </c>
       <c r="H246" t="n">
         <v>86458</v>
@@ -7532,7 +7532,7 @@
         <v>0.412900000810623</v>
       </c>
       <c r="G247" t="n">
-        <v>0.286275833845139</v>
+        <v>0.286275863647461</v>
       </c>
       <c r="H247" t="n">
         <v>162995</v>
@@ -7648,7 +7648,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G251" t="n">
-        <v>0.29397177696228</v>
+        <v>0.293971806764603</v>
       </c>
       <c r="H251" t="n">
         <v>688263</v>
@@ -7735,7 +7735,7 @@
         <v>0.456999987363815</v>
       </c>
       <c r="G254" t="n">
-        <v>0.316851675510406</v>
+        <v>0.316851645708084</v>
       </c>
       <c r="H254" t="n">
         <v>279270</v>
@@ -7764,7 +7764,7 @@
         <v>0.475800007581711</v>
       </c>
       <c r="G255" t="n">
-        <v>0.329886257648468</v>
+        <v>0.32988628745079</v>
       </c>
       <c r="H255" t="n">
         <v>1250952</v>
@@ -7793,7 +7793,7 @@
         <v>0.482400000095367</v>
       </c>
       <c r="G256" t="n">
-        <v>0.334462255239487</v>
+        <v>0.334462285041809</v>
       </c>
       <c r="H256" t="n">
         <v>929465</v>
@@ -7880,7 +7880,7 @@
         <v>0.482199996709824</v>
       </c>
       <c r="G259" t="n">
-        <v>0.334323555231094</v>
+        <v>0.334323614835739</v>
       </c>
       <c r="H259" t="n">
         <v>352742</v>
@@ -7909,7 +7909,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G260" t="n">
-        <v>0.336958229541779</v>
+        <v>0.336958259344101</v>
       </c>
       <c r="H260" t="n">
         <v>217712</v>
@@ -8054,7 +8054,7 @@
         <v>0.473300009965897</v>
       </c>
       <c r="G265" t="n">
-        <v>0.3281529545784</v>
+        <v>0.328152984380722</v>
       </c>
       <c r="H265" t="n">
         <v>815286</v>
@@ -8083,7 +8083,7 @@
         <v>0.477400004863739</v>
       </c>
       <c r="G266" t="n">
-        <v>0.330995589494705</v>
+        <v>0.33099564909935</v>
       </c>
       <c r="H266" t="n">
         <v>477547</v>
@@ -8112,7 +8112,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G267" t="n">
-        <v>0.331411629915237</v>
+        <v>0.331411600112915</v>
       </c>
       <c r="H267" t="n">
         <v>106481</v>
@@ -8141,7 +8141,7 @@
         <v>0.477800011634827</v>
       </c>
       <c r="G268" t="n">
-        <v>0.331272959709167</v>
+        <v>0.331272929906845</v>
       </c>
       <c r="H268" t="n">
         <v>85348</v>
@@ -8199,7 +8199,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G270" t="n">
-        <v>0.334878236055374</v>
+        <v>0.334878265857697</v>
       </c>
       <c r="H270" t="n">
         <v>122203</v>
@@ -8257,7 +8257,7 @@
         <v>0.53549998998642</v>
       </c>
       <c r="G272" t="n">
-        <v>0.371278047561646</v>
+        <v>0.37127810716629</v>
       </c>
       <c r="H272" t="n">
         <v>1803953</v>
@@ -8286,7 +8286,7 @@
         <v>0.548500001430511</v>
       </c>
       <c r="G273" t="n">
-        <v>0.380291312932968</v>
+        <v>0.380291372537613</v>
       </c>
       <c r="H273" t="n">
         <v>1437275</v>
@@ -8344,7 +8344,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G275" t="n">
-        <v>0.365384787321091</v>
+        <v>0.365384817123413</v>
       </c>
       <c r="H275" t="n">
         <v>532997</v>
@@ -8373,7 +8373,7 @@
         <v>0.517000019550323</v>
       </c>
       <c r="G276" t="n">
-        <v>0.35845148563385</v>
+        <v>0.358451455831528</v>
       </c>
       <c r="H276" t="n">
         <v>492865</v>
@@ -8431,7 +8431,7 @@
         <v>0.520500004291534</v>
       </c>
       <c r="G278" t="n">
-        <v>0.360878139734268</v>
+        <v>0.360878080129623</v>
       </c>
       <c r="H278" t="n">
         <v>618202</v>
@@ -8460,7 +8460,7 @@
         <v>0.514500021934509</v>
       </c>
       <c r="G279" t="n">
-        <v>0.356718152761459</v>
+        <v>0.356718182563782</v>
       </c>
       <c r="H279" t="n">
         <v>254300</v>
@@ -8489,7 +8489,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G280" t="n">
-        <v>0.353598088026047</v>
+        <v>0.353598177433014</v>
       </c>
       <c r="H280" t="n">
         <v>86695</v>
@@ -8518,7 +8518,7 @@
         <v>0.520500004291534</v>
       </c>
       <c r="G281" t="n">
-        <v>0.360878139734268</v>
+        <v>0.360878080129623</v>
       </c>
       <c r="H281" t="n">
         <v>644514</v>
@@ -8547,7 +8547,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G282" t="n">
-        <v>0.366771370172501</v>
+        <v>0.366771429777145</v>
       </c>
       <c r="H282" t="n">
         <v>416543</v>
@@ -8605,7 +8605,7 @@
         <v>0.50900000333786</v>
       </c>
       <c r="G284" t="n">
-        <v>0.352904826402664</v>
+        <v>0.352904796600342</v>
       </c>
       <c r="H284" t="n">
         <v>280229</v>
@@ -8634,7 +8634,7 @@
         <v>0.493999987840652</v>
       </c>
       <c r="G285" t="n">
-        <v>0.342504858970642</v>
+        <v>0.342504888772964</v>
       </c>
       <c r="H285" t="n">
         <v>462534</v>
@@ -8663,7 +8663,7 @@
         <v>0.493800014257431</v>
       </c>
       <c r="G286" t="n">
-        <v>0.342366218566895</v>
+        <v>0.342366248369217</v>
       </c>
       <c r="H286" t="n">
         <v>243260</v>
@@ -8692,7 +8692,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>0.353598088026047</v>
+        <v>0.353598177433014</v>
       </c>
       <c r="H287" t="n">
         <v>224529</v>
@@ -8750,7 +8750,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G289" t="n">
-        <v>0.394504606723785</v>
+        <v>0.394504636526108</v>
       </c>
       <c r="H289" t="n">
         <v>6785613</v>
@@ -8779,7 +8779,7 @@
         <v>0.527499973773956</v>
       </c>
       <c r="G290" t="n">
-        <v>0.365731418132782</v>
+        <v>0.36573138833046</v>
       </c>
       <c r="H290" t="n">
         <v>4935558</v>
@@ -8837,7 +8837,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G292" t="n">
-        <v>0.377171397209167</v>
+        <v>0.377171337604523</v>
       </c>
       <c r="H292" t="n">
         <v>576696</v>
@@ -8866,7 +8866,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G293" t="n">
-        <v>0.368851453065872</v>
+        <v>0.36885142326355</v>
       </c>
       <c r="H293" t="n">
         <v>1362978</v>
@@ -8895,7 +8895,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G294" t="n">
-        <v>0.376478016376495</v>
+        <v>0.37647807598114</v>
       </c>
       <c r="H294" t="n">
         <v>347158</v>
@@ -8953,7 +8953,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G296" t="n">
-        <v>0.367464751005173</v>
+        <v>0.36746472120285</v>
       </c>
       <c r="H296" t="n">
         <v>197677</v>
@@ -9040,7 +9040,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G299" t="n">
-        <v>0.373704671859741</v>
+        <v>0.373704701662064</v>
       </c>
       <c r="H299" t="n">
         <v>2461350</v>
@@ -9069,7 +9069,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G300" t="n">
-        <v>0.377171397209167</v>
+        <v>0.377171337604523</v>
       </c>
       <c r="H300" t="n">
         <v>387300</v>
@@ -9098,7 +9098,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G301" t="n">
-        <v>0.377171397209167</v>
+        <v>0.377171337604523</v>
       </c>
       <c r="H301" t="n">
         <v>481471</v>
@@ -9127,7 +9127,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G302" t="n">
-        <v>0.377864748239517</v>
+        <v>0.377864718437195</v>
       </c>
       <c r="H302" t="n">
         <v>207709</v>
@@ -9156,7 +9156,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G303" t="n">
-        <v>0.376478016376495</v>
+        <v>0.37647807598114</v>
       </c>
       <c r="H303" t="n">
         <v>144362</v>
@@ -9185,7 +9185,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G304" t="n">
-        <v>0.377171397209167</v>
+        <v>0.377171337604523</v>
       </c>
       <c r="H304" t="n">
         <v>394789</v>
@@ -9214,7 +9214,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G305" t="n">
-        <v>0.377864748239517</v>
+        <v>0.377864718437195</v>
       </c>
       <c r="H305" t="n">
         <v>386269</v>
@@ -9243,7 +9243,7 @@
         <v>0.542500019073486</v>
       </c>
       <c r="G306" t="n">
-        <v>0.376131385564804</v>
+        <v>0.376131445169449</v>
       </c>
       <c r="H306" t="n">
         <v>229120</v>
@@ -9272,7 +9272,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G307" t="n">
-        <v>0.379944682121277</v>
+        <v>0.379944652318954</v>
       </c>
       <c r="H307" t="n">
         <v>559210</v>
@@ -9301,7 +9301,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G308" t="n">
-        <v>0.381331354379654</v>
+        <v>0.381331384181976</v>
       </c>
       <c r="H308" t="n">
         <v>384788</v>
@@ -9330,7 +9330,7 @@
         <v>0.545499980449677</v>
       </c>
       <c r="G309" t="n">
-        <v>0.378211289644241</v>
+        <v>0.378211319446564</v>
       </c>
       <c r="H309" t="n">
         <v>279693</v>
@@ -9359,7 +9359,7 @@
         <v>0.546999990940094</v>
       </c>
       <c r="G310" t="n">
-        <v>0.379251331090927</v>
+        <v>0.379251390695572</v>
       </c>
       <c r="H310" t="n">
         <v>142786</v>
@@ -9388,7 +9388,7 @@
         <v>0.545499980449677</v>
       </c>
       <c r="G311" t="n">
-        <v>0.378211289644241</v>
+        <v>0.378211319446564</v>
       </c>
       <c r="H311" t="n">
         <v>244820</v>
@@ -9417,7 +9417,7 @@
         <v>0.548500001430511</v>
       </c>
       <c r="G312" t="n">
-        <v>0.380291312932968</v>
+        <v>0.380291372537613</v>
       </c>
       <c r="H312" t="n">
         <v>308744</v>
@@ -9446,7 +9446,7 @@
         <v>0.548500001430511</v>
       </c>
       <c r="G313" t="n">
-        <v>0.380291312932968</v>
+        <v>0.380291372537613</v>
       </c>
       <c r="H313" t="n">
         <v>326913</v>
@@ -9475,7 +9475,7 @@
         <v>0.549499988555908</v>
       </c>
       <c r="G314" t="n">
-        <v>0.380984663963318</v>
+        <v>0.38098469376564</v>
       </c>
       <c r="H314" t="n">
         <v>322580</v>
@@ -9504,7 +9504,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>0.3785580098629</v>
+        <v>0.378558039665222</v>
       </c>
       <c r="H315" t="n">
         <v>174957</v>
@@ -9533,7 +9533,7 @@
         <v>0.549499988555908</v>
       </c>
       <c r="G316" t="n">
-        <v>0.380984663963318</v>
+        <v>0.38098469376564</v>
       </c>
       <c r="H316" t="n">
         <v>941673</v>
@@ -9562,7 +9562,7 @@
         <v>0.548500001430511</v>
       </c>
       <c r="G317" t="n">
-        <v>0.380291312932968</v>
+        <v>0.380291372537613</v>
       </c>
       <c r="H317" t="n">
         <v>921233</v>
@@ -9620,7 +9620,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G319" t="n">
-        <v>0.379944682121277</v>
+        <v>0.379944652318954</v>
       </c>
       <c r="H319" t="n">
         <v>602553</v>
@@ -9649,7 +9649,7 @@
         <v>0.548500001430511</v>
       </c>
       <c r="G320" t="n">
-        <v>0.380291312932968</v>
+        <v>0.380291372537613</v>
       </c>
       <c r="H320" t="n">
         <v>1947674</v>
@@ -9678,7 +9678,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G321" t="n">
-        <v>0.380638003349304</v>
+        <v>0.380637973546982</v>
       </c>
       <c r="H321" t="n">
         <v>460479</v>
@@ -9707,7 +9707,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G322" t="n">
-        <v>0.384104669094086</v>
+        <v>0.384104698896408</v>
       </c>
       <c r="H322" t="n">
         <v>1231033</v>
@@ -9736,7 +9736,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G323" t="n">
-        <v>0.379944682121277</v>
+        <v>0.379944652318954</v>
       </c>
       <c r="H323" t="n">
         <v>1376632</v>
@@ -9765,7 +9765,7 @@
         <v>0.545499980449677</v>
       </c>
       <c r="G324" t="n">
-        <v>0.378211289644241</v>
+        <v>0.378211319446564</v>
       </c>
       <c r="H324" t="n">
         <v>525567</v>
@@ -9794,7 +9794,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G325" t="n">
-        <v>0.381331354379654</v>
+        <v>0.381331384181976</v>
       </c>
       <c r="H325" t="n">
         <v>862314</v>
@@ -9823,7 +9823,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G326" t="n">
-        <v>0.381331354379654</v>
+        <v>0.381331384181976</v>
       </c>
       <c r="H326" t="n">
         <v>763705</v>
@@ -9852,7 +9852,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G327" t="n">
-        <v>0.376478016376495</v>
+        <v>0.37647807598114</v>
       </c>
       <c r="H327" t="n">
         <v>170626</v>
@@ -9881,7 +9881,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G328" t="n">
-        <v>0.377171397209167</v>
+        <v>0.377171337604523</v>
       </c>
       <c r="H328" t="n">
         <v>302130</v>
@@ -9939,7 +9939,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G330" t="n">
-        <v>0.375091373920441</v>
+        <v>0.375091433525085</v>
       </c>
       <c r="H330" t="n">
         <v>233050</v>
@@ -9968,7 +9968,7 @@
         <v>0.542500019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>0.376131385564804</v>
+        <v>0.376131445169449</v>
       </c>
       <c r="H331" t="n">
         <v>510105</v>
@@ -9997,7 +9997,7 @@
         <v>0.53549998998642</v>
       </c>
       <c r="G332" t="n">
-        <v>0.371278047561646</v>
+        <v>0.37127810716629</v>
       </c>
       <c r="H332" t="n">
         <v>598380</v>
@@ -10026,7 +10026,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G333" t="n">
-        <v>0.370238035917282</v>
+        <v>0.370238065719604</v>
       </c>
       <c r="H333" t="n">
         <v>209216</v>
@@ -10055,7 +10055,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G334" t="n">
-        <v>0.369544744491577</v>
+        <v>0.369544714689255</v>
       </c>
       <c r="H334" t="n">
         <v>219687</v>
@@ -10084,7 +10084,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G335" t="n">
-        <v>0.366078108549118</v>
+        <v>0.366078048944473</v>
       </c>
       <c r="H335" t="n">
         <v>216288</v>
@@ -10113,7 +10113,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G336" t="n">
-        <v>0.369544744491577</v>
+        <v>0.369544714689255</v>
       </c>
       <c r="H336" t="n">
         <v>156309</v>
@@ -10171,7 +10171,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G338" t="n">
-        <v>0.375091373920441</v>
+        <v>0.375091433525085</v>
       </c>
       <c r="H338" t="n">
         <v>456699</v>
@@ -10200,7 +10200,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G339" t="n">
-        <v>0.377171397209167</v>
+        <v>0.377171337604523</v>
       </c>
       <c r="H339" t="n">
         <v>443799</v>
@@ -10287,7 +10287,7 @@
         <v>0.52649998664856</v>
       </c>
       <c r="G342" t="n">
-        <v>0.365038126707077</v>
+        <v>0.365038096904755</v>
       </c>
       <c r="H342" t="n">
         <v>379604</v>
@@ -10316,7 +10316,7 @@
         <v>0.525499999523163</v>
       </c>
       <c r="G343" t="n">
-        <v>0.36434480547905</v>
+        <v>0.364344745874405</v>
       </c>
       <c r="H343" t="n">
         <v>541683</v>
@@ -10374,7 +10374,7 @@
         <v>0.53549998998642</v>
       </c>
       <c r="G345" t="n">
-        <v>0.371278047561646</v>
+        <v>0.37127810716629</v>
       </c>
       <c r="H345" t="n">
         <v>386997</v>
@@ -10403,7 +10403,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G346" t="n">
-        <v>0.377171397209167</v>
+        <v>0.377171337604523</v>
       </c>
       <c r="H346" t="n">
         <v>627083</v>
@@ -10519,7 +10519,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G350" t="n">
-        <v>0.375091373920441</v>
+        <v>0.375091433525085</v>
       </c>
       <c r="H350" t="n">
         <v>131289</v>
@@ -10548,7 +10548,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G351" t="n">
-        <v>0.371624708175659</v>
+        <v>0.371624767780304</v>
       </c>
       <c r="H351" t="n">
         <v>395496</v>
@@ -10577,7 +10577,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G352" t="n">
-        <v>0.368851453065872</v>
+        <v>0.36885142326355</v>
       </c>
       <c r="H352" t="n">
         <v>382116</v>
@@ -10606,7 +10606,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G353" t="n">
-        <v>0.3681580722332</v>
+        <v>0.368158131837845</v>
       </c>
       <c r="H353" t="n">
         <v>550023</v>
@@ -10635,7 +10635,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G354" t="n">
-        <v>0.370238035917282</v>
+        <v>0.370238065719604</v>
       </c>
       <c r="H354" t="n">
         <v>328442</v>
@@ -10722,7 +10722,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G357" t="n">
-        <v>0.373704671859741</v>
+        <v>0.373704701662064</v>
       </c>
       <c r="H357" t="n">
         <v>349245</v>
@@ -10751,7 +10751,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G358" t="n">
-        <v>0.373704671859741</v>
+        <v>0.373704701662064</v>
       </c>
       <c r="H358" t="n">
         <v>393705</v>
@@ -10809,7 +10809,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G360" t="n">
-        <v>0.373704671859741</v>
+        <v>0.373704701662064</v>
       </c>
       <c r="H360" t="n">
         <v>761662</v>
@@ -10867,7 +10867,7 @@
         <v>0.541499972343445</v>
       </c>
       <c r="G362" t="n">
-        <v>0.375438034534454</v>
+        <v>0.375438004732132</v>
       </c>
       <c r="H362" t="n">
         <v>2392283</v>
@@ -10925,7 +10925,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G364" t="n">
-        <v>0.375091373920441</v>
+        <v>0.375091433525085</v>
       </c>
       <c r="H364" t="n">
         <v>2449470</v>
@@ -10954,7 +10954,7 @@
         <v>0.587000012397766</v>
       </c>
       <c r="G365" t="n">
-        <v>0.40698453783989</v>
+        <v>0.406984567642212</v>
       </c>
       <c r="H365" t="n">
         <v>3087667</v>
@@ -10983,7 +10983,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G366" t="n">
-        <v>0.400744587182999</v>
+        <v>0.400744557380676</v>
       </c>
       <c r="H366" t="n">
         <v>1689582</v>
@@ -11012,7 +11012,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G367" t="n">
-        <v>0.425704479217529</v>
+        <v>0.425704449415207</v>
       </c>
       <c r="H367" t="n">
         <v>2929691</v>
@@ -11041,7 +11041,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G368" t="n">
-        <v>0.415997862815857</v>
+        <v>0.415997833013535</v>
       </c>
       <c r="H368" t="n">
         <v>2439950</v>
@@ -11070,7 +11070,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G369" t="n">
-        <v>0.422931164503098</v>
+        <v>0.422931104898453</v>
       </c>
       <c r="H369" t="n">
         <v>2082638</v>
@@ -11128,7 +11128,7 @@
         <v>0.554499983787537</v>
       </c>
       <c r="G371" t="n">
-        <v>0.395472705364227</v>
+        <v>0.395472645759583</v>
       </c>
       <c r="H371" t="n">
         <v>2207324</v>
@@ -11157,7 +11157,7 @@
         <v>0.547500014305115</v>
       </c>
       <c r="G372" t="n">
-        <v>0.390480220317841</v>
+        <v>0.390480250120163</v>
       </c>
       <c r="H372" t="n">
         <v>620503</v>
@@ -11331,7 +11331,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G378" t="n">
-        <v>0.382991582155228</v>
+        <v>0.38299161195755</v>
       </c>
       <c r="H378" t="n">
         <v>147938</v>
@@ -11360,7 +11360,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G379" t="n">
-        <v>0.377999097108841</v>
+        <v>0.377999126911163</v>
       </c>
       <c r="H379" t="n">
         <v>471094</v>
@@ -11389,7 +11389,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G380" t="n">
-        <v>0.379425585269928</v>
+        <v>0.37942561507225</v>
       </c>
       <c r="H380" t="n">
         <v>56186</v>
@@ -11418,7 +11418,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G381" t="n">
-        <v>0.378712385892868</v>
+        <v>0.378712356090546</v>
       </c>
       <c r="H381" t="n">
         <v>261934</v>
@@ -11447,7 +11447,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G382" t="n">
-        <v>0.375859528779984</v>
+        <v>0.375859558582306</v>
       </c>
       <c r="H382" t="n">
         <v>200254</v>
@@ -11505,7 +11505,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G384" t="n">
-        <v>0.378712385892868</v>
+        <v>0.378712356090546</v>
       </c>
       <c r="H384" t="n">
         <v>159154</v>
@@ -11534,7 +11534,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>0.370867103338242</v>
+        <v>0.370867073535919</v>
       </c>
       <c r="H385" t="n">
         <v>974032</v>
@@ -11563,7 +11563,7 @@
         <v>0.50900000333786</v>
       </c>
       <c r="G386" t="n">
-        <v>0.363021850585938</v>
+        <v>0.36302188038826</v>
       </c>
       <c r="H386" t="n">
         <v>809198</v>
@@ -11592,7 +11592,7 @@
         <v>0.50900000333786</v>
       </c>
       <c r="G387" t="n">
-        <v>0.363021850585938</v>
+        <v>0.36302188038826</v>
       </c>
       <c r="H387" t="n">
         <v>268009</v>
@@ -11621,7 +11621,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G388" t="n">
-        <v>0.364448249340057</v>
+        <v>0.364448219537735</v>
       </c>
       <c r="H388" t="n">
         <v>166729</v>
@@ -11737,7 +11737,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G392" t="n">
-        <v>0.368014276027679</v>
+        <v>0.368014246225357</v>
       </c>
       <c r="H392" t="n">
         <v>181156</v>
@@ -11766,7 +11766,7 @@
         <v>0.514500021934509</v>
       </c>
       <c r="G393" t="n">
-        <v>0.366944521665573</v>
+        <v>0.366944462060928</v>
       </c>
       <c r="H393" t="n">
         <v>177091</v>
@@ -11824,7 +11824,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G395" t="n">
-        <v>0.373006701469421</v>
+        <v>0.373006731271744</v>
       </c>
       <c r="H395" t="n">
         <v>191162</v>
@@ -11882,7 +11882,7 @@
         <v>0.541000008583069</v>
       </c>
       <c r="G397" t="n">
-        <v>0.385844379663467</v>
+        <v>0.385844439268112</v>
       </c>
       <c r="H397" t="n">
         <v>784130</v>
@@ -11911,7 +11911,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G398" t="n">
-        <v>0.392263352870941</v>
+        <v>0.392263293266296</v>
       </c>
       <c r="H398" t="n">
         <v>835831</v>
@@ -11940,7 +11940,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>0.389410495758057</v>
+        <v>0.389410465955734</v>
       </c>
       <c r="H399" t="n">
         <v>632068</v>
@@ -11969,7 +11969,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>0.389410495758057</v>
+        <v>0.389410465955734</v>
       </c>
       <c r="H400" t="n">
         <v>84126</v>
@@ -11998,7 +11998,7 @@
         <v>0.546500027179718</v>
       </c>
       <c r="G401" t="n">
-        <v>0.389767110347748</v>
+        <v>0.389767050743103</v>
       </c>
       <c r="H401" t="n">
         <v>206747</v>
@@ -12114,7 +12114,7 @@
         <v>0.537500023841858</v>
       </c>
       <c r="G405" t="n">
-        <v>0.383348226547241</v>
+        <v>0.383348196744919</v>
       </c>
       <c r="H405" t="n">
         <v>225624</v>
@@ -12143,7 +12143,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G406" t="n">
-        <v>0.379425585269928</v>
+        <v>0.37942561507225</v>
       </c>
       <c r="H406" t="n">
         <v>240630</v>
@@ -12201,7 +12201,7 @@
         <v>0.537500023841858</v>
       </c>
       <c r="G408" t="n">
-        <v>0.383348226547241</v>
+        <v>0.383348196744919</v>
       </c>
       <c r="H408" t="n">
         <v>112854</v>
@@ -12259,7 +12259,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G410" t="n">
-        <v>0.379425585269928</v>
+        <v>0.37942561507225</v>
       </c>
       <c r="H410" t="n">
         <v>309515</v>
@@ -12288,7 +12288,7 @@
         <v>0.528500020503998</v>
       </c>
       <c r="G411" t="n">
-        <v>0.376929402351379</v>
+        <v>0.376929312944412</v>
       </c>
       <c r="H411" t="n">
         <v>187465</v>
@@ -12346,7 +12346,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>0.373006701469421</v>
+        <v>0.373006731271744</v>
       </c>
       <c r="H413" t="n">
         <v>209683</v>
@@ -12375,7 +12375,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G414" t="n">
-        <v>0.373719960451126</v>
+        <v>0.373719900846481</v>
       </c>
       <c r="H414" t="n">
         <v>134310</v>
@@ -12404,7 +12404,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G415" t="n">
-        <v>0.375146359205246</v>
+        <v>0.375146329402924</v>
       </c>
       <c r="H415" t="n">
         <v>108364</v>
@@ -12433,7 +12433,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>0.373006701469421</v>
+        <v>0.373006731271744</v>
       </c>
       <c r="H416" t="n">
         <v>93017</v>
@@ -12462,7 +12462,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G417" t="n">
-        <v>0.370867103338242</v>
+        <v>0.370867073535919</v>
       </c>
       <c r="H417" t="n">
         <v>124834</v>
@@ -12491,7 +12491,7 @@
         <v>0.520500004291534</v>
       </c>
       <c r="G418" t="n">
-        <v>0.37122368812561</v>
+        <v>0.371223717927933</v>
       </c>
       <c r="H418" t="n">
         <v>13999</v>
@@ -12578,7 +12578,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G421" t="n">
-        <v>0.372293561697006</v>
+        <v>0.372293502092361</v>
       </c>
       <c r="H421" t="n">
         <v>16183</v>
@@ -12607,7 +12607,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G422" t="n">
-        <v>0.372293561697006</v>
+        <v>0.372293502092361</v>
       </c>
       <c r="H422" t="n">
         <v>10912</v>
@@ -12694,7 +12694,7 @@
         <v>0.510500013828278</v>
       </c>
       <c r="G425" t="n">
-        <v>0.364091664552689</v>
+        <v>0.364091634750366</v>
       </c>
       <c r="H425" t="n">
         <v>79003</v>
@@ -12723,7 +12723,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G426" t="n">
-        <v>0.364448249340057</v>
+        <v>0.364448219537735</v>
       </c>
       <c r="H426" t="n">
         <v>60069</v>
@@ -12810,7 +12810,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G429" t="n">
-        <v>0.373006701469421</v>
+        <v>0.373006731271744</v>
       </c>
       <c r="H429" t="n">
         <v>129868</v>
@@ -12868,7 +12868,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G431" t="n">
-        <v>0.370867103338242</v>
+        <v>0.370867073535919</v>
       </c>
       <c r="H431" t="n">
         <v>68681</v>
@@ -12897,7 +12897,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G432" t="n">
-        <v>0.372293561697006</v>
+        <v>0.372293502092361</v>
       </c>
       <c r="H432" t="n">
         <v>139099</v>
@@ -12926,7 +12926,7 @@
         <v>0.516499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>0.368370860815048</v>
+        <v>0.368370890617371</v>
       </c>
       <c r="H433" t="n">
         <v>52579</v>
@@ -12955,7 +12955,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>0.370867103338242</v>
+        <v>0.370867073535919</v>
       </c>
       <c r="H434" t="n">
         <v>222014</v>
@@ -12984,7 +12984,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G435" t="n">
-        <v>0.366587817668915</v>
+        <v>0.36658787727356</v>
       </c>
       <c r="H435" t="n">
         <v>268550</v>
@@ -13013,7 +13013,7 @@
         <v>0.533500015735626</v>
       </c>
       <c r="G436" t="n">
-        <v>0.380495369434357</v>
+        <v>0.380495399236679</v>
       </c>
       <c r="H436" t="n">
         <v>1384814</v>
@@ -13071,7 +13071,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G438" t="n">
-        <v>0.391550123691559</v>
+        <v>0.391550093889236</v>
       </c>
       <c r="H438" t="n">
         <v>448261</v>
@@ -13100,7 +13100,7 @@
         <v>0.546500027179718</v>
       </c>
       <c r="G439" t="n">
-        <v>0.389767110347748</v>
+        <v>0.389767050743103</v>
       </c>
       <c r="H439" t="n">
         <v>263573</v>
@@ -13158,7 +13158,7 @@
         <v>0.550999999046326</v>
       </c>
       <c r="G441" t="n">
-        <v>0.392976522445679</v>
+        <v>0.392976492643356</v>
       </c>
       <c r="H441" t="n">
         <v>327574</v>
@@ -13216,7 +13216,7 @@
         <v>0.556500017642975</v>
       </c>
       <c r="G443" t="n">
-        <v>0.396899163722992</v>
+        <v>0.396899104118347</v>
       </c>
       <c r="H443" t="n">
         <v>327223</v>
@@ -13245,7 +13245,7 @@
         <v>0.558499991893768</v>
       </c>
       <c r="G444" t="n">
-        <v>0.398325473070145</v>
+        <v>0.398325502872467</v>
       </c>
       <c r="H444" t="n">
         <v>379848</v>
@@ -13274,7 +13274,7 @@
         <v>0.557500004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>0.397612303495407</v>
+        <v>0.397612333297729</v>
       </c>
       <c r="H445" t="n">
         <v>260760</v>
@@ -13303,7 +13303,7 @@
         <v>0.568499982357025</v>
       </c>
       <c r="G446" t="n">
-        <v>0.405457526445389</v>
+        <v>0.405457556247711</v>
       </c>
       <c r="H446" t="n">
         <v>294416</v>
@@ -13332,7 +13332,7 @@
         <v>0.58899998664856</v>
       </c>
       <c r="G447" t="n">
-        <v>0.420078337192535</v>
+        <v>0.420078307390213</v>
       </c>
       <c r="H447" t="n">
         <v>1511134</v>
@@ -13390,7 +13390,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G449" t="n">
-        <v>0.410093426704407</v>
+        <v>0.410093396902084</v>
       </c>
       <c r="H449" t="n">
         <v>547273</v>
@@ -13448,7 +13448,7 @@
         <v>0.565500020980835</v>
       </c>
       <c r="G451" t="n">
-        <v>0.403317958116531</v>
+        <v>0.403317987918854</v>
       </c>
       <c r="H451" t="n">
         <v>384052</v>
@@ -13477,7 +13477,7 @@
         <v>0.574500024318695</v>
       </c>
       <c r="G452" t="n">
-        <v>0.409736812114716</v>
+        <v>0.409736841917038</v>
       </c>
       <c r="H452" t="n">
         <v>489291</v>
@@ -13535,7 +13535,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G454" t="n">
-        <v>0.435055613517761</v>
+        <v>0.435055643320084</v>
       </c>
       <c r="H454" t="n">
         <v>2019601</v>
@@ -13564,7 +13564,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G455" t="n">
-        <v>0.425783902406693</v>
+        <v>0.42578399181366</v>
       </c>
       <c r="H455" t="n">
         <v>1090255</v>
@@ -13651,7 +13651,7 @@
         <v>0.58899998664856</v>
       </c>
       <c r="G458" t="n">
-        <v>0.420078337192535</v>
+        <v>0.420078307390213</v>
       </c>
       <c r="H458" t="n">
         <v>363716</v>
@@ -13680,7 +13680,7 @@
         <v>0.602999985218048</v>
       </c>
       <c r="G459" t="n">
-        <v>0.430063188076019</v>
+        <v>0.430063158273697</v>
       </c>
       <c r="H459" t="n">
         <v>658253</v>
@@ -13709,7 +13709,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G460" t="n">
-        <v>0.439334839582443</v>
+        <v>0.439334809780121</v>
       </c>
       <c r="H460" t="n">
         <v>1176624</v>
@@ -13738,7 +13738,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G461" t="n">
-        <v>0.440761297941208</v>
+        <v>0.440761268138885</v>
       </c>
       <c r="H461" t="n">
         <v>352996</v>
@@ -13825,7 +13825,7 @@
         <v>0.635500013828278</v>
       </c>
       <c r="G464" t="n">
-        <v>0.453242391347885</v>
+        <v>0.453242361545563</v>
       </c>
       <c r="H464" t="n">
         <v>528014</v>
@@ -13883,7 +13883,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G466" t="n">
-        <v>0.459304600954056</v>
+        <v>0.459304690361023</v>
       </c>
       <c r="H466" t="n">
         <v>911489</v>
@@ -13999,7 +13999,7 @@
         <v>0.683000028133392</v>
       </c>
       <c r="G470" t="n">
-        <v>0.487119674682617</v>
+        <v>0.487119793891907</v>
       </c>
       <c r="H470" t="n">
         <v>1747173</v>
@@ -14028,7 +14028,7 @@
         <v>0.685500025749207</v>
       </c>
       <c r="G471" t="n">
-        <v>0.488902717828751</v>
+        <v>0.488902747631073</v>
       </c>
       <c r="H471" t="n">
         <v>1025136</v>
@@ -14115,7 +14115,7 @@
         <v>0.69650000333786</v>
       </c>
       <c r="G474" t="n">
-        <v>0.49674791097641</v>
+        <v>0.496747970581055</v>
       </c>
       <c r="H474" t="n">
         <v>525842</v>
@@ -14144,7 +14144,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G475" t="n">
-        <v>0.489259332418442</v>
+        <v>0.489259272813797</v>
       </c>
       <c r="H475" t="n">
         <v>883944</v>
@@ -14202,7 +14202,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G477" t="n">
-        <v>0.479274362325668</v>
+        <v>0.479274421930313</v>
       </c>
       <c r="H477" t="n">
         <v>805168</v>
@@ -14260,7 +14260,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G479" t="n">
-        <v>0.473568707704544</v>
+        <v>0.473568797111511</v>
       </c>
       <c r="H479" t="n">
         <v>636967</v>
@@ -14318,7 +14318,7 @@
         <v>0.640500009059906</v>
       </c>
       <c r="G481" t="n">
-        <v>0.45680844783783</v>
+        <v>0.456808418035507</v>
       </c>
       <c r="H481" t="n">
         <v>1212506</v>
@@ -14376,7 +14376,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>0.460017800331116</v>
+        <v>0.46001785993576</v>
       </c>
       <c r="H483" t="n">
         <v>213076</v>
@@ -14405,7 +14405,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G484" t="n">
-        <v>0.470715939998627</v>
+        <v>0.470715969800949</v>
       </c>
       <c r="H484" t="n">
         <v>267053</v>
@@ -14434,7 +14434,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G485" t="n">
-        <v>0.477847933769226</v>
+        <v>0.477848052978516</v>
       </c>
       <c r="H485" t="n">
         <v>160100</v>
@@ -14463,7 +14463,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G486" t="n">
-        <v>0.472142279148102</v>
+        <v>0.472142368555069</v>
       </c>
       <c r="H486" t="n">
         <v>178100</v>
@@ -14492,7 +14492,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G487" t="n">
-        <v>0.473568707704544</v>
+        <v>0.473568797111511</v>
       </c>
       <c r="H487" t="n">
         <v>109781</v>
@@ -14521,7 +14521,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G488" t="n">
-        <v>0.473568707704544</v>
+        <v>0.473568797111511</v>
       </c>
       <c r="H488" t="n">
         <v>146261</v>
@@ -14550,7 +14550,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G489" t="n">
-        <v>0.473568707704544</v>
+        <v>0.473568797111511</v>
       </c>
       <c r="H489" t="n">
         <v>306532</v>
@@ -14579,7 +14579,7 @@
         <v>0.664499998092651</v>
       </c>
       <c r="G490" t="n">
-        <v>0.473925411701202</v>
+        <v>0.473925352096558</v>
       </c>
       <c r="H490" t="n">
         <v>473764</v>
@@ -14608,7 +14608,7 @@
         <v>0.680999994277954</v>
       </c>
       <c r="G491" t="n">
-        <v>0.485693246126175</v>
+        <v>0.485693275928497</v>
       </c>
       <c r="H491" t="n">
         <v>735175</v>
@@ -14637,7 +14637,7 @@
         <v>0.670499980449677</v>
       </c>
       <c r="G492" t="n">
-        <v>0.478204607963562</v>
+        <v>0.47820457816124</v>
       </c>
       <c r="H492" t="n">
         <v>436203</v>
@@ -14666,7 +14666,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G493" t="n">
-        <v>0.471429169178009</v>
+        <v>0.471429198980331</v>
       </c>
       <c r="H493" t="n">
         <v>333090</v>
@@ -14753,7 +14753,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G496" t="n">
-        <v>0.486406534910202</v>
+        <v>0.486406475305557</v>
       </c>
       <c r="H496" t="n">
         <v>363841</v>
@@ -14782,7 +14782,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G497" t="n">
-        <v>0.481413960456848</v>
+        <v>0.481414049863815</v>
       </c>
       <c r="H497" t="n">
         <v>261864</v>
@@ -14811,7 +14811,7 @@
         <v>0.681500017642975</v>
       </c>
       <c r="G498" t="n">
-        <v>0.486049920320511</v>
+        <v>0.486049860715866</v>
       </c>
       <c r="H498" t="n">
         <v>150334</v>
@@ -14840,7 +14840,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G499" t="n">
-        <v>0.484980046749115</v>
+        <v>0.484980076551437</v>
       </c>
       <c r="H499" t="n">
         <v>454933</v>
@@ -14869,7 +14869,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G500" t="n">
-        <v>0.487832963466644</v>
+        <v>0.487832933664322</v>
       </c>
       <c r="H500" t="n">
         <v>165732</v>
@@ -14898,7 +14898,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G501" t="n">
-        <v>0.490685701370239</v>
+        <v>0.490685731172562</v>
       </c>
       <c r="H501" t="n">
         <v>572022</v>
@@ -14927,7 +14927,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G502" t="n">
-        <v>0.486406534910202</v>
+        <v>0.486406475305557</v>
       </c>
       <c r="H502" t="n">
         <v>385933</v>
@@ -14956,7 +14956,7 @@
         <v>0.671500027179718</v>
       </c>
       <c r="G503" t="n">
-        <v>0.478917866945267</v>
+        <v>0.478917807340622</v>
       </c>
       <c r="H503" t="n">
         <v>406752</v>
@@ -14985,7 +14985,7 @@
         <v>0.674499988555908</v>
       </c>
       <c r="G504" t="n">
-        <v>0.481057405471802</v>
+        <v>0.481057375669479</v>
       </c>
       <c r="H504" t="n">
         <v>382655</v>
@@ -15043,7 +15043,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G506" t="n">
-        <v>0.477847933769226</v>
+        <v>0.477848052978516</v>
       </c>
       <c r="H506" t="n">
         <v>296703</v>
@@ -15072,7 +15072,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G507" t="n">
-        <v>0.477847933769226</v>
+        <v>0.477848052978516</v>
       </c>
       <c r="H507" t="n">
         <v>229628</v>
@@ -15101,7 +15101,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G508" t="n">
-        <v>0.477847933769226</v>
+        <v>0.477848052978516</v>
       </c>
       <c r="H508" t="n">
         <v>139779</v>
@@ -15130,7 +15130,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G509" t="n">
-        <v>0.479274362325668</v>
+        <v>0.479274421930313</v>
       </c>
       <c r="H509" t="n">
         <v>174437</v>
@@ -15159,7 +15159,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G510" t="n">
-        <v>0.480700790882111</v>
+        <v>0.480700820684433</v>
       </c>
       <c r="H510" t="n">
         <v>230818</v>
@@ -15188,7 +15188,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G511" t="n">
-        <v>0.480700790882111</v>
+        <v>0.480700820684433</v>
       </c>
       <c r="H511" t="n">
         <v>222261</v>
@@ -15217,7 +15217,7 @@
         <v>0.672500014305115</v>
       </c>
       <c r="G512" t="n">
-        <v>0.479631036520004</v>
+        <v>0.479630976915359</v>
       </c>
       <c r="H512" t="n">
         <v>191872</v>
@@ -15246,7 +15246,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G513" t="n">
-        <v>0.476421564817429</v>
+        <v>0.476421505212784</v>
       </c>
       <c r="H513" t="n">
         <v>303975</v>
@@ -15275,7 +15275,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G514" t="n">
-        <v>0.484980046749115</v>
+        <v>0.484980076551437</v>
       </c>
       <c r="H514" t="n">
         <v>387763</v>
@@ -15304,7 +15304,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G515" t="n">
-        <v>0.488546043634415</v>
+        <v>0.488546073436737</v>
       </c>
       <c r="H515" t="n">
         <v>465344</v>
@@ -15362,7 +15362,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G517" t="n">
-        <v>0.533478021621704</v>
+        <v>0.533478140830994</v>
       </c>
       <c r="H517" t="n">
         <v>3500455</v>
@@ -15420,7 +15420,7 @@
         <v>0.75</v>
       </c>
       <c r="G519" t="n">
-        <v>0.534904420375824</v>
+        <v>0.534904479980469</v>
       </c>
       <c r="H519" t="n">
         <v>776365</v>
@@ -15478,7 +15478,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G521" t="n">
-        <v>0.567712008953094</v>
+        <v>0.56771194934845</v>
       </c>
       <c r="H521" t="n">
         <v>3649667</v>
@@ -15536,7 +15536,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G523" t="n">
-        <v>0.551308274269104</v>
+        <v>0.551308155059814</v>
       </c>
       <c r="H523" t="n">
         <v>1020040</v>
@@ -15565,7 +15565,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G524" t="n">
-        <v>0.552021443843842</v>
+        <v>0.552021384239197</v>
       </c>
       <c r="H524" t="n">
         <v>1014101</v>
@@ -15594,7 +15594,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G525" t="n">
-        <v>0.557727098464966</v>
+        <v>0.557727038860321</v>
       </c>
       <c r="H525" t="n">
         <v>762556</v>
@@ -15652,7 +15652,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G527" t="n">
-        <v>0.559866607189178</v>
+        <v>0.559866666793823</v>
       </c>
       <c r="H527" t="n">
         <v>971070</v>
@@ -15739,7 +15739,7 @@
         <v>0.820999979972839</v>
       </c>
       <c r="G530" t="n">
-        <v>0.585542142391205</v>
+        <v>0.58554208278656</v>
       </c>
       <c r="H530" t="n">
         <v>2116241</v>
@@ -15768,7 +15768,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G531" t="n">
-        <v>0.557727098464966</v>
+        <v>0.557727038860321</v>
       </c>
       <c r="H531" t="n">
         <v>1941450</v>
@@ -15826,7 +15826,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G533" t="n">
-        <v>0.52777236700058</v>
+        <v>0.527772486209869</v>
       </c>
       <c r="H533" t="n">
         <v>443051</v>
@@ -15855,7 +15855,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G534" t="n">
-        <v>0.524206340312958</v>
+        <v>0.524206399917603</v>
       </c>
       <c r="H534" t="n">
         <v>854181</v>
@@ -15884,7 +15884,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G535" t="n">
-        <v>0.511368632316589</v>
+        <v>0.511368751525879</v>
       </c>
       <c r="H535" t="n">
         <v>592218</v>
@@ -15913,7 +15913,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>0.498531013727188</v>
+        <v>0.498530954122543</v>
       </c>
       <c r="H536" t="n">
         <v>1211023</v>
@@ -15942,7 +15942,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G537" t="n">
-        <v>0.483553647994995</v>
+        <v>0.48355370759964</v>
       </c>
       <c r="H537" t="n">
         <v>921482</v>
@@ -16029,7 +16029,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G540" t="n">
-        <v>0.524206340312958</v>
+        <v>0.524206399917603</v>
       </c>
       <c r="H540" t="n">
         <v>1116376</v>
@@ -16058,7 +16058,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G541" t="n">
-        <v>0.499957323074341</v>
+        <v>0.499957382678986</v>
       </c>
       <c r="H541" t="n">
         <v>641735</v>
@@ -16087,7 +16087,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>0.494964867830276</v>
+        <v>0.494964957237244</v>
       </c>
       <c r="H542" t="n">
         <v>376768</v>
@@ -16116,7 +16116,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G543" t="n">
-        <v>0.509229063987732</v>
+        <v>0.509229123592377</v>
       </c>
       <c r="H543" t="n">
         <v>645637</v>
@@ -16145,7 +16145,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G544" t="n">
-        <v>0.499957323074341</v>
+        <v>0.499957382678986</v>
       </c>
       <c r="H544" t="n">
         <v>272422</v>
@@ -16174,7 +16174,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G545" t="n">
-        <v>0.50851583480835</v>
+        <v>0.508515775203705</v>
       </c>
       <c r="H545" t="n">
         <v>161307</v>
@@ -16232,7 +16232,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G547" t="n">
-        <v>0.493538498878479</v>
+        <v>0.493538558483124</v>
       </c>
       <c r="H547" t="n">
         <v>413718</v>
@@ -16261,7 +16261,7 @@
         <v>0.686999976634979</v>
       </c>
       <c r="G548" t="n">
-        <v>0.489972442388535</v>
+        <v>0.489972472190857</v>
       </c>
       <c r="H548" t="n">
         <v>169305</v>
@@ -16290,7 +16290,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G549" t="n">
-        <v>0.496391296386719</v>
+        <v>0.496391355991364</v>
       </c>
       <c r="H549" t="n">
         <v>730849</v>
@@ -16319,7 +16319,7 @@
         <v>0.683000028133392</v>
       </c>
       <c r="G550" t="n">
-        <v>0.487119674682617</v>
+        <v>0.487119793891907</v>
       </c>
       <c r="H550" t="n">
         <v>255279</v>
@@ -16348,7 +16348,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G551" t="n">
-        <v>0.471429169178009</v>
+        <v>0.471429198980331</v>
       </c>
       <c r="H551" t="n">
         <v>746198</v>
@@ -16377,7 +16377,7 @@
         <v>0.669000029563904</v>
       </c>
       <c r="G552" t="n">
-        <v>0.477134823799133</v>
+        <v>0.477134853601456</v>
       </c>
       <c r="H552" t="n">
         <v>399800</v>
@@ -16406,7 +16406,7 @@
         <v>0.669000029563904</v>
       </c>
       <c r="G553" t="n">
-        <v>0.477134823799133</v>
+        <v>0.477134853601456</v>
       </c>
       <c r="H553" t="n">
         <v>250562</v>
@@ -16493,7 +16493,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G556" t="n">
-        <v>0.44931972026825</v>
+        <v>0.449319750070572</v>
       </c>
       <c r="H556" t="n">
         <v>331073</v>
@@ -16551,7 +16551,7 @@
         <v>0.638999998569489</v>
       </c>
       <c r="G558" t="n">
-        <v>0.455738633871078</v>
+        <v>0.455738663673401</v>
       </c>
       <c r="H558" t="n">
         <v>166118</v>
@@ -16609,7 +16609,7 @@
         <v>0.662999987602234</v>
       </c>
       <c r="G560" t="n">
-        <v>0.472855538129807</v>
+        <v>0.472855567932129</v>
       </c>
       <c r="H560" t="n">
         <v>328687</v>
@@ -16638,7 +16638,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G561" t="n">
-        <v>0.481413960456848</v>
+        <v>0.481414049863815</v>
       </c>
       <c r="H561" t="n">
         <v>390403</v>
@@ -16667,7 +16667,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G562" t="n">
-        <v>0.479274362325668</v>
+        <v>0.479274421930313</v>
       </c>
       <c r="H562" t="n">
         <v>440613</v>
@@ -16696,7 +16696,7 @@
         <v>0.657000005245209</v>
       </c>
       <c r="G563" t="n">
-        <v>0.468576371669769</v>
+        <v>0.468576341867447</v>
       </c>
       <c r="H563" t="n">
         <v>350178</v>
@@ -16725,7 +16725,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G564" t="n">
-        <v>0.477847933769226</v>
+        <v>0.477848052978516</v>
       </c>
       <c r="H564" t="n">
         <v>186181</v>
@@ -16783,7 +16783,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G566" t="n">
-        <v>0.457878202199936</v>
+        <v>0.457878261804581</v>
       </c>
       <c r="H566" t="n">
         <v>207250</v>
@@ -16841,7 +16841,7 @@
         <v>0.640999972820282</v>
       </c>
       <c r="G568" t="n">
-        <v>0.457165062427521</v>
+        <v>0.457165002822876</v>
       </c>
       <c r="H568" t="n">
         <v>63224</v>
@@ -16870,7 +16870,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G569" t="n">
-        <v>0.447893410921097</v>
+        <v>0.447893381118774</v>
       </c>
       <c r="H569" t="n">
         <v>321587</v>
@@ -16899,7 +16899,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G570" t="n">
-        <v>0.460731089115143</v>
+        <v>0.460731118917465</v>
       </c>
       <c r="H570" t="n">
         <v>595768</v>
@@ -16928,7 +16928,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G571" t="n">
-        <v>0.462870657444</v>
+        <v>0.462870687246323</v>
       </c>
       <c r="H571" t="n">
         <v>294321</v>
@@ -16986,7 +16986,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G573" t="n">
-        <v>0.452885776758194</v>
+        <v>0.452885746955872</v>
       </c>
       <c r="H573" t="n">
         <v>212451</v>
@@ -17044,7 +17044,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>0.44931972026825</v>
+        <v>0.449319750070572</v>
       </c>
       <c r="H575" t="n">
         <v>167042</v>
@@ -17073,7 +17073,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G576" t="n">
-        <v>0.447893410921097</v>
+        <v>0.447893381118774</v>
       </c>
       <c r="H576" t="n">
         <v>430709</v>
@@ -17102,7 +17102,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G577" t="n">
-        <v>0.46358385682106</v>
+        <v>0.463583886623383</v>
       </c>
       <c r="H577" t="n">
         <v>953448</v>
@@ -17131,7 +17131,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G578" t="n">
-        <v>0.457878202199936</v>
+        <v>0.457878261804581</v>
       </c>
       <c r="H578" t="n">
         <v>272503</v>
@@ -17160,7 +17160,7 @@
         <v>0.640999972820282</v>
       </c>
       <c r="G579" t="n">
-        <v>0.457165062427521</v>
+        <v>0.457165002822876</v>
       </c>
       <c r="H579" t="n">
         <v>196518</v>
@@ -17189,7 +17189,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G580" t="n">
-        <v>0.459304600954056</v>
+        <v>0.459304690361023</v>
       </c>
       <c r="H580" t="n">
         <v>241513</v>
@@ -17247,7 +17247,7 @@
         <v>0.640999972820282</v>
       </c>
       <c r="G582" t="n">
-        <v>0.457165062427521</v>
+        <v>0.457165002822876</v>
       </c>
       <c r="H582" t="n">
         <v>169509</v>
@@ -17276,7 +17276,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G583" t="n">
-        <v>0.462870657444</v>
+        <v>0.462870687246323</v>
       </c>
       <c r="H583" t="n">
         <v>558481</v>
@@ -17305,7 +17305,7 @@
         <v>0.652999997138977</v>
       </c>
       <c r="G584" t="n">
-        <v>0.465723484754562</v>
+        <v>0.465723514556885</v>
       </c>
       <c r="H584" t="n">
         <v>47510</v>
@@ -17334,7 +17334,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G585" t="n">
-        <v>0.462157487869263</v>
+        <v>0.46215745806694</v>
       </c>
       <c r="H585" t="n">
         <v>262672</v>
@@ -17363,7 +17363,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G586" t="n">
-        <v>0.462157487869263</v>
+        <v>0.46215745806694</v>
       </c>
       <c r="H586" t="n">
         <v>124001</v>
@@ -17392,7 +17392,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G587" t="n">
-        <v>0.482127219438553</v>
+        <v>0.482127249240875</v>
       </c>
       <c r="H587" t="n">
         <v>1047312</v>
@@ -17421,7 +17421,7 @@
         <v>0.680999994277954</v>
       </c>
       <c r="G588" t="n">
-        <v>0.485693246126175</v>
+        <v>0.485693275928497</v>
       </c>
       <c r="H588" t="n">
         <v>469368</v>
@@ -17450,7 +17450,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G589" t="n">
-        <v>0.479274362325668</v>
+        <v>0.479274421930313</v>
       </c>
       <c r="H589" t="n">
         <v>283037</v>
@@ -17479,7 +17479,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G590" t="n">
-        <v>0.487832963466644</v>
+        <v>0.487832933664322</v>
       </c>
       <c r="H590" t="n">
         <v>367211</v>
@@ -17508,7 +17508,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G591" t="n">
-        <v>0.484980046749115</v>
+        <v>0.484980076551437</v>
       </c>
       <c r="H591" t="n">
         <v>297030</v>
@@ -17537,7 +17537,7 @@
         <v>0.676999986171722</v>
       </c>
       <c r="G592" t="n">
-        <v>0.482840329408646</v>
+        <v>0.482840418815613</v>
       </c>
       <c r="H592" t="n">
         <v>336282</v>
@@ -17566,7 +17566,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G593" t="n">
-        <v>0.480700790882111</v>
+        <v>0.480700820684433</v>
       </c>
       <c r="H593" t="n">
         <v>228977</v>
@@ -17595,7 +17595,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G594" t="n">
-        <v>0.479274362325668</v>
+        <v>0.479274421930313</v>
       </c>
       <c r="H594" t="n">
         <v>21265</v>
@@ -17624,7 +17624,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G595" t="n">
-        <v>0.474995106458664</v>
+        <v>0.474995195865631</v>
       </c>
       <c r="H595" t="n">
         <v>428171</v>
@@ -17653,7 +17653,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G596" t="n">
-        <v>0.484980046749115</v>
+        <v>0.484980076551437</v>
       </c>
       <c r="H596" t="n">
         <v>632920</v>
@@ -17682,7 +17682,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G597" t="n">
-        <v>0.496391296386719</v>
+        <v>0.496391355991364</v>
       </c>
       <c r="H597" t="n">
         <v>1067476</v>
@@ -17711,7 +17711,7 @@
         <v>0.686999976634979</v>
       </c>
       <c r="G598" t="n">
-        <v>0.489972442388535</v>
+        <v>0.489972472190857</v>
       </c>
       <c r="H598" t="n">
         <v>413713</v>
@@ -17740,7 +17740,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G599" t="n">
-        <v>0.482127219438553</v>
+        <v>0.482127249240875</v>
       </c>
       <c r="H599" t="n">
         <v>415358</v>
@@ -17769,7 +17769,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G600" t="n">
-        <v>0.482127219438553</v>
+        <v>0.482127249240875</v>
       </c>
       <c r="H600" t="n">
         <v>337865</v>
@@ -17798,7 +17798,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G601" t="n">
-        <v>0.483553647994995</v>
+        <v>0.48355370759964</v>
       </c>
       <c r="H601" t="n">
         <v>375749</v>
@@ -17827,7 +17827,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G602" t="n">
-        <v>0.482127219438553</v>
+        <v>0.482127249240875</v>
       </c>
       <c r="H602" t="n">
         <v>184830</v>
@@ -17856,7 +17856,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G603" t="n">
-        <v>0.475708365440369</v>
+        <v>0.475708395242691</v>
       </c>
       <c r="H603" t="n">
         <v>238406</v>
@@ -17885,7 +17885,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G604" t="n">
-        <v>0.479274362325668</v>
+        <v>0.479274421930313</v>
       </c>
       <c r="H604" t="n">
         <v>214414</v>
@@ -17914,7 +17914,7 @@
         <v>0.662999987602234</v>
       </c>
       <c r="G605" t="n">
-        <v>0.472855538129807</v>
+        <v>0.472855567932129</v>
       </c>
       <c r="H605" t="n">
         <v>559316</v>
@@ -17943,7 +17943,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G606" t="n">
-        <v>0.471429169178009</v>
+        <v>0.471429198980331</v>
       </c>
       <c r="H606" t="n">
         <v>414467</v>
@@ -18001,7 +18001,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G608" t="n">
-        <v>0.465010315179825</v>
+        <v>0.465010285377502</v>
       </c>
       <c r="H608" t="n">
         <v>429401</v>
@@ -18030,7 +18030,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G609" t="n">
-        <v>0.471429169178009</v>
+        <v>0.471429198980331</v>
       </c>
       <c r="H609" t="n">
         <v>229524</v>
@@ -18059,7 +18059,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G610" t="n">
-        <v>0.471429169178009</v>
+        <v>0.471429198980331</v>
       </c>
       <c r="H610" t="n">
         <v>199447</v>
@@ -18088,7 +18088,7 @@
         <v>0.671000003814697</v>
       </c>
       <c r="G611" t="n">
-        <v>0.478561282157898</v>
+        <v>0.478561222553253</v>
       </c>
       <c r="H611" t="n">
         <v>363350</v>
@@ -18117,7 +18117,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G612" t="n">
-        <v>0.46358385682106</v>
+        <v>0.463583886623383</v>
       </c>
       <c r="H612" t="n">
         <v>638512</v>
@@ -18146,7 +18146,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G613" t="n">
-        <v>0.435055613517761</v>
+        <v>0.435055643320084</v>
       </c>
       <c r="H613" t="n">
         <v>2361187</v>
@@ -18204,7 +18204,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G615" t="n">
-        <v>0.445040553808212</v>
+        <v>0.445040583610535</v>
       </c>
       <c r="H615" t="n">
         <v>402882</v>
@@ -18233,7 +18233,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G616" t="n">
-        <v>0.432202845811844</v>
+        <v>0.432202816009521</v>
       </c>
       <c r="H616" t="n">
         <v>300659</v>
@@ -18291,7 +18291,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>0.43862172961235</v>
+        <v>0.438621670007706</v>
       </c>
       <c r="H618" t="n">
         <v>188963</v>
@@ -18320,7 +18320,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G619" t="n">
-        <v>0.435055613517761</v>
+        <v>0.435055643320084</v>
       </c>
       <c r="H619" t="n">
         <v>209643</v>
@@ -18378,7 +18378,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G621" t="n">
-        <v>0.435055613517761</v>
+        <v>0.435055643320084</v>
       </c>
       <c r="H621" t="n">
         <v>297713</v>
@@ -18465,7 +18465,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G624" t="n">
-        <v>0.435768842697144</v>
+        <v>0.435768872499466</v>
       </c>
       <c r="H624" t="n">
         <v>160866</v>
@@ -18552,7 +18552,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G627" t="n">
-        <v>0.437908470630646</v>
+        <v>0.437908560037613</v>
       </c>
       <c r="H627" t="n">
         <v>250579</v>
@@ -18581,7 +18581,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G628" t="n">
-        <v>0.46444833278656</v>
+        <v>0.464448362588882</v>
       </c>
       <c r="H628" t="n">
         <v>524270</v>
@@ -18639,7 +18639,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G630" t="n">
-        <v>0.454127252101898</v>
+        <v>0.454127281904221</v>
       </c>
       <c r="H630" t="n">
         <v>157895</v>
@@ -18697,7 +18697,7 @@
         <v>0.602999985218048</v>
       </c>
       <c r="G632" t="n">
-        <v>0.444543391466141</v>
+        <v>0.444543421268463</v>
       </c>
       <c r="H632" t="n">
         <v>133227</v>
@@ -18726,7 +18726,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G633" t="n">
-        <v>0.440857321023941</v>
+        <v>0.440857350826263</v>
       </c>
       <c r="H633" t="n">
         <v>140708</v>
@@ -18755,7 +18755,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G634" t="n">
-        <v>0.443069070577621</v>
+        <v>0.443069010972977</v>
       </c>
       <c r="H634" t="n">
         <v>119659</v>
@@ -18784,7 +18784,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G635" t="n">
-        <v>0.439382970333099</v>
+        <v>0.439382940530777</v>
       </c>
       <c r="H635" t="n">
         <v>271339</v>
@@ -18813,7 +18813,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G636" t="n">
-        <v>0.437908411026001</v>
+        <v>0.437908500432968</v>
       </c>
       <c r="H636" t="n">
         <v>76203</v>
@@ -18842,7 +18842,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G637" t="n">
-        <v>0.43864569067955</v>
+        <v>0.438645660877228</v>
       </c>
       <c r="H637" t="n">
         <v>102014</v>
@@ -18871,7 +18871,7 @@
         <v>0.580999970436096</v>
       </c>
       <c r="G638" t="n">
-        <v>0.428324550390244</v>
+        <v>0.428324580192566</v>
       </c>
       <c r="H638" t="n">
         <v>135971</v>
@@ -18929,7 +18929,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G640" t="n">
-        <v>0.434959471225739</v>
+        <v>0.434959560632706</v>
       </c>
       <c r="H640" t="n">
         <v>85124</v>
@@ -18987,7 +18987,7 @@
         <v>0.573000013828278</v>
       </c>
       <c r="G642" t="n">
-        <v>0.422426819801331</v>
+        <v>0.422426879405975</v>
       </c>
       <c r="H642" t="n">
         <v>199579</v>
@@ -19016,7 +19016,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G643" t="n">
-        <v>0.423901230096817</v>
+        <v>0.423901259899139</v>
       </c>
       <c r="H643" t="n">
         <v>313684</v>
@@ -19045,7 +19045,7 @@
         <v>0.640999972820282</v>
       </c>
       <c r="G644" t="n">
-        <v>0.472557753324509</v>
+        <v>0.472557723522186</v>
       </c>
       <c r="H644" t="n">
         <v>1172416</v>
@@ -19074,7 +19074,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G645" t="n">
-        <v>0.453390121459961</v>
+        <v>0.453390061855316</v>
       </c>
       <c r="H645" t="n">
         <v>658847</v>
@@ -19103,7 +19103,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G646" t="n">
-        <v>0.46444833278656</v>
+        <v>0.464448362588882</v>
       </c>
       <c r="H646" t="n">
         <v>307664</v>
@@ -19132,7 +19132,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G647" t="n">
-        <v>0.460025072097778</v>
+        <v>0.460025101900101</v>
       </c>
       <c r="H647" t="n">
         <v>439185</v>
@@ -19161,7 +19161,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G648" t="n">
-        <v>0.46444833278656</v>
+        <v>0.464448362588882</v>
       </c>
       <c r="H648" t="n">
         <v>155737</v>
@@ -19190,7 +19190,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G649" t="n">
-        <v>0.468134433031082</v>
+        <v>0.468134462833405</v>
       </c>
       <c r="H649" t="n">
         <v>233736</v>
@@ -19277,7 +19277,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>0.443806201219559</v>
+        <v>0.443806171417236</v>
       </c>
       <c r="H652" t="n">
         <v>151234</v>
@@ -19306,7 +19306,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>0.443806201219559</v>
+        <v>0.443806171417236</v>
       </c>
       <c r="H653" t="n">
         <v>54731</v>
@@ -19364,7 +19364,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>0.436434030532837</v>
+        <v>0.436434000730515</v>
       </c>
       <c r="H655" t="n">
         <v>110650</v>
@@ -19393,7 +19393,7 @@
         <v>0.58899998664856</v>
       </c>
       <c r="G656" t="n">
-        <v>0.434222310781479</v>
+        <v>0.434222340583801</v>
       </c>
       <c r="H656" t="n">
         <v>116429</v>
@@ -19422,7 +19422,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>0.436434030532837</v>
+        <v>0.436434000730515</v>
       </c>
       <c r="H657" t="n">
         <v>185796</v>
@@ -19451,7 +19451,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>0.446017891168594</v>
+        <v>0.446017950773239</v>
       </c>
       <c r="H658" t="n">
         <v>257544</v>
@@ -19480,7 +19480,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>0.446017891168594</v>
+        <v>0.446017950773239</v>
       </c>
       <c r="H659" t="n">
         <v>34679</v>
@@ -19538,7 +19538,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G661" t="n">
-        <v>0.437908411026001</v>
+        <v>0.437908500432968</v>
       </c>
       <c r="H661" t="n">
         <v>122167</v>
@@ -19567,7 +19567,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G662" t="n">
-        <v>0.42021518945694</v>
+        <v>0.420215159654617</v>
       </c>
       <c r="H662" t="n">
         <v>445495</v>
@@ -19625,7 +19625,7 @@
         <v>0.587000012397766</v>
       </c>
       <c r="G664" t="n">
-        <v>0.432747960090637</v>
+        <v>0.432747930288315</v>
       </c>
       <c r="H664" t="n">
         <v>238971</v>
@@ -19712,7 +19712,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G667" t="n">
-        <v>0.421689629554749</v>
+        <v>0.421689659357071</v>
       </c>
       <c r="H667" t="n">
         <v>121439</v>
@@ -19741,7 +19741,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G668" t="n">
-        <v>0.418740749359131</v>
+        <v>0.418740779161453</v>
       </c>
       <c r="H668" t="n">
         <v>113963</v>
@@ -19799,7 +19799,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G670" t="n">
-        <v>0.414317399263382</v>
+        <v>0.414317429065704</v>
       </c>
       <c r="H670" t="n">
         <v>68699</v>
@@ -19828,7 +19828,7 @@
         <v>0.559000015258789</v>
       </c>
       <c r="G671" t="n">
-        <v>0.412105798721313</v>
+        <v>0.412105768918991</v>
       </c>
       <c r="H671" t="n">
         <v>16118</v>
@@ -19886,7 +19886,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G673" t="n">
-        <v>0.42021518945694</v>
+        <v>0.420215159654617</v>
       </c>
       <c r="H673" t="n">
         <v>51140</v>
@@ -19915,7 +19915,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G674" t="n">
-        <v>0.42021518945694</v>
+        <v>0.420215159654617</v>
       </c>
       <c r="H674" t="n">
         <v>18820</v>
@@ -19944,7 +19944,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G675" t="n">
-        <v>0.41652911901474</v>
+        <v>0.416529059410095</v>
       </c>
       <c r="H675" t="n">
         <v>46803</v>
@@ -19973,7 +19973,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G676" t="n">
-        <v>0.414317399263382</v>
+        <v>0.414317429065704</v>
       </c>
       <c r="H676" t="n">
         <v>249768</v>
@@ -20031,7 +20031,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G678" t="n">
-        <v>0.434959471225739</v>
+        <v>0.434959560632706</v>
       </c>
       <c r="H678" t="n">
         <v>212010</v>
@@ -20060,7 +20060,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G679" t="n">
-        <v>0.440120100975037</v>
+        <v>0.440120130777359</v>
       </c>
       <c r="H679" t="n">
         <v>407194</v>
@@ -20089,7 +20089,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G680" t="n">
-        <v>0.443806201219559</v>
+        <v>0.443806171417236</v>
       </c>
       <c r="H680" t="n">
         <v>592388</v>
@@ -20118,7 +20118,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G681" t="n">
-        <v>0.43201071023941</v>
+        <v>0.432010740041733</v>
       </c>
       <c r="H681" t="n">
         <v>266895</v>
@@ -20176,7 +20176,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>0.436434030532837</v>
+        <v>0.436434000730515</v>
       </c>
       <c r="H683" t="n">
         <v>211672</v>
@@ -20205,7 +20205,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G684" t="n">
-        <v>0.446017891168594</v>
+        <v>0.446017950773239</v>
       </c>
       <c r="H684" t="n">
         <v>430145</v>
@@ -20234,7 +20234,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G685" t="n">
-        <v>0.449703991413116</v>
+        <v>0.449703961610794</v>
       </c>
       <c r="H685" t="n">
         <v>228702</v>
@@ -20263,7 +20263,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G686" t="n">
-        <v>0.451178371906281</v>
+        <v>0.451178401708603</v>
       </c>
       <c r="H686" t="n">
         <v>273842</v>
@@ -20321,7 +20321,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G688" t="n">
-        <v>0.437171280384064</v>
+        <v>0.437171220779419</v>
       </c>
       <c r="H688" t="n">
         <v>170043</v>
@@ -20350,7 +20350,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G689" t="n">
-        <v>0.442331850528717</v>
+        <v>0.442331790924072</v>
       </c>
       <c r="H689" t="n">
         <v>202453</v>
@@ -20379,7 +20379,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>0.443806201219559</v>
+        <v>0.443806171417236</v>
       </c>
       <c r="H690" t="n">
         <v>89733</v>
@@ -20466,7 +20466,7 @@
         <v>0.580999970436096</v>
       </c>
       <c r="G693" t="n">
-        <v>0.428324550390244</v>
+        <v>0.428324580192566</v>
       </c>
       <c r="H693" t="n">
         <v>245882</v>
@@ -20495,7 +20495,7 @@
         <v>0.587000012397766</v>
       </c>
       <c r="G694" t="n">
-        <v>0.432747960090637</v>
+        <v>0.432747930288315</v>
       </c>
       <c r="H694" t="n">
         <v>66411</v>
@@ -20524,7 +20524,7 @@
         <v>0.591000020503998</v>
       </c>
       <c r="G695" t="n">
-        <v>0.435696810483932</v>
+        <v>0.435696840286255</v>
       </c>
       <c r="H695" t="n">
         <v>31803</v>
@@ -20553,7 +20553,7 @@
         <v>0.58899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>0.434222310781479</v>
+        <v>0.434222340583801</v>
       </c>
       <c r="H696" t="n">
         <v>130248</v>
@@ -20611,7 +20611,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G698" t="n">
-        <v>0.439382970333099</v>
+        <v>0.439382940530777</v>
       </c>
       <c r="H698" t="n">
         <v>24964</v>
@@ -20640,7 +20640,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G699" t="n">
-        <v>0.437908411026001</v>
+        <v>0.437908500432968</v>
       </c>
       <c r="H699" t="n">
         <v>86478</v>
@@ -20669,7 +20669,7 @@
         <v>0.583000004291534</v>
       </c>
       <c r="G700" t="n">
-        <v>0.429799050092697</v>
+        <v>0.42979907989502</v>
       </c>
       <c r="H700" t="n">
         <v>50758</v>
@@ -20756,7 +20756,7 @@
         <v>0.552999973297119</v>
       </c>
       <c r="G703" t="n">
-        <v>0.407682418823242</v>
+        <v>0.407682478427887</v>
       </c>
       <c r="H703" t="n">
         <v>275869</v>
@@ -20843,7 +20843,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G706" t="n">
-        <v>0.409156888723373</v>
+        <v>0.409156918525696</v>
       </c>
       <c r="H706" t="n">
         <v>242559</v>
@@ -20901,7 +20901,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G708" t="n">
-        <v>0.388514786958694</v>
+        <v>0.38851472735405</v>
       </c>
       <c r="H708" t="n">
         <v>500545</v>
@@ -20930,7 +20930,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G709" t="n">
-        <v>0.392200797796249</v>
+        <v>0.392200857400894</v>
       </c>
       <c r="H709" t="n">
         <v>424694</v>
@@ -20959,7 +20959,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G710" t="n">
-        <v>0.392200797796249</v>
+        <v>0.392200857400894</v>
       </c>
       <c r="H710" t="n">
         <v>131050</v>
@@ -21017,7 +21017,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G712" t="n">
-        <v>0.389989137649536</v>
+        <v>0.389989167451859</v>
       </c>
       <c r="H712" t="n">
         <v>193763</v>
@@ -21046,7 +21046,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G713" t="n">
-        <v>0.392938047647476</v>
+        <v>0.392938077449799</v>
       </c>
       <c r="H713" t="n">
         <v>112600</v>
@@ -21075,7 +21075,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G714" t="n">
-        <v>0.392200797796249</v>
+        <v>0.392200857400894</v>
       </c>
       <c r="H714" t="n">
         <v>68363</v>
@@ -21104,7 +21104,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G715" t="n">
-        <v>0.389989137649536</v>
+        <v>0.389989167451859</v>
       </c>
       <c r="H715" t="n">
         <v>27708</v>
@@ -21133,7 +21133,7 @@
         <v>0.518999993801117</v>
       </c>
       <c r="G716" t="n">
-        <v>0.382616996765137</v>
+        <v>0.382616966962814</v>
       </c>
       <c r="H716" t="n">
         <v>124260</v>
@@ -21336,7 +21336,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G723" t="n">
-        <v>0.371558666229248</v>
+        <v>0.371558725833893</v>
       </c>
       <c r="H723" t="n">
         <v>58285</v>
@@ -21365,7 +21365,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G724" t="n">
-        <v>0.371558666229248</v>
+        <v>0.371558725833893</v>
       </c>
       <c r="H724" t="n">
         <v>137526</v>
@@ -21423,7 +21423,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G726" t="n">
-        <v>0.377456486225128</v>
+        <v>0.377456456422806</v>
       </c>
       <c r="H726" t="n">
         <v>69643</v>
@@ -21452,7 +21452,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G727" t="n">
-        <v>0.377456486225128</v>
+        <v>0.377456456422806</v>
       </c>
       <c r="H727" t="n">
         <v>136460</v>
@@ -21510,7 +21510,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G729" t="n">
-        <v>0.371558666229248</v>
+        <v>0.371558725833893</v>
       </c>
       <c r="H729" t="n">
         <v>158324</v>
@@ -21539,7 +21539,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G730" t="n">
-        <v>0.371558666229248</v>
+        <v>0.371558725833893</v>
       </c>
       <c r="H730" t="n">
         <v>43118</v>
@@ -21626,7 +21626,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G733" t="n">
-        <v>0.371558666229248</v>
+        <v>0.371558725833893</v>
       </c>
       <c r="H733" t="n">
         <v>75452</v>
@@ -21713,7 +21713,7 @@
         <v>0.5</v>
       </c>
       <c r="G736" t="n">
-        <v>0.36860978603363</v>
+        <v>0.368609815835953</v>
       </c>
       <c r="H736" t="n">
         <v>79828</v>
@@ -21742,7 +21742,7 @@
         <v>0.486999988555908</v>
       </c>
       <c r="G737" t="n">
-        <v>0.359025955200195</v>
+        <v>0.359025925397873</v>
       </c>
       <c r="H737" t="n">
         <v>131240</v>
@@ -21800,7 +21800,7 @@
         <v>0.45550000667572</v>
       </c>
       <c r="G739" t="n">
-        <v>0.335803538560867</v>
+        <v>0.335803508758545</v>
       </c>
       <c r="H739" t="n">
         <v>162133</v>
@@ -21829,7 +21829,7 @@
         <v>0.448000013828278</v>
       </c>
       <c r="G740" t="n">
-        <v>0.330274432897568</v>
+        <v>0.330274403095245</v>
       </c>
       <c r="H740" t="n">
         <v>89646</v>
@@ -21945,7 +21945,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>0.351653754711151</v>
+        <v>0.351653724908829</v>
       </c>
       <c r="H744" t="n">
         <v>60680</v>
@@ -22119,7 +22119,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G750" t="n">
-        <v>0.349810719490051</v>
+        <v>0.349810689687729</v>
       </c>
       <c r="H750" t="n">
         <v>125434</v>
@@ -22148,7 +22148,7 @@
         <v>0.48199999332428</v>
       </c>
       <c r="G751" t="n">
-        <v>0.355339884757996</v>
+        <v>0.355339854955673</v>
       </c>
       <c r="H751" t="n">
         <v>151005</v>
@@ -22351,7 +22351,7 @@
         <v>0.478500008583069</v>
       </c>
       <c r="G758" t="n">
-        <v>0.352759599685669</v>
+        <v>0.352759629487991</v>
       </c>
       <c r="H758" t="n">
         <v>37156</v>
@@ -22380,7 +22380,7 @@
         <v>0.491499990224838</v>
       </c>
       <c r="G759" t="n">
-        <v>0.362343460321426</v>
+        <v>0.362343430519104</v>
       </c>
       <c r="H759" t="n">
         <v>332758</v>
@@ -22554,7 +22554,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G765" t="n">
-        <v>0.381879776716232</v>
+        <v>0.381879806518555</v>
       </c>
       <c r="H765" t="n">
         <v>278796</v>
@@ -22583,7 +22583,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G766" t="n">
-        <v>0.392200797796249</v>
+        <v>0.392200857400894</v>
       </c>
       <c r="H766" t="n">
         <v>172766</v>
@@ -22612,7 +22612,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G767" t="n">
-        <v>0.398098647594452</v>
+        <v>0.398098587989807</v>
       </c>
       <c r="H767" t="n">
         <v>110001</v>
@@ -22641,7 +22641,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G768" t="n">
-        <v>0.405470818281174</v>
+        <v>0.405470758676529</v>
       </c>
       <c r="H768" t="n">
         <v>235448</v>
@@ -22670,7 +22670,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G769" t="n">
-        <v>0.405470818281174</v>
+        <v>0.405470758676529</v>
       </c>
       <c r="H769" t="n">
         <v>178881</v>
@@ -22757,7 +22757,7 @@
         <v>0.552999973297119</v>
       </c>
       <c r="G772" t="n">
-        <v>0.407682418823242</v>
+        <v>0.407682478427887</v>
       </c>
       <c r="H772" t="n">
         <v>309056</v>
@@ -22815,7 +22815,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G774" t="n">
-        <v>0.403996288776398</v>
+        <v>0.403996348381042</v>
       </c>
       <c r="H774" t="n">
         <v>74649</v>
@@ -22844,7 +22844,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G775" t="n">
-        <v>0.403996288776398</v>
+        <v>0.403996348381042</v>
       </c>
       <c r="H775" t="n">
         <v>186743</v>
@@ -22873,7 +22873,7 @@
         <v>0.546999990940094</v>
       </c>
       <c r="G776" t="n">
-        <v>0.40325915813446</v>
+        <v>0.403259128332138</v>
       </c>
       <c r="H776" t="n">
         <v>126301</v>
@@ -22902,7 +22902,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G777" t="n">
-        <v>0.405470818281174</v>
+        <v>0.405470758676529</v>
       </c>
       <c r="H777" t="n">
         <v>18425</v>
@@ -22931,7 +22931,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>0.402521878480911</v>
+        <v>0.402521938085556</v>
       </c>
       <c r="H778" t="n">
         <v>154958</v>
@@ -22960,7 +22960,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>0.402521878480911</v>
+        <v>0.402521938085556</v>
       </c>
       <c r="H779" t="n">
         <v>365198</v>
@@ -22989,7 +22989,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G780" t="n">
-        <v>0.392200797796249</v>
+        <v>0.392200857400894</v>
       </c>
       <c r="H780" t="n">
         <v>959746</v>
@@ -23018,7 +23018,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G781" t="n">
-        <v>0.392200797796249</v>
+        <v>0.392200857400894</v>
       </c>
       <c r="H781" t="n">
         <v>230001</v>
@@ -23047,7 +23047,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G782" t="n">
-        <v>0.392938047647476</v>
+        <v>0.392938077449799</v>
       </c>
       <c r="H782" t="n">
         <v>146855</v>
@@ -23105,7 +23105,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G784" t="n">
-        <v>0.392938047647476</v>
+        <v>0.392938077449799</v>
       </c>
       <c r="H784" t="n">
         <v>74868</v>
@@ -23134,7 +23134,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G785" t="n">
-        <v>0.389989137649536</v>
+        <v>0.389989167451859</v>
       </c>
       <c r="H785" t="n">
         <v>145072</v>
@@ -23163,7 +23163,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G786" t="n">
-        <v>0.388514786958694</v>
+        <v>0.38851472735405</v>
       </c>
       <c r="H786" t="n">
         <v>92638</v>
@@ -23192,7 +23192,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G787" t="n">
-        <v>0.389989137649536</v>
+        <v>0.389989167451859</v>
       </c>
       <c r="H787" t="n">
         <v>33929</v>
@@ -23221,7 +23221,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G788" t="n">
-        <v>0.388514786958694</v>
+        <v>0.38851472735405</v>
       </c>
       <c r="H788" t="n">
         <v>323180</v>
@@ -23250,7 +23250,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G789" t="n">
-        <v>0.383354216814041</v>
+        <v>0.383354187011719</v>
       </c>
       <c r="H789" t="n">
         <v>568651</v>
@@ -23279,7 +23279,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G790" t="n">
-        <v>0.383354216814041</v>
+        <v>0.383354187011719</v>
       </c>
       <c r="H790" t="n">
         <v>303345</v>
@@ -23308,7 +23308,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G791" t="n">
-        <v>0.387040317058563</v>
+        <v>0.387040257453918</v>
       </c>
       <c r="H791" t="n">
         <v>84318</v>
@@ -23337,7 +23337,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G792" t="n">
-        <v>0.38777756690979</v>
+        <v>0.387777537107468</v>
       </c>
       <c r="H792" t="n">
         <v>45857</v>
@@ -23366,7 +23366,7 @@
         <v>0.532999992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>0.392938047647476</v>
+        <v>0.392938077449799</v>
       </c>
       <c r="H793" t="n">
         <v>242923</v>
@@ -23395,7 +23395,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G794" t="n">
-        <v>0.393675237894058</v>
+        <v>0.393675267696381</v>
       </c>
       <c r="H794" t="n">
         <v>227492</v>
@@ -23453,7 +23453,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G796" t="n">
-        <v>0.398098647594452</v>
+        <v>0.398098587989807</v>
       </c>
       <c r="H796" t="n">
         <v>158427</v>
@@ -23482,7 +23482,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G797" t="n">
-        <v>0.403996288776398</v>
+        <v>0.403996348381042</v>
       </c>
       <c r="H797" t="n">
         <v>104300</v>
@@ -23511,7 +23511,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G798" t="n">
-        <v>0.405470818281174</v>
+        <v>0.405470758676529</v>
       </c>
       <c r="H798" t="n">
         <v>47514</v>
@@ -23540,7 +23540,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G799" t="n">
-        <v>0.405470818281174</v>
+        <v>0.405470758676529</v>
       </c>
       <c r="H799" t="n">
         <v>39816</v>
@@ -23598,7 +23598,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G801" t="n">
-        <v>0.405470818281174</v>
+        <v>0.405470758676529</v>
       </c>
       <c r="H801" t="n">
         <v>106675</v>
@@ -23627,7 +23627,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G802" t="n">
-        <v>0.404733598232269</v>
+        <v>0.404733628034592</v>
       </c>
       <c r="H802" t="n">
         <v>234040</v>
@@ -23656,7 +23656,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G803" t="n">
-        <v>0.406945258378983</v>
+        <v>0.406945198774338</v>
       </c>
       <c r="H803" t="n">
         <v>61002</v>
@@ -23685,7 +23685,7 @@
         <v>0.546999990940094</v>
       </c>
       <c r="G804" t="n">
-        <v>0.40325915813446</v>
+        <v>0.403259128332138</v>
       </c>
       <c r="H804" t="n">
         <v>21622</v>
@@ -23714,7 +23714,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G805" t="n">
-        <v>0.401047468185425</v>
+        <v>0.401047497987747</v>
       </c>
       <c r="H805" t="n">
         <v>75265</v>
@@ -23830,7 +23830,7 @@
         <v>0.552999973297119</v>
       </c>
       <c r="G809" t="n">
-        <v>0.407682418823242</v>
+        <v>0.407682478427887</v>
       </c>
       <c r="H809" t="n">
         <v>80731</v>
@@ -23859,7 +23859,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G810" t="n">
-        <v>0.403996288776398</v>
+        <v>0.403996348381042</v>
       </c>
       <c r="H810" t="n">
         <v>135376</v>
@@ -23888,7 +23888,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G811" t="n">
-        <v>0.405470818281174</v>
+        <v>0.405470758676529</v>
       </c>
       <c r="H811" t="n">
         <v>54085</v>
@@ -23917,7 +23917,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G812" t="n">
-        <v>0.401047468185425</v>
+        <v>0.401047497987747</v>
       </c>
       <c r="H812" t="n">
         <v>29392</v>
@@ -23975,7 +23975,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G814" t="n">
-        <v>0.404733598232269</v>
+        <v>0.404733628034592</v>
       </c>
       <c r="H814" t="n">
         <v>183609</v>
@@ -24004,7 +24004,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G815" t="n">
-        <v>0.409156888723373</v>
+        <v>0.409156918525696</v>
       </c>
       <c r="H815" t="n">
         <v>186195</v>
@@ -24062,7 +24062,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G817" t="n">
-        <v>0.409156888723373</v>
+        <v>0.409156918525696</v>
       </c>
       <c r="H817" t="n">
         <v>79773</v>
@@ -24091,7 +24091,7 @@
         <v>0.552999973297119</v>
       </c>
       <c r="G818" t="n">
-        <v>0.407682418823242</v>
+        <v>0.407682478427887</v>
       </c>
       <c r="H818" t="n">
         <v>74761</v>
@@ -24120,7 +24120,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G819" t="n">
-        <v>0.408419668674469</v>
+        <v>0.408419698476791</v>
       </c>
       <c r="H819" t="n">
         <v>189195</v>
@@ -24149,7 +24149,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G820" t="n">
-        <v>0.405470818281174</v>
+        <v>0.405470758676529</v>
       </c>
       <c r="H820" t="n">
         <v>69736</v>
@@ -24178,7 +24178,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G821" t="n">
-        <v>0.398098647594452</v>
+        <v>0.398098587989807</v>
       </c>
       <c r="H821" t="n">
         <v>250347</v>
@@ -24207,7 +24207,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G822" t="n">
-        <v>0.395886898040771</v>
+        <v>0.395886927843094</v>
       </c>
       <c r="H822" t="n">
         <v>85457</v>
@@ -24236,7 +24236,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G823" t="n">
-        <v>0.396624177694321</v>
+        <v>0.396624118089676</v>
       </c>
       <c r="H823" t="n">
         <v>79081</v>
@@ -24294,7 +24294,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G825" t="n">
-        <v>0.395149767398834</v>
+        <v>0.395149737596512</v>
       </c>
       <c r="H825" t="n">
         <v>50282</v>
@@ -24323,7 +24323,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G826" t="n">
-        <v>0.393675237894058</v>
+        <v>0.393675267696381</v>
       </c>
       <c r="H826" t="n">
         <v>500235</v>
@@ -24352,7 +24352,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G827" t="n">
-        <v>0.396624177694321</v>
+        <v>0.396624118089676</v>
       </c>
       <c r="H827" t="n">
         <v>117710</v>
@@ -24381,7 +24381,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G828" t="n">
-        <v>0.392200797796249</v>
+        <v>0.392200857400894</v>
       </c>
       <c r="H828" t="n">
         <v>164982</v>
@@ -24439,7 +24439,7 @@
         <v>0.531000018119812</v>
       </c>
       <c r="G830" t="n">
-        <v>0.391463607549667</v>
+        <v>0.39146363735199</v>
       </c>
       <c r="H830" t="n">
         <v>108816</v>
@@ -24497,7 +24497,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G832" t="n">
-        <v>0.388514786958694</v>
+        <v>0.38851472735405</v>
       </c>
       <c r="H832" t="n">
         <v>91963</v>
@@ -24584,7 +24584,7 @@
         <v>0.518999993801117</v>
       </c>
       <c r="G835" t="n">
-        <v>0.382616996765137</v>
+        <v>0.382616966962814</v>
       </c>
       <c r="H835" t="n">
         <v>199196</v>
@@ -24613,7 +24613,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G836" t="n">
-        <v>0.37819367647171</v>
+        <v>0.378193646669388</v>
       </c>
       <c r="H836" t="n">
         <v>108511</v>
@@ -24642,7 +24642,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G837" t="n">
-        <v>0.383354216814041</v>
+        <v>0.383354187011719</v>
       </c>
       <c r="H837" t="n">
         <v>107693</v>
@@ -24700,7 +24700,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>0.375981986522675</v>
+        <v>0.375982016324997</v>
       </c>
       <c r="H839" t="n">
         <v>137873</v>
@@ -24758,7 +24758,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>0.375981986522675</v>
+        <v>0.375982016324997</v>
       </c>
       <c r="H841" t="n">
         <v>102325</v>
@@ -24903,7 +24903,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G846" t="n">
-        <v>0.375981986522675</v>
+        <v>0.375982016324997</v>
       </c>
       <c r="H846" t="n">
         <v>70881</v>
@@ -24990,7 +24990,7 @@
         <v>0.517000019550323</v>
       </c>
       <c r="G849" t="n">
-        <v>0.381142556667328</v>
+        <v>0.38114258646965</v>
       </c>
       <c r="H849" t="n">
         <v>119267</v>
@@ -25048,7 +25048,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G851" t="n">
-        <v>0.375981986522675</v>
+        <v>0.375982016324997</v>
       </c>
       <c r="H851" t="n">
         <v>81543</v>
@@ -25106,7 +25106,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G853" t="n">
-        <v>0.375981986522675</v>
+        <v>0.375982016324997</v>
       </c>
       <c r="H853" t="n">
         <v>126676</v>
@@ -25164,7 +25164,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G855" t="n">
-        <v>0.375981986522675</v>
+        <v>0.375982016324997</v>
       </c>
       <c r="H855" t="n">
         <v>273252</v>
@@ -25251,7 +25251,7 @@
         <v>0.513000011444092</v>
       </c>
       <c r="G858" t="n">
-        <v>0.37819367647171</v>
+        <v>0.378193646669388</v>
       </c>
       <c r="H858" t="n">
         <v>119080</v>
@@ -25280,7 +25280,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G859" t="n">
-        <v>0.377456486225128</v>
+        <v>0.377456456422806</v>
       </c>
       <c r="H859" t="n">
         <v>170414</v>
@@ -25338,7 +25338,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G861" t="n">
-        <v>0.385565906763077</v>
+        <v>0.385565876960754</v>
       </c>
       <c r="H861" t="n">
         <v>89040</v>
@@ -25367,7 +25367,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G862" t="n">
-        <v>0.383354216814041</v>
+        <v>0.383354187011719</v>
       </c>
       <c r="H862" t="n">
         <v>301196</v>
@@ -25396,7 +25396,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>0.383354216814041</v>
+        <v>0.383354187011719</v>
       </c>
       <c r="H863" t="n">
         <v>136523</v>
@@ -25425,7 +25425,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>0.383354216814041</v>
+        <v>0.383354187011719</v>
       </c>
       <c r="H864" t="n">
         <v>158109</v>
@@ -25483,7 +25483,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G866" t="n">
-        <v>0.388514786958694</v>
+        <v>0.38851472735405</v>
       </c>
       <c r="H866" t="n">
         <v>291310</v>
@@ -25599,7 +25599,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G870" t="n">
-        <v>0.392488569021225</v>
+        <v>0.392488539218903</v>
       </c>
       <c r="H870" t="n">
         <v>69495</v>
@@ -25657,7 +25657,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G872" t="n">
-        <v>0.397106051445007</v>
+        <v>0.397106021642685</v>
       </c>
       <c r="H872" t="n">
         <v>119186</v>
@@ -25715,7 +25715,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G874" t="n">
-        <v>0.39402773976326</v>
+        <v>0.394027709960938</v>
       </c>
       <c r="H874" t="n">
         <v>60108</v>
@@ -25744,7 +25744,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G875" t="n">
-        <v>0.392488569021225</v>
+        <v>0.392488539218903</v>
       </c>
       <c r="H875" t="n">
         <v>166450</v>
@@ -25802,7 +25802,7 @@
         <v>0.498499989509583</v>
       </c>
       <c r="G877" t="n">
-        <v>0.383638292551041</v>
+        <v>0.383638322353363</v>
       </c>
       <c r="H877" t="n">
         <v>91948</v>
@@ -25831,7 +25831,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G878" t="n">
-        <v>0.386331856250763</v>
+        <v>0.386331826448441</v>
       </c>
       <c r="H878" t="n">
         <v>186896</v>
@@ -25860,7 +25860,7 @@
         <v>0.494500011205673</v>
       </c>
       <c r="G879" t="n">
-        <v>0.380559951066971</v>
+        <v>0.380560010671616</v>
       </c>
       <c r="H879" t="n">
         <v>80695</v>
@@ -25889,7 +25889,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G880" t="n">
-        <v>0.385562241077423</v>
+        <v>0.385562300682068</v>
       </c>
       <c r="H880" t="n">
         <v>61693</v>
@@ -25918,7 +25918,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G881" t="n">
-        <v>0.380944788455963</v>
+        <v>0.380944758653641</v>
       </c>
       <c r="H881" t="n">
         <v>107184</v>
@@ -25947,7 +25947,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G882" t="n">
-        <v>0.385562241077423</v>
+        <v>0.385562300682068</v>
       </c>
       <c r="H882" t="n">
         <v>57013</v>
@@ -26005,7 +26005,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G884" t="n">
-        <v>0.385562241077423</v>
+        <v>0.385562300682068</v>
       </c>
       <c r="H884" t="n">
         <v>73715</v>
@@ -26063,7 +26063,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G886" t="n">
-        <v>0.382868736982346</v>
+        <v>0.382868707180023</v>
       </c>
       <c r="H886" t="n">
         <v>20568</v>
@@ -26150,7 +26150,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G889" t="n">
-        <v>0.380944788455963</v>
+        <v>0.380944758653641</v>
       </c>
       <c r="H889" t="n">
         <v>76595</v>
@@ -26208,7 +26208,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G891" t="n">
-        <v>0.400184363126755</v>
+        <v>0.400184392929077</v>
       </c>
       <c r="H891" t="n">
         <v>800166</v>
@@ -26237,7 +26237,7 @@
         <v>0.518999993801117</v>
       </c>
       <c r="G892" t="n">
-        <v>0.39941480755806</v>
+        <v>0.399414777755737</v>
       </c>
       <c r="H892" t="n">
         <v>195271</v>
@@ -26266,7 +26266,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G893" t="n">
-        <v>0.397106051445007</v>
+        <v>0.397106021642685</v>
       </c>
       <c r="H893" t="n">
         <v>106240</v>
@@ -26324,7 +26324,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G895" t="n">
-        <v>0.397106051445007</v>
+        <v>0.397106021642685</v>
       </c>
       <c r="H895" t="n">
         <v>63173</v>
@@ -26353,7 +26353,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G896" t="n">
-        <v>0.397106051445007</v>
+        <v>0.397106021642685</v>
       </c>
       <c r="H896" t="n">
         <v>42220</v>
@@ -26382,7 +26382,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G897" t="n">
-        <v>0.39402773976326</v>
+        <v>0.394027709960938</v>
       </c>
       <c r="H897" t="n">
         <v>65212</v>
@@ -26440,7 +26440,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G899" t="n">
-        <v>0.39402773976326</v>
+        <v>0.394027709960938</v>
       </c>
       <c r="H899" t="n">
         <v>276630</v>
@@ -26469,7 +26469,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G900" t="n">
-        <v>0.39402773976326</v>
+        <v>0.394027709960938</v>
       </c>
       <c r="H900" t="n">
         <v>196721</v>
@@ -26498,7 +26498,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G901" t="n">
-        <v>0.39402773976326</v>
+        <v>0.394027709960938</v>
       </c>
       <c r="H901" t="n">
         <v>25787</v>
@@ -26527,7 +26527,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G902" t="n">
-        <v>0.387101471424103</v>
+        <v>0.387101411819458</v>
       </c>
       <c r="H902" t="n">
         <v>585385</v>
@@ -26672,7 +26672,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G907" t="n">
-        <v>0.389410138130188</v>
+        <v>0.38941016793251</v>
       </c>
       <c r="H907" t="n">
         <v>50877</v>
@@ -26701,7 +26701,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G908" t="n">
-        <v>0.392488569021225</v>
+        <v>0.392488539218903</v>
       </c>
       <c r="H908" t="n">
         <v>25745</v>
@@ -26759,7 +26759,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G910" t="n">
-        <v>0.392488569021225</v>
+        <v>0.392488539218903</v>
       </c>
       <c r="H910" t="n">
         <v>150028</v>
@@ -26817,7 +26817,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G912" t="n">
-        <v>0.392488569021225</v>
+        <v>0.392488539218903</v>
       </c>
       <c r="H912" t="n">
         <v>45277</v>
@@ -26904,7 +26904,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G915" t="n">
-        <v>0.386331856250763</v>
+        <v>0.386331826448441</v>
       </c>
       <c r="H915" t="n">
         <v>56691</v>
@@ -26962,7 +26962,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G917" t="n">
-        <v>0.387101471424103</v>
+        <v>0.387101411819458</v>
       </c>
       <c r="H917" t="n">
         <v>129448</v>
@@ -26991,7 +26991,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G918" t="n">
-        <v>0.380944788455963</v>
+        <v>0.380944758653641</v>
       </c>
       <c r="H918" t="n">
         <v>258913</v>
@@ -27020,7 +27020,7 @@
         <v>0.503000020980835</v>
       </c>
       <c r="G919" t="n">
-        <v>0.387101471424103</v>
+        <v>0.387101411819458</v>
       </c>
       <c r="H919" t="n">
         <v>137165</v>
@@ -27049,7 +27049,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G920" t="n">
-        <v>0.386331856250763</v>
+        <v>0.386331826448441</v>
       </c>
       <c r="H920" t="n">
         <v>50133</v>
@@ -27107,7 +27107,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G922" t="n">
-        <v>0.374018520116806</v>
+        <v>0.374018490314484</v>
       </c>
       <c r="H922" t="n">
         <v>51960</v>
@@ -27223,7 +27223,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G926" t="n">
-        <v>0.385562241077423</v>
+        <v>0.385562300682068</v>
       </c>
       <c r="H926" t="n">
         <v>16873</v>
@@ -27281,7 +27281,7 @@
         <v>0.494500011205673</v>
       </c>
       <c r="G928" t="n">
-        <v>0.380559951066971</v>
+        <v>0.380560010671616</v>
       </c>
       <c r="H928" t="n">
         <v>21200</v>
@@ -27310,7 +27310,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G929" t="n">
-        <v>0.386331856250763</v>
+        <v>0.386331826448441</v>
       </c>
       <c r="H929" t="n">
         <v>267463</v>
@@ -27368,7 +27368,7 @@
         <v>0.498499989509583</v>
       </c>
       <c r="G931" t="n">
-        <v>0.383638292551041</v>
+        <v>0.383638322353363</v>
       </c>
       <c r="H931" t="n">
         <v>34886</v>
@@ -27397,7 +27397,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G932" t="n">
-        <v>0.382868736982346</v>
+        <v>0.382868707180023</v>
       </c>
       <c r="H932" t="n">
         <v>92156</v>
@@ -27426,7 +27426,7 @@
         <v>0.500999987125397</v>
       </c>
       <c r="G933" t="n">
-        <v>0.385562241077423</v>
+        <v>0.385562300682068</v>
       </c>
       <c r="H933" t="n">
         <v>27013</v>
@@ -27455,7 +27455,7 @@
         <v>0.494500011205673</v>
       </c>
       <c r="G934" t="n">
-        <v>0.380559951066971</v>
+        <v>0.380560010671616</v>
       </c>
       <c r="H934" t="n">
         <v>303456</v>
@@ -27484,7 +27484,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G935" t="n">
-        <v>0.380944788455963</v>
+        <v>0.380944758653641</v>
       </c>
       <c r="H935" t="n">
         <v>128803</v>
@@ -27513,7 +27513,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G936" t="n">
-        <v>0.380944788455963</v>
+        <v>0.380944758653641</v>
       </c>
       <c r="H936" t="n">
         <v>52540</v>
@@ -27629,7 +27629,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G940" t="n">
-        <v>0.389410138130188</v>
+        <v>0.38941016793251</v>
       </c>
       <c r="H940" t="n">
         <v>291816</v>
@@ -27658,7 +27658,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G941" t="n">
-        <v>0.39402773976326</v>
+        <v>0.394027709960938</v>
       </c>
       <c r="H941" t="n">
         <v>209630</v>
@@ -27687,7 +27687,7 @@
         <v>0.518999993801117</v>
       </c>
       <c r="G942" t="n">
-        <v>0.39941480755806</v>
+        <v>0.399414777755737</v>
       </c>
       <c r="H942" t="n">
         <v>495221</v>
@@ -27745,7 +27745,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G944" t="n">
-        <v>0.414806485176086</v>
+        <v>0.414806514978409</v>
       </c>
       <c r="H944" t="n">
         <v>326207</v>
@@ -27774,7 +27774,7 @@
         <v>0.52700001001358</v>
       </c>
       <c r="G945" t="n">
-        <v>0.405571520328522</v>
+        <v>0.405571490526199</v>
       </c>
       <c r="H945" t="n">
         <v>377311</v>
@@ -27803,7 +27803,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G946" t="n">
-        <v>0.413267314434052</v>
+        <v>0.413267344236374</v>
       </c>
       <c r="H946" t="n">
         <v>123367</v>
@@ -27832,7 +27832,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G947" t="n">
-        <v>0.407110661268234</v>
+        <v>0.407110631465912</v>
       </c>
       <c r="H947" t="n">
         <v>102414</v>
@@ -27861,7 +27861,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G948" t="n">
-        <v>0.409419387578964</v>
+        <v>0.409419447183609</v>
       </c>
       <c r="H948" t="n">
         <v>170959</v>
@@ -27890,7 +27890,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G949" t="n">
-        <v>0.413267314434052</v>
+        <v>0.413267344236374</v>
       </c>
       <c r="H949" t="n">
         <v>74521</v>
@@ -27919,7 +27919,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G950" t="n">
-        <v>0.414036929607391</v>
+        <v>0.414036899805069</v>
       </c>
       <c r="H950" t="n">
         <v>79926</v>
@@ -27948,7 +27948,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G951" t="n">
-        <v>0.414806485176086</v>
+        <v>0.414806514978409</v>
       </c>
       <c r="H951" t="n">
         <v>27911</v>
@@ -28006,7 +28006,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G953" t="n">
-        <v>0.414806485176086</v>
+        <v>0.414806514978409</v>
       </c>
       <c r="H953" t="n">
         <v>85795</v>
@@ -28035,7 +28035,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G954" t="n">
-        <v>0.409419387578964</v>
+        <v>0.409419447183609</v>
       </c>
       <c r="H954" t="n">
         <v>35645</v>
@@ -28064,7 +28064,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G955" t="n">
-        <v>0.40249314904213</v>
+        <v>0.402493178844452</v>
       </c>
       <c r="H955" t="n">
         <v>220795</v>
@@ -28093,7 +28093,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G956" t="n">
-        <v>0.407110661268234</v>
+        <v>0.407110631465912</v>
       </c>
       <c r="H956" t="n">
         <v>33842</v>
@@ -28122,7 +28122,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G957" t="n">
-        <v>0.409419387578964</v>
+        <v>0.409419447183609</v>
       </c>
       <c r="H957" t="n">
         <v>54589</v>
@@ -28238,7 +28238,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G961" t="n">
-        <v>0.414036929607391</v>
+        <v>0.414036899805069</v>
       </c>
       <c r="H961" t="n">
         <v>70662</v>
@@ -28267,7 +28267,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G962" t="n">
-        <v>0.414036929607391</v>
+        <v>0.414036899805069</v>
       </c>
       <c r="H962" t="n">
         <v>105591</v>
@@ -28296,7 +28296,7 @@
         <v>0.538999974727631</v>
       </c>
       <c r="G963" t="n">
-        <v>0.414806485176086</v>
+        <v>0.414806514978409</v>
       </c>
       <c r="H963" t="n">
         <v>61228</v>
@@ -28325,7 +28325,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G964" t="n">
-        <v>0.414036929607391</v>
+        <v>0.414036899805069</v>
       </c>
       <c r="H964" t="n">
         <v>183961</v>
@@ -28354,7 +28354,7 @@
         <v>0.537000000476837</v>
       </c>
       <c r="G965" t="n">
-        <v>0.413267314434052</v>
+        <v>0.413267344236374</v>
       </c>
       <c r="H965" t="n">
         <v>263283</v>
@@ -28383,7 +28383,7 @@
         <v>0.542999982833862</v>
       </c>
       <c r="G966" t="n">
-        <v>0.417884886264801</v>
+        <v>0.417884856462479</v>
       </c>
       <c r="H966" t="n">
         <v>97652</v>
@@ -28441,7 +28441,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G968" t="n">
-        <v>0.409419387578964</v>
+        <v>0.409419447183609</v>
       </c>
       <c r="H968" t="n">
         <v>73995</v>
@@ -28528,7 +28528,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G971" t="n">
-        <v>0.411728203296661</v>
+        <v>0.411728233098984</v>
       </c>
       <c r="H971" t="n">
         <v>172848</v>
@@ -28557,7 +28557,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G972" t="n">
-        <v>0.414036929607391</v>
+        <v>0.414036899805069</v>
       </c>
       <c r="H972" t="n">
         <v>194906</v>
@@ -28615,7 +28615,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G974" t="n">
-        <v>0.438663691282272</v>
+        <v>0.43866366147995</v>
       </c>
       <c r="H974" t="n">
         <v>972286</v>
@@ -28644,7 +28644,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G975" t="n">
-        <v>0.446359515190125</v>
+        <v>0.446359544992447</v>
       </c>
       <c r="H975" t="n">
         <v>1593927</v>
@@ -28673,7 +28673,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G976" t="n">
-        <v>0.452516138553619</v>
+        <v>0.452516198158264</v>
       </c>
       <c r="H976" t="n">
         <v>726632</v>
@@ -28702,7 +28702,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G977" t="n">
-        <v>0.455594509840012</v>
+        <v>0.455594539642334</v>
       </c>
       <c r="H977" t="n">
         <v>130814</v>
@@ -28731,7 +28731,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G978" t="n">
-        <v>0.457903325557709</v>
+        <v>0.457903295755386</v>
       </c>
       <c r="H978" t="n">
         <v>299115</v>
@@ -28789,7 +28789,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G980" t="n">
-        <v>0.460212081670761</v>
+        <v>0.460212051868439</v>
       </c>
       <c r="H980" t="n">
         <v>98843</v>
@@ -28818,7 +28818,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G981" t="n">
-        <v>0.460212081670761</v>
+        <v>0.460212051868439</v>
       </c>
       <c r="H981" t="n">
         <v>146019</v>
@@ -28847,7 +28847,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G982" t="n">
-        <v>0.457133680582047</v>
+        <v>0.457133740186691</v>
       </c>
       <c r="H982" t="n">
         <v>196512</v>
@@ -28876,7 +28876,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G983" t="n">
-        <v>0.457133680582047</v>
+        <v>0.457133740186691</v>
       </c>
       <c r="H983" t="n">
         <v>95496</v>
@@ -28963,7 +28963,7 @@
         <v>0.587000012397766</v>
       </c>
       <c r="G986" t="n">
-        <v>0.451746612787247</v>
+        <v>0.451746672391891</v>
       </c>
       <c r="H986" t="n">
         <v>246517</v>
@@ -29079,7 +29079,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G990" t="n">
-        <v>0.460212081670761</v>
+        <v>0.460212051868439</v>
       </c>
       <c r="H990" t="n">
         <v>131109</v>
@@ -29108,7 +29108,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G991" t="n">
-        <v>0.460212081670761</v>
+        <v>0.460212051868439</v>
       </c>
       <c r="H991" t="n">
         <v>52186</v>
@@ -29137,7 +29137,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G992" t="n">
-        <v>0.47329506278038</v>
+        <v>0.473295003175735</v>
       </c>
       <c r="H992" t="n">
         <v>652098</v>
@@ -29166,7 +29166,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G993" t="n">
-        <v>0.489456295967102</v>
+        <v>0.489456236362457</v>
       </c>
       <c r="H993" t="n">
         <v>692698</v>
@@ -29195,7 +29195,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G994" t="n">
-        <v>0.490995466709137</v>
+        <v>0.490995496511459</v>
       </c>
       <c r="H994" t="n">
         <v>1240217</v>
@@ -29224,7 +29224,7 @@
         <v>0.647000014781952</v>
       </c>
       <c r="G995" t="n">
-        <v>0.497921705245972</v>
+        <v>0.497921794652939</v>
       </c>
       <c r="H995" t="n">
         <v>849094</v>
@@ -29282,7 +29282,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G997" t="n">
-        <v>0.511004626750946</v>
+        <v>0.511004745960236</v>
       </c>
       <c r="H997" t="n">
         <v>440471</v>
@@ -29311,7 +29311,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G998" t="n">
-        <v>0.500230431556702</v>
+        <v>0.500230491161346</v>
       </c>
       <c r="H998" t="n">
         <v>342548</v>
@@ -29340,7 +29340,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G999" t="n">
-        <v>0.492534577846527</v>
+        <v>0.492534637451172</v>
       </c>
       <c r="H999" t="n">
         <v>185083</v>
@@ -29369,7 +29369,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.492534577846527</v>
+        <v>0.492534637451172</v>
       </c>
       <c r="H1000" t="n">
         <v>207265</v>
@@ -29398,7 +29398,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.494073897600174</v>
+        <v>0.494073837995529</v>
       </c>
       <c r="H1001" t="n">
         <v>136291</v>
@@ -29427,7 +29427,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.499460846185684</v>
+        <v>0.499460875988007</v>
       </c>
       <c r="H1002" t="n">
         <v>28614</v>
@@ -29456,7 +29456,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.511004626750946</v>
+        <v>0.511004745960236</v>
       </c>
       <c r="H1003" t="n">
         <v>354716</v>
@@ -29485,7 +29485,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.53178346157074</v>
+        <v>0.531783521175385</v>
       </c>
       <c r="H1004" t="n">
         <v>901980</v>
@@ -29514,7 +29514,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1005" t="n">
-        <v>0.531013965606689</v>
+        <v>0.531013906002045</v>
       </c>
       <c r="H1005" t="n">
         <v>1198913</v>
@@ -29572,7 +29572,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G1007" t="n">
-        <v>0.533322691917419</v>
+        <v>0.533322632312775</v>
       </c>
       <c r="H1007" t="n">
         <v>339879</v>
@@ -29601,7 +29601,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.546405553817749</v>
+        <v>0.546405613422394</v>
       </c>
       <c r="H1008" t="n">
         <v>1165072</v>
@@ -29630,7 +29630,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1009" t="n">
-        <v>0.53717052936554</v>
+        <v>0.537170648574829</v>
       </c>
       <c r="H1009" t="n">
         <v>768539</v>
@@ -29659,7 +29659,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1010" t="n">
-        <v>0.53717052936554</v>
+        <v>0.537170648574829</v>
       </c>
       <c r="H1010" t="n">
         <v>199769</v>
@@ -29717,7 +29717,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.531013965606689</v>
+        <v>0.531013906002045</v>
       </c>
       <c r="H1012" t="n">
         <v>639278</v>
@@ -29746,7 +29746,7 @@
         <v>0.686999976634979</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.528705179691315</v>
+        <v>0.52870512008667</v>
       </c>
       <c r="H1013" t="n">
         <v>495706</v>
@@ -29775,7 +29775,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.530244290828705</v>
+        <v>0.530244410037994</v>
       </c>
       <c r="H1014" t="n">
         <v>292366</v>
@@ -29833,7 +29833,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.566414892673492</v>
+        <v>0.566414833068848</v>
       </c>
       <c r="H1016" t="n">
         <v>786522</v>
@@ -29949,7 +29949,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.584884881973267</v>
+        <v>0.584884822368622</v>
       </c>
       <c r="H1020" t="n">
         <v>692423</v>
@@ -30036,7 +30036,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.587963163852692</v>
+        <v>0.587963223457336</v>
       </c>
       <c r="H1023" t="n">
         <v>596973</v>
@@ -30123,7 +30123,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.567954003810883</v>
+        <v>0.567953944206238</v>
       </c>
       <c r="H1026" t="n">
         <v>316818</v>
@@ -30152,7 +30152,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.564875662326813</v>
+        <v>0.564875721931458</v>
       </c>
       <c r="H1027" t="n">
         <v>506699</v>
@@ -30181,7 +30181,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.569493114948273</v>
+        <v>0.569493234157562</v>
       </c>
       <c r="H1028" t="n">
         <v>410062</v>
@@ -30210,7 +30210,7 @@
         <v>0.757000029087067</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.582576155662537</v>
+        <v>0.582576096057892</v>
       </c>
       <c r="H1029" t="n">
         <v>387830</v>
@@ -30239,7 +30239,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.584884881973267</v>
+        <v>0.584884822368622</v>
       </c>
       <c r="H1030" t="n">
         <v>713666</v>
@@ -30326,7 +30326,7 @@
         <v>0.736999988555908</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.567184388637543</v>
+        <v>0.567184448242188</v>
       </c>
       <c r="H1033" t="n">
         <v>584802</v>
@@ -30442,7 +30442,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1037" t="n">
-        <v>0.568723618984222</v>
+        <v>0.568723738193512</v>
       </c>
       <c r="H1037" t="n">
         <v>171417</v>
@@ -30558,7 +30558,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1041" t="n">
-        <v>0.583345711231232</v>
+        <v>0.583345770835876</v>
       </c>
       <c r="H1041" t="n">
         <v>116241</v>
@@ -30616,7 +30616,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.571801900863647</v>
+        <v>0.571801841259003</v>
       </c>
       <c r="H1043" t="n">
         <v>185324</v>
@@ -30732,7 +30732,7 @@
         <v>0.802999973297119</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.61797708272934</v>
+        <v>0.617977023124695</v>
       </c>
       <c r="H1047" t="n">
         <v>2113453</v>
@@ -30848,7 +30848,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1051" t="n">
-        <v>0.654147565364838</v>
+        <v>0.654147624969482</v>
       </c>
       <c r="H1051" t="n">
         <v>916572</v>
@@ -30877,7 +30877,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.632599234580994</v>
+        <v>0.632599174976349</v>
       </c>
       <c r="H1052" t="n">
         <v>901206</v>
@@ -30993,7 +30993,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.51716136932373</v>
+        <v>0.517161428928375</v>
       </c>
       <c r="H1056" t="n">
         <v>634414</v>
@@ -31022,7 +31022,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.51947009563446</v>
+        <v>0.519470155239105</v>
       </c>
       <c r="H1057" t="n">
         <v>448600</v>
@@ -31051,7 +31051,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.495612949132919</v>
+        <v>0.495613008737564</v>
       </c>
       <c r="H1058" t="n">
         <v>723308</v>
@@ -31109,7 +31109,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.469447106122971</v>
+        <v>0.469447076320648</v>
       </c>
       <c r="H1060" t="n">
         <v>738531</v>
@@ -31196,7 +31196,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.400184363126755</v>
+        <v>0.400184392929077</v>
       </c>
       <c r="H1063" t="n">
         <v>595224</v>
@@ -31283,7 +31283,7 @@
         <v>0.40149998664856</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.30898854136467</v>
+        <v>0.308988511562347</v>
       </c>
       <c r="H1066" t="n">
         <v>366072</v>
@@ -31312,7 +31312,7 @@
         <v>0.432500004768372</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.332845687866211</v>
+        <v>0.332845658063889</v>
       </c>
       <c r="H1067" t="n">
         <v>1049735</v>
@@ -31399,7 +31399,7 @@
         <v>0.358999997377396</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.276281148195267</v>
+        <v>0.276281118392944</v>
       </c>
       <c r="H1070" t="n">
         <v>259869</v>
@@ -31457,7 +31457,7 @@
         <v>0.378500014543533</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.291288077831268</v>
+        <v>0.291288048028946</v>
       </c>
       <c r="H1072" t="n">
         <v>229150</v>
@@ -31515,7 +31515,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.328612893819809</v>
+        <v>0.328612953424454</v>
       </c>
       <c r="H1074" t="n">
         <v>447440</v>
@@ -31544,7 +31544,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.343235045671463</v>
+        <v>0.343235075473785</v>
       </c>
       <c r="H1075" t="n">
         <v>484924</v>
@@ -31573,7 +31573,7 @@
         <v>0.462500005960464</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.355933219194412</v>
+        <v>0.355933248996735</v>
       </c>
       <c r="H1076" t="n">
         <v>163295</v>
@@ -31602,7 +31602,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.343235045671463</v>
+        <v>0.343235075473785</v>
       </c>
       <c r="H1077" t="n">
         <v>155076</v>
@@ -31660,7 +31660,7 @@
         <v>0.46450001001358</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.35747241973877</v>
+        <v>0.357472389936447</v>
       </c>
       <c r="H1079" t="n">
         <v>138258</v>
@@ -31718,7 +31718,7 @@
         <v>0.470999985933304</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.362474709749222</v>
+        <v>0.362474679946899</v>
       </c>
       <c r="H1081" t="n">
         <v>319744</v>
@@ -31776,7 +31776,7 @@
         <v>0.477999985218048</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.367861807346344</v>
+        <v>0.367861777544022</v>
       </c>
       <c r="H1083" t="n">
         <v>131080</v>
@@ -31805,7 +31805,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.369401007890701</v>
+        <v>0.369400978088379</v>
       </c>
       <c r="H1084" t="n">
         <v>263057</v>
@@ -31834,7 +31834,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.369401007890701</v>
+        <v>0.369400978088379</v>
       </c>
       <c r="H1085" t="n">
         <v>164384</v>
@@ -31863,7 +31863,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.357857197523117</v>
+        <v>0.357857227325439</v>
       </c>
       <c r="H1086" t="n">
         <v>638018</v>
@@ -31921,7 +31921,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.346313416957855</v>
+        <v>0.346313387155533</v>
       </c>
       <c r="H1088" t="n">
         <v>286674</v>
@@ -31950,7 +31950,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.336308807134628</v>
+        <v>0.336308836936951</v>
       </c>
       <c r="H1089" t="n">
         <v>172954</v>
@@ -32008,7 +32008,7 @@
         <v>0.433999985456467</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.334000021219254</v>
+        <v>0.334000080823898</v>
       </c>
       <c r="H1091" t="n">
         <v>71027</v>
@@ -32066,7 +32066,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.30937334895134</v>
+        <v>0.309373319149017</v>
       </c>
       <c r="H1093" t="n">
         <v>427435</v>
@@ -32153,7 +32153,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.326304167509079</v>
+        <v>0.326304197311401</v>
       </c>
       <c r="H1096" t="n">
         <v>524095</v>
@@ -32211,7 +32211,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.335539221763611</v>
+        <v>0.335539162158966</v>
       </c>
       <c r="H1098" t="n">
         <v>360417</v>
@@ -32269,7 +32269,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.327843368053436</v>
+        <v>0.327843338251114</v>
       </c>
       <c r="H1100" t="n">
         <v>509499</v>
@@ -32298,7 +32298,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.326304167509079</v>
+        <v>0.326304197311401</v>
       </c>
       <c r="H1101" t="n">
         <v>211911</v>
@@ -32356,7 +32356,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.326304167509079</v>
+        <v>0.326304197311401</v>
       </c>
       <c r="H1103" t="n">
         <v>99262</v>
@@ -32443,7 +32443,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.330152124166489</v>
+        <v>0.330152094364166</v>
       </c>
       <c r="H1106" t="n">
         <v>107880</v>
@@ -32472,7 +32472,7 @@
         <v>0.418000012636185</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.321686655282974</v>
+        <v>0.321686685085297</v>
       </c>
       <c r="H1107" t="n">
         <v>249291</v>
@@ -32501,7 +32501,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.310142874717712</v>
+        <v>0.310142904520035</v>
       </c>
       <c r="H1108" t="n">
         <v>106550</v>
@@ -32588,7 +32588,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.312451630830765</v>
+        <v>0.312451660633087</v>
       </c>
       <c r="H1111" t="n">
         <v>353567</v>
@@ -32617,7 +32617,7 @@
         <v>0.400000005960464</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.307834178209305</v>
+        <v>0.307834148406982</v>
       </c>
       <c r="H1112" t="n">
         <v>273834</v>
@@ -32646,7 +32646,7 @@
         <v>0.402999997138977</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.310142874717712</v>
+        <v>0.310142904520035</v>
       </c>
       <c r="H1113" t="n">
         <v>63654</v>
@@ -32675,7 +32675,7 @@
         <v>0.412000000476837</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.31706914305687</v>
+        <v>0.317069172859192</v>
       </c>
       <c r="H1114" t="n">
         <v>64710</v>
@@ -32704,7 +32704,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.325534671545029</v>
+        <v>0.325534611940384</v>
       </c>
       <c r="H1115" t="n">
         <v>141932</v>
@@ -32762,7 +32762,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.335539221763611</v>
+        <v>0.335539162158966</v>
       </c>
       <c r="H1117" t="n">
         <v>311982</v>
@@ -32791,7 +32791,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.335539221763611</v>
+        <v>0.335539162158966</v>
       </c>
       <c r="H1118" t="n">
         <v>224259</v>
@@ -32849,7 +32849,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.337078392505646</v>
+        <v>0.337078362703323</v>
       </c>
       <c r="H1120" t="n">
         <v>132594</v>
@@ -32878,7 +32878,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.339387178421021</v>
+        <v>0.339387148618698</v>
       </c>
       <c r="H1121" t="n">
         <v>245932</v>
@@ -32936,7 +32936,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.365553021430969</v>
+        <v>0.365553051233292</v>
       </c>
       <c r="H1123" t="n">
         <v>511540</v>
@@ -32965,7 +32965,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.365553021430969</v>
+        <v>0.365553051233292</v>
       </c>
       <c r="H1124" t="n">
         <v>903213</v>
@@ -33052,7 +33052,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.338617563247681</v>
+        <v>0.338617593050003</v>
       </c>
       <c r="H1127" t="n">
         <v>474125</v>
@@ -33081,7 +33081,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G1128" t="n">
-        <v>0.316299617290497</v>
+        <v>0.316299587488174</v>
       </c>
       <c r="H1128" t="n">
         <v>300039</v>
@@ -33110,7 +33110,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.325534671545029</v>
+        <v>0.325534611940384</v>
       </c>
       <c r="H1129" t="n">
         <v>246953</v>
@@ -33139,7 +33139,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.328612893819809</v>
+        <v>0.328612953424454</v>
       </c>
       <c r="H1130" t="n">
         <v>107931</v>
@@ -33168,7 +33168,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.335539221763611</v>
+        <v>0.335539162158966</v>
       </c>
       <c r="H1131" t="n">
         <v>213890</v>
@@ -33197,7 +33197,7 @@
         <v>0.441000014543533</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.339387178421021</v>
+        <v>0.339387148618698</v>
       </c>
       <c r="H1132" t="n">
         <v>59283</v>
@@ -33226,7 +33226,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.338617563247681</v>
+        <v>0.338617593050003</v>
       </c>
       <c r="H1133" t="n">
         <v>79924</v>
@@ -33255,7 +33255,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.336308807134628</v>
+        <v>0.336308836936951</v>
       </c>
       <c r="H1134" t="n">
         <v>84681</v>
@@ -33284,7 +33284,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.338617563247681</v>
+        <v>0.338617593050003</v>
       </c>
       <c r="H1135" t="n">
         <v>40284</v>
@@ -33371,7 +33371,7 @@
         <v>0.435999989509583</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.335539221763611</v>
+        <v>0.335539162158966</v>
       </c>
       <c r="H1138" t="n">
         <v>107383</v>
@@ -33400,7 +33400,7 @@
         <v>0.437000006437302</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.336308807134628</v>
+        <v>0.336308836936951</v>
       </c>
       <c r="H1139" t="n">
         <v>71273</v>
@@ -33429,7 +33429,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.337078392505646</v>
+        <v>0.337078362703323</v>
       </c>
       <c r="H1140" t="n">
         <v>62676</v>
@@ -33458,7 +33458,7 @@
         <v>0.446000009775162</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.343235045671463</v>
+        <v>0.343235075473785</v>
       </c>
       <c r="H1141" t="n">
         <v>164145</v>
@@ -33516,7 +33516,7 @@
         <v>0.444000005722046</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.341695934534073</v>
+        <v>0.34169590473175</v>
       </c>
       <c r="H1143" t="n">
         <v>84599</v>
@@ -33545,7 +33545,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.337078392505646</v>
+        <v>0.337078362703323</v>
       </c>
       <c r="H1144" t="n">
         <v>66250</v>
@@ -33574,7 +33574,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.338617563247681</v>
+        <v>0.338617593050003</v>
       </c>
       <c r="H1145" t="n">
         <v>60488</v>
@@ -33603,7 +33603,7 @@
         <v>0.437999993562698</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.337078392505646</v>
+        <v>0.337078362703323</v>
       </c>
       <c r="H1146" t="n">
         <v>79605</v>
@@ -33632,7 +33632,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.334769636392593</v>
+        <v>0.334769606590271</v>
       </c>
       <c r="H1147" t="n">
         <v>37115</v>
@@ -33661,7 +33661,7 @@
         <v>0.435000002384186</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.334769636392593</v>
+        <v>0.334769606590271</v>
       </c>
       <c r="H1148" t="n">
         <v>126526</v>
@@ -33719,7 +33719,7 @@
         <v>0.425999999046326</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.327843368053436</v>
+        <v>0.327843338251114</v>
       </c>
       <c r="H1150" t="n">
         <v>55878</v>
@@ -33748,7 +33748,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.331691324710846</v>
+        <v>0.331691294908524</v>
       </c>
       <c r="H1151" t="n">
         <v>53708</v>
@@ -33777,7 +33777,7 @@
         <v>0.430999994277954</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.331691324710846</v>
+        <v>0.331691294908524</v>
       </c>
       <c r="H1152" t="n">
         <v>88857</v>
@@ -33835,7 +33835,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.327073782682419</v>
+        <v>0.327073812484741</v>
       </c>
       <c r="H1154" t="n">
         <v>81494</v>
@@ -33893,7 +33893,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.327073782682419</v>
+        <v>0.327073812484741</v>
       </c>
       <c r="H1156" t="n">
         <v>152200</v>
@@ -34009,7 +34009,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.320917099714279</v>
+        <v>0.320917069911957</v>
       </c>
       <c r="H1160" t="n">
         <v>216486</v>
@@ -34038,7 +34038,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.35400927066803</v>
+        <v>0.354009240865707</v>
       </c>
       <c r="H1161" t="n">
         <v>1389648</v>
@@ -34096,7 +34096,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.342465490102768</v>
+        <v>0.342465460300446</v>
       </c>
       <c r="H1163" t="n">
         <v>515153</v>
@@ -34125,7 +34125,7 @@
         <v>0.444999992847443</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.342465490102768</v>
+        <v>0.342465460300446</v>
       </c>
       <c r="H1164" t="n">
         <v>1298714</v>
@@ -34154,7 +34154,7 @@
         <v>0.451999992132187</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.34785258769989</v>
+        <v>0.347852557897568</v>
       </c>
       <c r="H1165" t="n">
         <v>464726</v>
@@ -34183,7 +34183,7 @@
         <v>0.465000003576279</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.357857197523117</v>
+        <v>0.357857227325439</v>
       </c>
       <c r="H1166" t="n">
         <v>377669</v>
@@ -34270,7 +34270,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.397106051445007</v>
+        <v>0.397106021642685</v>
       </c>
       <c r="H1169" t="n">
         <v>326273</v>
@@ -34299,7 +34299,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.406341135501862</v>
+        <v>0.406341075897217</v>
       </c>
       <c r="H1170" t="n">
         <v>945712</v>
@@ -34357,7 +34357,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.418654441833496</v>
+        <v>0.418654471635818</v>
       </c>
       <c r="H1172" t="n">
         <v>390033</v>
@@ -34386,7 +34386,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.424811154603958</v>
+        <v>0.424811094999313</v>
       </c>
       <c r="H1173" t="n">
         <v>246415</v>
@@ -34415,7 +34415,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.418654441833496</v>
+        <v>0.418654471635818</v>
       </c>
       <c r="H1174" t="n">
         <v>204089</v>
@@ -34473,7 +34473,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.461751282215118</v>
+        <v>0.461751252412796</v>
       </c>
       <c r="H1176" t="n">
         <v>1566908</v>
@@ -34502,7 +34502,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.535631418228149</v>
+        <v>0.535631477832794</v>
       </c>
       <c r="H1177" t="n">
         <v>3333804</v>
@@ -34531,7 +34531,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.53717052936554</v>
+        <v>0.537170648574829</v>
       </c>
       <c r="H1178" t="n">
         <v>4602323</v>
@@ -34560,7 +34560,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.531013965606689</v>
+        <v>0.531013906002045</v>
       </c>
       <c r="H1179" t="n">
         <v>1670447</v>
@@ -34589,7 +34589,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.504848003387451</v>
+        <v>0.504848062992096</v>
       </c>
       <c r="H1180" t="n">
         <v>783444</v>
@@ -34618,7 +34618,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.498691320419312</v>
+        <v>0.498691290616989</v>
       </c>
       <c r="H1181" t="n">
         <v>309471</v>
@@ -34647,7 +34647,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.495612949132919</v>
+        <v>0.495613008737564</v>
       </c>
       <c r="H1182" t="n">
         <v>508291</v>
@@ -34705,7 +34705,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.504848003387451</v>
+        <v>0.504848062992096</v>
       </c>
       <c r="H1184" t="n">
         <v>436060</v>
@@ -34734,7 +34734,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.497152179479599</v>
+        <v>0.497152209281921</v>
       </c>
       <c r="H1185" t="n">
         <v>572612</v>
@@ -34763,7 +34763,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.48483881354332</v>
+        <v>0.484838783740997</v>
       </c>
       <c r="H1186" t="n">
         <v>156833</v>
@@ -34792,7 +34792,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.478682100772858</v>
+        <v>0.478682070970535</v>
       </c>
       <c r="H1187" t="n">
         <v>89207</v>
@@ -34821,7 +34821,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.478682100772858</v>
+        <v>0.478682070970535</v>
       </c>
       <c r="H1188" t="n">
         <v>185337</v>
@@ -34850,7 +34850,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.472525417804718</v>
+        <v>0.472525507211685</v>
       </c>
       <c r="H1189" t="n">
         <v>244726</v>
@@ -34879,7 +34879,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.480221301317215</v>
+        <v>0.480221331119537</v>
       </c>
       <c r="H1190" t="n">
         <v>675560</v>
@@ -34908,7 +34908,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.490995466709137</v>
+        <v>0.490995496511459</v>
       </c>
       <c r="H1191" t="n">
         <v>536268</v>
@@ -34937,7 +34937,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.514083027839661</v>
+        <v>0.514082968235016</v>
       </c>
       <c r="H1192" t="n">
         <v>1177681</v>
@@ -34966,7 +34966,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.501769721508026</v>
+        <v>0.501769661903381</v>
       </c>
       <c r="H1193" t="n">
         <v>917715</v>
@@ -34995,7 +34995,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.487917065620422</v>
+        <v>0.487917095422745</v>
       </c>
       <c r="H1194" t="n">
         <v>117042</v>
@@ -35024,7 +35024,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.477142870426178</v>
+        <v>0.4771429002285</v>
       </c>
       <c r="H1195" t="n">
         <v>349410</v>
@@ -35053,7 +35053,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.470986247062683</v>
+        <v>0.470986276865005</v>
       </c>
       <c r="H1196" t="n">
         <v>183340</v>
@@ -35111,7 +35111,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.461751282215118</v>
+        <v>0.461751252412796</v>
       </c>
       <c r="H1198" t="n">
         <v>269636</v>
@@ -35140,7 +35140,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.463290363550186</v>
+        <v>0.463290393352509</v>
       </c>
       <c r="H1199" t="n">
         <v>118245</v>
@@ -35169,7 +35169,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.418654441833496</v>
+        <v>0.418654471635818</v>
       </c>
       <c r="H1200" t="n">
         <v>882587</v>
@@ -35198,7 +35198,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.424811154603958</v>
+        <v>0.424811094999313</v>
       </c>
       <c r="H1201" t="n">
         <v>404475</v>
@@ -35227,7 +35227,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.427889466285706</v>
+        <v>0.427889496088028</v>
       </c>
       <c r="H1202" t="n">
         <v>129885</v>
@@ -35285,7 +35285,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.412497788667679</v>
+        <v>0.412497758865356</v>
       </c>
       <c r="H1204" t="n">
         <v>151804</v>
@@ -35343,7 +35343,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.414036929607391</v>
+        <v>0.414036899805069</v>
       </c>
       <c r="H1206" t="n">
         <v>94987</v>
@@ -35401,7 +35401,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.438663691282272</v>
+        <v>0.43866366147995</v>
       </c>
       <c r="H1208" t="n">
         <v>1353750</v>
@@ -35430,7 +35430,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.427889466285706</v>
+        <v>0.427889496088028</v>
       </c>
       <c r="H1209" t="n">
         <v>441074</v>
@@ -35575,7 +35575,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.417115300893784</v>
+        <v>0.417115271091461</v>
       </c>
       <c r="H1214" t="n">
         <v>133638</v>
@@ -35778,7 +35778,7 @@
         <v>0.488999992609024</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.376327246427536</v>
+        <v>0.376327276229858</v>
       </c>
       <c r="H1221" t="n">
         <v>116191</v>
@@ -35807,7 +35807,7 @@
         <v>0.486000001430511</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.374018520116806</v>
+        <v>0.374018490314484</v>
       </c>
       <c r="H1222" t="n">
         <v>107681</v>
@@ -35923,7 +35923,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.346313416957855</v>
+        <v>0.346313387155533</v>
       </c>
       <c r="H1226" t="n">
         <v>175264</v>
@@ -35952,7 +35952,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.327073782682419</v>
+        <v>0.327073812484741</v>
       </c>
       <c r="H1227" t="n">
         <v>270285</v>
@@ -35981,7 +35981,7 @@
         <v>0.425000011920929</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.327073782682419</v>
+        <v>0.327073812484741</v>
       </c>
       <c r="H1228" t="n">
         <v>69004</v>
@@ -36010,7 +36010,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.35400927066803</v>
+        <v>0.354009240865707</v>
       </c>
       <c r="H1229" t="n">
         <v>89162</v>
@@ -36039,7 +36039,7 @@
         <v>0.446999996900558</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.344004690647125</v>
+        <v>0.344004660844803</v>
       </c>
       <c r="H1230" t="n">
         <v>87120</v>
@@ -36213,7 +36213,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.403262734413147</v>
+        <v>0.403262704610825</v>
       </c>
       <c r="H1236" t="n">
         <v>253815</v>
@@ -36242,7 +36242,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.406341135501862</v>
+        <v>0.406341075897217</v>
       </c>
       <c r="H1237" t="n">
         <v>336216</v>
@@ -36358,7 +36358,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.418654441833496</v>
+        <v>0.418654471635818</v>
       </c>
       <c r="H1241" t="n">
         <v>237076</v>
@@ -36387,7 +36387,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.424811154603958</v>
+        <v>0.424811094999313</v>
       </c>
       <c r="H1242" t="n">
         <v>319066</v>
@@ -36445,7 +36445,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.414036929607391</v>
+        <v>0.414036899805069</v>
       </c>
       <c r="H1244" t="n">
         <v>154505</v>
@@ -36474,7 +36474,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.421732753515244</v>
+        <v>0.421732783317566</v>
       </c>
       <c r="H1245" t="n">
         <v>261136</v>
@@ -36503,7 +36503,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.452516138553619</v>
+        <v>0.452516198158264</v>
       </c>
       <c r="H1246" t="n">
         <v>895798</v>
@@ -36532,7 +36532,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.461751282215118</v>
+        <v>0.461751252412796</v>
       </c>
       <c r="H1247" t="n">
         <v>773318</v>
@@ -36561,7 +36561,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.483299642801285</v>
+        <v>0.483299672603607</v>
       </c>
       <c r="H1248" t="n">
         <v>1110379</v>
@@ -36590,7 +36590,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.470986247062683</v>
+        <v>0.470986276865005</v>
       </c>
       <c r="H1249" t="n">
         <v>424477</v>
@@ -36619,7 +36619,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.463290363550186</v>
+        <v>0.463290393352509</v>
       </c>
       <c r="H1250" t="n">
         <v>226396</v>
@@ -36677,7 +36677,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.452516138553619</v>
+        <v>0.452516198158264</v>
       </c>
       <c r="H1252" t="n">
         <v>137875</v>
@@ -36706,7 +36706,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.446359515190125</v>
+        <v>0.446359544992447</v>
       </c>
       <c r="H1253" t="n">
         <v>135219</v>
@@ -36735,7 +36735,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.447898715734482</v>
+        <v>0.447898685932159</v>
       </c>
       <c r="H1254" t="n">
         <v>209340</v>
@@ -36764,7 +36764,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.460212081670761</v>
+        <v>0.460212051868439</v>
       </c>
       <c r="H1255" t="n">
         <v>161790</v>
@@ -36822,7 +36822,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.441742032766342</v>
+        <v>0.44174200296402</v>
       </c>
       <c r="H1257" t="n">
         <v>158276</v>
@@ -36851,7 +36851,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.438663691282272</v>
+        <v>0.43866366147995</v>
       </c>
       <c r="H1258" t="n">
         <v>125369</v>
@@ -36880,7 +36880,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.446359515190125</v>
+        <v>0.446359544992447</v>
       </c>
       <c r="H1259" t="n">
         <v>165630</v>
@@ -36909,7 +36909,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.457133680582047</v>
+        <v>0.457133740186691</v>
       </c>
       <c r="H1260" t="n">
         <v>367412</v>
@@ -36996,7 +36996,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.444820284843445</v>
+        <v>0.444820374250412</v>
       </c>
       <c r="H1263" t="n">
         <v>209301</v>
@@ -37025,7 +37025,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.446359515190125</v>
+        <v>0.446359544992447</v>
       </c>
       <c r="H1264" t="n">
         <v>79796</v>
@@ -37054,7 +37054,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.432506948709488</v>
+        <v>0.43250697851181</v>
       </c>
       <c r="H1265" t="n">
         <v>162180</v>
@@ -37141,7 +37141,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.438663691282272</v>
+        <v>0.43866366147995</v>
       </c>
       <c r="H1268" t="n">
         <v>503273</v>
@@ -37170,7 +37170,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.438663691282272</v>
+        <v>0.43866366147995</v>
       </c>
       <c r="H1269" t="n">
         <v>276073</v>
@@ -37199,7 +37199,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.438663691282272</v>
+        <v>0.43866366147995</v>
       </c>
       <c r="H1270" t="n">
         <v>67708</v>
@@ -37228,7 +37228,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.447898715734482</v>
+        <v>0.447898685932159</v>
       </c>
       <c r="H1271" t="n">
         <v>183319</v>
@@ -37257,7 +37257,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.444820284843445</v>
+        <v>0.444820374250412</v>
       </c>
       <c r="H1272" t="n">
         <v>239362</v>
@@ -37286,7 +37286,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.447898715734482</v>
+        <v>0.447898685932159</v>
       </c>
       <c r="H1273" t="n">
         <v>250356</v>
@@ -37373,7 +37373,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.432506948709488</v>
+        <v>0.43250697851181</v>
       </c>
       <c r="H1276" t="n">
         <v>78741</v>
@@ -37576,7 +37576,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.427889466285706</v>
+        <v>0.427889496088028</v>
       </c>
       <c r="H1283" t="n">
         <v>181544</v>
@@ -37634,7 +37634,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.418654441833496</v>
+        <v>0.418654471635818</v>
       </c>
       <c r="H1285" t="n">
         <v>193498</v>
@@ -37692,7 +37692,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.418654441833496</v>
+        <v>0.418654471635818</v>
       </c>
       <c r="H1287" t="n">
         <v>190882</v>
@@ -37721,7 +37721,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.409419387578964</v>
+        <v>0.409419447183609</v>
       </c>
       <c r="H1288" t="n">
         <v>58629</v>
@@ -37750,7 +37750,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.412497788667679</v>
+        <v>0.412497758865356</v>
       </c>
       <c r="H1289" t="n">
         <v>78989</v>
@@ -37779,7 +37779,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.412497788667679</v>
+        <v>0.412497758865356</v>
       </c>
       <c r="H1290" t="n">
         <v>74965</v>
@@ -37808,7 +37808,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.414036929607391</v>
+        <v>0.414036899805069</v>
       </c>
       <c r="H1291" t="n">
         <v>986358</v>
@@ -37837,7 +37837,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.421732753515244</v>
+        <v>0.421732783317566</v>
       </c>
       <c r="H1292" t="n">
         <v>196581</v>
@@ -37953,7 +37953,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.434046119451523</v>
+        <v>0.434046179056168</v>
       </c>
       <c r="H1296" t="n">
         <v>234732</v>
@@ -38185,7 +38185,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.414036929607391</v>
+        <v>0.414036899805069</v>
       </c>
       <c r="H1304" t="n">
         <v>85250</v>
@@ -38214,7 +38214,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.409419387578964</v>
+        <v>0.409419447183609</v>
       </c>
       <c r="H1305" t="n">
         <v>237351</v>
@@ -38243,7 +38243,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.427889466285706</v>
+        <v>0.427889496088028</v>
       </c>
       <c r="H1306" t="n">
         <v>647263</v>
@@ -38301,7 +38301,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.421732753515244</v>
+        <v>0.421732783317566</v>
       </c>
       <c r="H1308" t="n">
         <v>286565</v>
@@ -38330,7 +38330,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.424811154603958</v>
+        <v>0.424811094999313</v>
       </c>
       <c r="H1309" t="n">
         <v>172798</v>
@@ -38359,7 +38359,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.421732753515244</v>
+        <v>0.421732783317566</v>
       </c>
       <c r="H1310" t="n">
         <v>166323</v>
@@ -38388,7 +38388,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.438663691282272</v>
+        <v>0.43866366147995</v>
       </c>
       <c r="H1311" t="n">
         <v>1674003</v>
@@ -38475,7 +38475,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.460212081670761</v>
+        <v>0.460212051868439</v>
       </c>
       <c r="H1314" t="n">
         <v>708879</v>
@@ -38504,7 +38504,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.447898715734482</v>
+        <v>0.447898685932159</v>
       </c>
       <c r="H1315" t="n">
         <v>994928</v>
@@ -38562,7 +38562,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.469447106122971</v>
+        <v>0.469447076320648</v>
       </c>
       <c r="H1317" t="n">
         <v>529286</v>
@@ -38591,7 +38591,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.458672881126404</v>
+        <v>0.458672910928726</v>
       </c>
       <c r="H1318" t="n">
         <v>263744</v>
@@ -38620,7 +38620,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.457133680582047</v>
+        <v>0.457133740186691</v>
       </c>
       <c r="H1319" t="n">
         <v>312500</v>
@@ -38649,7 +38649,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.470986247062683</v>
+        <v>0.470986276865005</v>
       </c>
       <c r="H1320" t="n">
         <v>221091</v>
@@ -38678,7 +38678,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.458672881126404</v>
+        <v>0.458672910928726</v>
       </c>
       <c r="H1321" t="n">
         <v>445253</v>
@@ -38765,7 +38765,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.467907875776291</v>
+        <v>0.467907905578613</v>
       </c>
       <c r="H1324" t="n">
         <v>233624</v>
@@ -38823,7 +38823,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.461751282215118</v>
+        <v>0.461751252412796</v>
       </c>
       <c r="H1326" t="n">
         <v>299991</v>
@@ -38881,7 +38881,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.467907875776291</v>
+        <v>0.467907905578613</v>
       </c>
       <c r="H1328" t="n">
         <v>87083</v>
@@ -38910,7 +38910,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.460212081670761</v>
+        <v>0.460212051868439</v>
       </c>
       <c r="H1329" t="n">
         <v>166371</v>
@@ -38968,7 +38968,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.472525417804718</v>
+        <v>0.472525507211685</v>
       </c>
       <c r="H1331" t="n">
         <v>211641</v>
@@ -38997,7 +38997,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.478682100772858</v>
+        <v>0.478682070970535</v>
       </c>
       <c r="H1332" t="n">
         <v>284071</v>
@@ -39026,7 +39026,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.483299642801285</v>
+        <v>0.483299672603607</v>
       </c>
       <c r="H1333" t="n">
         <v>247130</v>
@@ -39113,7 +39113,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.535631418228149</v>
+        <v>0.535631477832794</v>
       </c>
       <c r="H1336" t="n">
         <v>680975</v>
@@ -39142,7 +39142,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.551023125648499</v>
+        <v>0.551023185253143</v>
       </c>
       <c r="H1337" t="n">
         <v>832527</v>
@@ -39200,7 +39200,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.544866442680359</v>
+        <v>0.544866502285004</v>
       </c>
       <c r="H1339" t="n">
         <v>329002</v>
@@ -39229,7 +39229,7 @@
         <v>0.683000028133392</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.525626838207245</v>
+        <v>0.52562689781189</v>
       </c>
       <c r="H1340" t="n">
         <v>659690</v>
@@ -39258,7 +39258,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.51947009563446</v>
+        <v>0.519470155239105</v>
       </c>
       <c r="H1341" t="n">
         <v>451822</v>
@@ -39287,7 +39287,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.546405553817749</v>
+        <v>0.546405613422394</v>
       </c>
       <c r="H1342" t="n">
         <v>514093</v>
@@ -39403,7 +39403,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.52177882194519</v>
+        <v>0.52177894115448</v>
       </c>
       <c r="H1346" t="n">
         <v>365824</v>
@@ -39432,7 +39432,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.531013965606689</v>
+        <v>0.531013906002045</v>
       </c>
       <c r="H1347" t="n">
         <v>278536</v>
@@ -39635,7 +39635,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.530244290828705</v>
+        <v>0.530244410037994</v>
       </c>
       <c r="H1354" t="n">
         <v>323462</v>
@@ -39664,7 +39664,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.51716136932373</v>
+        <v>0.517161428928375</v>
       </c>
       <c r="H1355" t="n">
         <v>623783</v>
@@ -39693,7 +39693,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.53717052936554</v>
+        <v>0.537170648574829</v>
       </c>
       <c r="H1356" t="n">
         <v>276274</v>
@@ -39722,7 +39722,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.53486180305481</v>
+        <v>0.534861862659454</v>
       </c>
       <c r="H1357" t="n">
         <v>573994</v>
@@ -39751,7 +39751,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.53486180305481</v>
+        <v>0.534861862659454</v>
       </c>
       <c r="H1358" t="n">
         <v>169995</v>
@@ -39809,7 +39809,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.548714399337769</v>
+        <v>0.548714339733124</v>
       </c>
       <c r="H1360" t="n">
         <v>343505</v>
@@ -39867,7 +39867,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.554101526737213</v>
+        <v>0.554101586341858</v>
       </c>
       <c r="H1362" t="n">
         <v>547568</v>
@@ -39925,7 +39925,7 @@
         <v>0.676999986171722</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.521009266376495</v>
+        <v>0.52100932598114</v>
       </c>
       <c r="H1364" t="n">
         <v>465535</v>
@@ -40012,7 +40012,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.52177882194519</v>
+        <v>0.52177894115448</v>
       </c>
       <c r="H1367" t="n">
         <v>460070</v>
@@ -40070,7 +40070,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.535631418228149</v>
+        <v>0.535631477832794</v>
       </c>
       <c r="H1369" t="n">
         <v>476943</v>
@@ -40128,7 +40128,7 @@
         <v>0.680999994277954</v>
       </c>
       <c r="G1371" t="n">
-        <v>0.52408766746521</v>
+        <v>0.524087607860565</v>
       </c>
       <c r="H1371" t="n">
         <v>134666</v>
@@ -40157,7 +40157,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1372" t="n">
-        <v>0.52485716342926</v>
+        <v>0.52485728263855</v>
       </c>
       <c r="H1372" t="n">
         <v>156011</v>
@@ -40186,7 +40186,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.52177882194519</v>
+        <v>0.52177894115448</v>
       </c>
       <c r="H1373" t="n">
         <v>223935</v>
@@ -40244,7 +40244,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.52947473526001</v>
+        <v>0.529474794864655</v>
       </c>
       <c r="H1375" t="n">
         <v>179169</v>
@@ -40302,7 +40302,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.531013965606689</v>
+        <v>0.531013906002045</v>
       </c>
       <c r="H1377" t="n">
         <v>207250</v>
@@ -40447,7 +40447,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.54224705696106</v>
+        <v>0.542247116565704</v>
       </c>
       <c r="H1382" t="n">
         <v>219123</v>
@@ -40476,7 +40476,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G1383" t="n">
-        <v>0.54940277338028</v>
+        <v>0.549402832984924</v>
       </c>
       <c r="H1383" t="n">
         <v>193207</v>
@@ -40505,7 +40505,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.547812700271606</v>
+        <v>0.547812759876251</v>
       </c>
       <c r="H1384" t="n">
         <v>123192</v>
@@ -40621,7 +40621,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.516804337501526</v>
+        <v>0.516804397106171</v>
       </c>
       <c r="H1388" t="n">
         <v>328131</v>
@@ -40679,7 +40679,7 @@
         <v>0.652999997138977</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.519189655780792</v>
+        <v>0.519189715385437</v>
       </c>
       <c r="H1390" t="n">
         <v>155332</v>
@@ -40737,7 +40737,7 @@
         <v>0.638999998569489</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.508058488368988</v>
+        <v>0.508058547973633</v>
       </c>
       <c r="H1392" t="n">
         <v>324094</v>
@@ -40795,7 +40795,7 @@
         <v>0.620999991893768</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.493746936321259</v>
+        <v>0.493746995925903</v>
       </c>
       <c r="H1394" t="n">
         <v>293783</v>
@@ -41027,7 +41027,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.473074853420258</v>
+        <v>0.473074793815613</v>
       </c>
       <c r="H1402" t="n">
         <v>272422</v>
@@ -41056,7 +41056,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.47864031791687</v>
+        <v>0.478640377521515</v>
       </c>
       <c r="H1403" t="n">
         <v>141724</v>
@@ -41085,7 +41085,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.473074853420258</v>
+        <v>0.473074793815613</v>
       </c>
       <c r="H1404" t="n">
         <v>177339</v>
@@ -41172,7 +41172,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.445246875286102</v>
+        <v>0.445246905088425</v>
       </c>
       <c r="H1407" t="n">
         <v>375689</v>
@@ -41230,7 +41230,7 @@
         <v>0.555000007152557</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.44127145409584</v>
+        <v>0.441271483898163</v>
       </c>
       <c r="H1409" t="n">
         <v>412845</v>
@@ -41288,7 +41288,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.453197717666626</v>
+        <v>0.453197687864304</v>
       </c>
       <c r="H1411" t="n">
         <v>122224</v>
@@ -41317,7 +41317,7 @@
         <v>0.569000005722046</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.452402621507645</v>
+        <v>0.452402651309967</v>
       </c>
       <c r="H1412" t="n">
         <v>82504</v>
@@ -41433,7 +41433,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.481025665998459</v>
+        <v>0.481025725603104</v>
       </c>
       <c r="H1416" t="n">
         <v>278739</v>
@@ -41491,7 +41491,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.481025665998459</v>
+        <v>0.481025725603104</v>
       </c>
       <c r="H1418" t="n">
         <v>236482</v>
@@ -41520,7 +41520,7 @@
         <v>0.609000027179718</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.484206020832062</v>
+        <v>0.484205961227417</v>
       </c>
       <c r="H1419" t="n">
         <v>256116</v>
@@ -41549,7 +41549,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.481025665998459</v>
+        <v>0.481025725603104</v>
       </c>
       <c r="H1420" t="n">
         <v>187782</v>
@@ -41578,7 +41578,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.488181412220001</v>
+        <v>0.488181471824646</v>
       </c>
       <c r="H1421" t="n">
         <v>128176</v>
@@ -41810,7 +41810,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.473869860172272</v>
+        <v>0.473869919776917</v>
       </c>
       <c r="H1429" t="n">
         <v>222698</v>
@@ -41839,7 +41839,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.473074853420258</v>
+        <v>0.473074793815613</v>
       </c>
       <c r="H1430" t="n">
         <v>80654</v>
@@ -41897,7 +41897,7 @@
         <v>0.583000004291534</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.463533759117126</v>
+        <v>0.463533818721771</v>
       </c>
       <c r="H1432" t="n">
         <v>442549</v>
@@ -41926,7 +41926,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1433" t="n">
-        <v>0.461148500442505</v>
+        <v>0.46114856004715</v>
       </c>
       <c r="H1433" t="n">
         <v>58126</v>
@@ -42013,7 +42013,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.461148500442505</v>
+        <v>0.46114856004715</v>
       </c>
       <c r="H1436" t="n">
         <v>92155</v>
@@ -42100,7 +42100,7 @@
         <v>0.583000004291534</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.463533759117126</v>
+        <v>0.463533818721771</v>
       </c>
       <c r="H1439" t="n">
         <v>58762</v>
@@ -42187,7 +42187,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.473869860172272</v>
+        <v>0.473869919776917</v>
       </c>
       <c r="H1442" t="n">
         <v>174128</v>
@@ -42216,7 +42216,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.473074853420258</v>
+        <v>0.473074793815613</v>
       </c>
       <c r="H1443" t="n">
         <v>163285</v>
@@ -42361,7 +42361,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.454787939786911</v>
+        <v>0.454787909984589</v>
       </c>
       <c r="H1448" t="n">
         <v>130639</v>
@@ -42419,7 +42419,7 @@
         <v>0.573000013828278</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.455582916736603</v>
+        <v>0.455582976341248</v>
       </c>
       <c r="H1450" t="n">
         <v>85315</v>
@@ -42448,7 +42448,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.453197717666626</v>
+        <v>0.453197687864304</v>
       </c>
       <c r="H1451" t="n">
         <v>139474</v>
@@ -42506,7 +42506,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.47864031791687</v>
+        <v>0.478640377521515</v>
       </c>
       <c r="H1453" t="n">
         <v>882178</v>
@@ -42622,7 +42622,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.504878103733063</v>
+        <v>0.504878163337708</v>
       </c>
       <c r="H1457" t="n">
         <v>705149</v>
@@ -42709,7 +42709,7 @@
         <v>0.638999998569489</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.508058488368988</v>
+        <v>0.508058547973633</v>
       </c>
       <c r="H1460" t="n">
         <v>441717</v>
@@ -42970,7 +42970,7 @@
         <v>0.633000016212463</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.503287971019745</v>
+        <v>0.50328803062439</v>
       </c>
       <c r="H1469" t="n">
         <v>253671</v>
@@ -42999,7 +42999,7 @@
         <v>0.633000016212463</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.503287971019745</v>
+        <v>0.50328803062439</v>
       </c>
       <c r="H1470" t="n">
         <v>346461</v>
@@ -43057,7 +43057,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G1472" t="n">
-        <v>0.530320763587952</v>
+        <v>0.530320823192596</v>
       </c>
       <c r="H1472" t="n">
         <v>1420962</v>
@@ -43115,7 +43115,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.550197839736938</v>
+        <v>0.550197899341583</v>
       </c>
       <c r="H1474" t="n">
         <v>1040691</v>
@@ -43260,7 +43260,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.550197839736938</v>
+        <v>0.550197899341583</v>
       </c>
       <c r="H1479" t="n">
         <v>434690</v>
@@ -43347,7 +43347,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.554968357086182</v>
+        <v>0.554968476295471</v>
       </c>
       <c r="H1482" t="n">
         <v>686301</v>
@@ -43434,7 +43434,7 @@
         <v>0.669000029563904</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.531911015510559</v>
+        <v>0.531911075115204</v>
       </c>
       <c r="H1485" t="n">
         <v>264285</v>
@@ -43579,7 +43579,7 @@
         <v>0.683000028133392</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.543042182922363</v>
+        <v>0.543042242527008</v>
       </c>
       <c r="H1490" t="n">
         <v>223482</v>
@@ -43695,7 +43695,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.52793550491333</v>
+        <v>0.52793562412262</v>
       </c>
       <c r="H1494" t="n">
         <v>204069</v>
@@ -43724,7 +43724,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.539861857891083</v>
+        <v>0.539861798286438</v>
       </c>
       <c r="H1495" t="n">
         <v>322584</v>
@@ -43840,7 +43840,7 @@
         <v>0.640999972820282</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.509648680686951</v>
+        <v>0.509648621082306</v>
       </c>
       <c r="H1499" t="n">
         <v>247094</v>
@@ -43869,7 +43869,7 @@
         <v>0.633000016212463</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.503287971019745</v>
+        <v>0.50328803062439</v>
       </c>
       <c r="H1500" t="n">
         <v>261496</v>
@@ -43898,7 +43898,7 @@
         <v>0.633000016212463</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.503287971019745</v>
+        <v>0.50328803062439</v>
       </c>
       <c r="H1501" t="n">
         <v>416845</v>
@@ -43927,7 +43927,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.501697719097137</v>
+        <v>0.501697838306427</v>
       </c>
       <c r="H1502" t="n">
         <v>182876</v>
@@ -44043,7 +44043,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.498517513275146</v>
+        <v>0.498517453670502</v>
       </c>
       <c r="H1506" t="n">
         <v>198237</v>
@@ -44217,7 +44217,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.498517513275146</v>
+        <v>0.498517453670502</v>
       </c>
       <c r="H1512" t="n">
         <v>90714</v>
@@ -44246,7 +44246,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.501697719097137</v>
+        <v>0.501697838306427</v>
       </c>
       <c r="H1513" t="n">
         <v>183018</v>
@@ -44333,7 +44333,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.488181412220001</v>
+        <v>0.488181471824646</v>
       </c>
       <c r="H1516" t="n">
         <v>42811</v>
@@ -44623,7 +44623,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.488181412220001</v>
+        <v>0.488181471824646</v>
       </c>
       <c r="H1526" t="n">
         <v>115269</v>
@@ -44681,7 +44681,7 @@
         <v>0.633000016212463</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.503287971019745</v>
+        <v>0.50328803062439</v>
       </c>
       <c r="H1528" t="n">
         <v>543417</v>
@@ -44710,7 +44710,7 @@
         <v>0.638999998569489</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.508058488368988</v>
+        <v>0.508058547973633</v>
       </c>
       <c r="H1529" t="n">
         <v>203055</v>
@@ -44797,7 +44797,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.488181412220001</v>
+        <v>0.488181471824646</v>
       </c>
       <c r="H1532" t="n">
         <v>320295</v>
@@ -45116,7 +45116,7 @@
         <v>0.587000012397766</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.466714113950729</v>
+        <v>0.466714173555374</v>
       </c>
       <c r="H1543" t="n">
         <v>219352</v>
@@ -45145,7 +45145,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.473074853420258</v>
+        <v>0.473074793815613</v>
       </c>
       <c r="H1544" t="n">
         <v>139101</v>
@@ -45174,7 +45174,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.473869860172272</v>
+        <v>0.473869919776917</v>
       </c>
       <c r="H1545" t="n">
         <v>240539</v>
@@ -45203,7 +45203,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.467509180307388</v>
+        <v>0.467509210109711</v>
       </c>
       <c r="H1546" t="n">
         <v>232161</v>
@@ -45290,7 +45290,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.474664956331253</v>
+        <v>0.474664986133575</v>
       </c>
       <c r="H1549" t="n">
         <v>80236</v>
@@ -45319,7 +45319,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.473869860172272</v>
+        <v>0.473869919776917</v>
       </c>
       <c r="H1550" t="n">
         <v>143133</v>
@@ -45377,7 +45377,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1552" t="n">
-        <v>0.464328914880753</v>
+        <v>0.464328855276108</v>
       </c>
       <c r="H1552" t="n">
         <v>202244</v>
@@ -45435,7 +45435,7 @@
         <v>0.573000013828278</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.455582916736603</v>
+        <v>0.455582976341248</v>
       </c>
       <c r="H1554" t="n">
         <v>226593</v>
@@ -45522,7 +45522,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.434115678071976</v>
+        <v>0.434115707874298</v>
       </c>
       <c r="H1557" t="n">
         <v>890249</v>
@@ -45580,7 +45580,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.457968145608902</v>
+        <v>0.457968175411224</v>
       </c>
       <c r="H1559" t="n">
         <v>167718</v>
@@ -45609,7 +45609,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G1560" t="n">
-        <v>0.445246875286102</v>
+        <v>0.445246905088425</v>
       </c>
       <c r="H1560" t="n">
         <v>132327</v>
@@ -45667,7 +45667,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.4293452501297</v>
+        <v>0.429345220327377</v>
       </c>
       <c r="H1562" t="n">
         <v>150820</v>
@@ -45696,7 +45696,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.420599281787872</v>
+        <v>0.42059925198555</v>
       </c>
       <c r="H1563" t="n">
         <v>272694</v>
@@ -45725,7 +45725,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.419804215431213</v>
+        <v>0.419804185628891</v>
       </c>
       <c r="H1564" t="n">
         <v>534927</v>
@@ -45841,7 +45841,7 @@
         <v>0.495000004768372</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.393566459417343</v>
+        <v>0.393566429615021</v>
       </c>
       <c r="H1568" t="n">
         <v>219968</v>
@@ -45899,7 +45899,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.378459841012955</v>
+        <v>0.378459870815277</v>
       </c>
       <c r="H1570" t="n">
         <v>505658</v>
@@ -45928,7 +45928,7 @@
         <v>0.453500002622604</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.360570430755615</v>
+        <v>0.360570460557938</v>
       </c>
       <c r="H1571" t="n">
         <v>780792</v>
@@ -46015,7 +46015,7 @@
         <v>0.497500002384186</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.395554155111313</v>
+        <v>0.39555412530899</v>
       </c>
       <c r="H1574" t="n">
         <v>260196</v>
@@ -46247,7 +46247,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.424574643373489</v>
+        <v>0.424574673175812</v>
       </c>
       <c r="H1582" t="n">
         <v>694972</v>
@@ -46276,7 +46276,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.4293452501297</v>
+        <v>0.429345220327377</v>
       </c>
       <c r="H1583" t="n">
         <v>239953</v>
@@ -46334,7 +46334,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1585" t="n">
-        <v>0.417418897151947</v>
+        <v>0.417418926954269</v>
       </c>
       <c r="H1585" t="n">
         <v>192806</v>
@@ -46392,7 +46392,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.4293452501297</v>
+        <v>0.429345220327377</v>
       </c>
       <c r="H1587" t="n">
         <v>225248</v>
@@ -46566,7 +46566,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.415828824043274</v>
+        <v>0.415828794240952</v>
       </c>
       <c r="H1593" t="n">
         <v>1069373</v>
@@ -46653,7 +46653,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.406287789344788</v>
+        <v>0.406287759542465</v>
       </c>
       <c r="H1596" t="n">
         <v>585124</v>
@@ -46682,7 +46682,7 @@
         <v>0.535000026226044</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.425369799137115</v>
+        <v>0.425369828939438</v>
       </c>
       <c r="H1597" t="n">
         <v>433543</v>
@@ -46711,7 +46711,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.427755028009415</v>
+        <v>0.427754998207092</v>
       </c>
       <c r="H1598" t="n">
         <v>376023</v>
@@ -46769,7 +46769,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1600" t="n">
-        <v>0.4293452501297</v>
+        <v>0.429345220327377</v>
       </c>
       <c r="H1600" t="n">
         <v>185112</v>
@@ -46798,7 +46798,7 @@
         <v>0.556999981403351</v>
       </c>
       <c r="G1601" t="n">
-        <v>0.442861646413803</v>
+        <v>0.442861586809158</v>
       </c>
       <c r="H1601" t="n">
         <v>357555</v>
@@ -46856,7 +46856,7 @@
         <v>0.583000004291534</v>
       </c>
       <c r="G1603" t="n">
-        <v>0.463533759117126</v>
+        <v>0.463533818721771</v>
       </c>
       <c r="H1603" t="n">
         <v>310571</v>
@@ -46885,7 +46885,7 @@
         <v>0.583000004291534</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.463533759117126</v>
+        <v>0.463533818721771</v>
       </c>
       <c r="H1604" t="n">
         <v>203345</v>
@@ -46943,7 +46943,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.450017392635345</v>
+        <v>0.450017362833023</v>
       </c>
       <c r="H1606" t="n">
         <v>67908</v>
@@ -47001,7 +47001,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.417418897151947</v>
+        <v>0.417418926954269</v>
       </c>
       <c r="H1608" t="n">
         <v>577979</v>
@@ -47030,7 +47030,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.424574643373489</v>
+        <v>0.424574673175812</v>
       </c>
       <c r="H1609" t="n">
         <v>99990</v>
@@ -47117,7 +47117,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1612" t="n">
-        <v>0.417418897151947</v>
+        <v>0.417418926954269</v>
       </c>
       <c r="H1612" t="n">
         <v>125095</v>
@@ -47146,7 +47146,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.410263180732727</v>
+        <v>0.410263150930405</v>
       </c>
       <c r="H1613" t="n">
         <v>174026</v>
@@ -47204,7 +47204,7 @@
         <v>0.493000000715256</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.391976237297058</v>
+        <v>0.39197626709938</v>
       </c>
       <c r="H1615" t="n">
         <v>224984</v>
@@ -47291,7 +47291,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.411853343248367</v>
+        <v>0.41185337305069</v>
       </c>
       <c r="H1618" t="n">
         <v>119802</v>
@@ -47378,7 +47378,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.406287789344788</v>
+        <v>0.406287759542465</v>
       </c>
       <c r="H1621" t="n">
         <v>336966</v>
@@ -47407,7 +47407,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.406287789344788</v>
+        <v>0.406287759542465</v>
       </c>
       <c r="H1622" t="n">
         <v>140252</v>
@@ -47436,7 +47436,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G1623" t="n">
-        <v>0.411853343248367</v>
+        <v>0.41185337305069</v>
       </c>
       <c r="H1623" t="n">
         <v>365244</v>
@@ -47494,7 +47494,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G1625" t="n">
-        <v>0.410263180732727</v>
+        <v>0.410263150930405</v>
       </c>
       <c r="H1625" t="n">
         <v>161374</v>
@@ -47523,7 +47523,7 @@
         <v>0.5</v>
       </c>
       <c r="G1626" t="n">
-        <v>0.39754182100296</v>
+        <v>0.397541850805283</v>
       </c>
       <c r="H1626" t="n">
         <v>87823</v>
@@ -47581,7 +47581,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G1628" t="n">
-        <v>0.411853343248367</v>
+        <v>0.41185337305069</v>
       </c>
       <c r="H1628" t="n">
         <v>76795</v>
@@ -47610,7 +47610,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.411853343248367</v>
+        <v>0.41185337305069</v>
       </c>
       <c r="H1629" t="n">
         <v>218909</v>
@@ -47639,7 +47639,7 @@
         <v>0.523000001907349</v>
       </c>
       <c r="G1630" t="n">
-        <v>0.415828824043274</v>
+        <v>0.415828794240952</v>
       </c>
       <c r="H1630" t="n">
         <v>173585</v>
@@ -47755,7 +47755,7 @@
         <v>0.524999976158142</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.417418897151947</v>
+        <v>0.417418926954269</v>
       </c>
       <c r="H1634" t="n">
         <v>41990</v>
@@ -79951,6 +79951,64 @@
         <v>406147</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>436502</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.396499991416931</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>408803</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>
